--- a/packages/data/src/talent.xlsx
+++ b/packages/data/src/talent.xlsx
@@ -1,1378 +1,1390 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vick\dev\lifeRestart\packages\data\src\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA48E9A-8385-4104-9854-1D99E52CEA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="5010" yWindow="1460" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="talent"/>
+    <sheet name="talent" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="447">
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>exclusive</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>effect:SPR</t>
+  </si>
+  <si>
+    <t>effect:MNY</t>
+  </si>
+  <si>
+    <t>effect:CHR</t>
+  </si>
+  <si>
+    <t>effect:STR</t>
+  </si>
+  <si>
+    <t>effect:INT</t>
+  </si>
+  <si>
+    <t>replacement:grade[]</t>
+  </si>
+  <si>
+    <t>replacement:talent[]</t>
+  </si>
+  <si>
+    <t>exclude[]</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>天赋名</t>
+  </si>
+  <si>
+    <t>括号中的内容</t>
+  </si>
+  <si>
+    <t>触发条件</t>
+  </si>
+  <si>
+    <t>稀有度</t>
+  </si>
+  <si>
+    <t>专属天赋</t>
+  </si>
+  <si>
+    <t>初始可用属性点</t>
+  </si>
+  <si>
+    <t>额外快乐</t>
+  </si>
+  <si>
+    <t>额外家境</t>
+  </si>
+  <si>
+    <t>额外颜值</t>
+  </si>
+  <si>
+    <t>额外体质</t>
+  </si>
+  <si>
+    <t>额外智力</t>
+  </si>
+  <si>
+    <t>随机属性</t>
+  </si>
+  <si>
+    <t>替换成某稀有度的天赋</t>
+  </si>
+  <si>
+    <t>替换成某天赋</t>
+  </si>
+  <si>
+    <t>互斥天赋</t>
+  </si>
+  <si>
+    <t>随身玉佩</t>
+  </si>
+  <si>
+    <t>或许有护佑作用</t>
+  </si>
+  <si>
+    <t>红肚兜</t>
+  </si>
+  <si>
+    <t>小时候死亡率降低</t>
+  </si>
+  <si>
+    <t>生而为男</t>
+  </si>
+  <si>
+    <t>性别一定为男</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>生而为女</t>
+  </si>
+  <si>
+    <t>性别一定为女</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>动漫高手</t>
+  </si>
+  <si>
+    <t>入宅的可能性翻6倍</t>
+  </si>
+  <si>
+    <t>乐观</t>
+  </si>
+  <si>
+    <t>快乐+1</t>
+  </si>
+  <si>
+    <t>天赋异禀</t>
+  </si>
+  <si>
+    <t>初始可用属性点+2</t>
+  </si>
+  <si>
+    <t>天生抑郁</t>
+  </si>
+  <si>
+    <t>快乐-3</t>
+  </si>
+  <si>
+    <t>网络巨魔</t>
+  </si>
+  <si>
+    <t>快乐+2</t>
+  </si>
+  <si>
+    <t>天龙人</t>
+  </si>
+  <si>
+    <t>你拥有北京户口</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>独生子女</t>
+  </si>
+  <si>
+    <t>你没有兄弟姐妹</t>
+  </si>
+  <si>
+    <t>乡间微风</t>
+  </si>
+  <si>
+    <t>你出生在农村</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>城中高楼</t>
+  </si>
+  <si>
+    <t>你出生在城市</t>
+  </si>
+  <si>
+    <t>美籍华人</t>
+  </si>
+  <si>
+    <t>你有美国国籍</t>
+  </si>
+  <si>
+    <t>家中老大</t>
+  </si>
+  <si>
+    <t>你最受父母宠爱</t>
+  </si>
+  <si>
+    <t>水性良好</t>
+  </si>
+  <si>
+    <t>不会被淹死</t>
+  </si>
+  <si>
+    <t>先天免疫</t>
+  </si>
+  <si>
+    <t>你不会得艾滋病</t>
+  </si>
+  <si>
+    <t>人类进化</t>
+  </si>
+  <si>
+    <t>所有属性+1</t>
+  </si>
+  <si>
+    <t>超凡</t>
+  </si>
+  <si>
+    <t>初始可用属性点+4</t>
+  </si>
+  <si>
+    <t>父母美貌</t>
+  </si>
+  <si>
+    <t>颜值+2</t>
+  </si>
+  <si>
+    <t>红颜薄命</t>
+  </si>
+  <si>
+    <t>颜值+2，体质-2</t>
+  </si>
+  <si>
+    <t>属蛇</t>
+  </si>
+  <si>
+    <t>不会被蛇咬死</t>
+  </si>
+  <si>
+    <t>半神</t>
+  </si>
+  <si>
+    <t>所有属性+2</t>
+  </si>
+  <si>
+    <t>人中龙凤</t>
+  </si>
+  <si>
+    <t>天生双重性别</t>
+  </si>
+  <si>
+    <t>阴阳之外</t>
+  </si>
+  <si>
+    <t>天生无性别</t>
+  </si>
+  <si>
+    <t>彩虹之下</t>
+  </si>
+  <si>
+    <t>可能和同性交往</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>斩情证道</t>
+  </si>
+  <si>
+    <t>终生不恋爱结婚</t>
+  </si>
+  <si>
+    <t>桃花连连</t>
+  </si>
+  <si>
+    <t>恋爱机会提升</t>
+  </si>
+  <si>
+    <t>平安童年</t>
+  </si>
+  <si>
+    <t>12岁前父母都健在</t>
+  </si>
+  <si>
+    <t>宠物大师</t>
+  </si>
+  <si>
+    <t>宠物不会意外死亡</t>
+  </si>
+  <si>
+    <t>天生残疾</t>
+  </si>
+  <si>
+    <t>体质-2</t>
+  </si>
+  <si>
+    <t>早产儿</t>
+  </si>
+  <si>
+    <t>所有属性-1</t>
+  </si>
+  <si>
+    <t>十死无生</t>
+  </si>
+  <si>
+    <t>体质-10</t>
+  </si>
+  <si>
+    <t>家运不顺</t>
+  </si>
+  <si>
+    <t>家境-2</t>
+  </si>
+  <si>
+    <t>头着地</t>
+  </si>
+  <si>
+    <t>智力-2</t>
+  </si>
+  <si>
+    <t>胎教</t>
+  </si>
+  <si>
+    <t>智力+1</t>
+  </si>
+  <si>
+    <t>班中红人</t>
+  </si>
+  <si>
+    <t>和同学容易处好关系</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>能轻松学会骑车</t>
+  </si>
+  <si>
+    <t>永远的神</t>
+  </si>
+  <si>
+    <t>电竞天才</t>
+  </si>
+  <si>
+    <t>戒律</t>
+  </si>
+  <si>
+    <t>赌毒不沾</t>
+  </si>
+  <si>
+    <t>丁克</t>
+  </si>
+  <si>
+    <t>不生孩子</t>
+  </si>
+  <si>
+    <t>少数民族</t>
+  </si>
+  <si>
+    <t>高考+5分</t>
+  </si>
+  <si>
+    <t>老司机</t>
+  </si>
+  <si>
+    <t>你和家人不会发生车祸</t>
+  </si>
+  <si>
+    <t>低压</t>
+  </si>
+  <si>
+    <t>你的家人不会心脏病</t>
+  </si>
+  <si>
+    <t>战功</t>
+  </si>
+  <si>
+    <t>你退伍后会当官</t>
+  </si>
+  <si>
+    <t>不孕不育</t>
+  </si>
+  <si>
+    <t>你生不出孩子</t>
+  </si>
+  <si>
+    <t>白头偕老</t>
+  </si>
+  <si>
+    <t>爱人至少能活到70岁</t>
+  </si>
+  <si>
+    <t>神秘的小盒子</t>
+  </si>
+  <si>
+    <t>100岁时才能开启</t>
+  </si>
+  <si>
+    <t>三十而立</t>
+  </si>
+  <si>
+    <t>30岁时家境+2</t>
+  </si>
+  <si>
+    <t>AGE?[30]</t>
+  </si>
+  <si>
+    <t>四十不惑</t>
+  </si>
+  <si>
+    <t>40岁时智力+2</t>
+  </si>
+  <si>
+    <t>AGE?[40]</t>
+  </si>
+  <si>
+    <t>知天命</t>
+  </si>
+  <si>
+    <t>50岁时智力、快乐+1</t>
+  </si>
+  <si>
+    <t>AGE?[50]</t>
+  </si>
+  <si>
+    <t>耳顺</t>
+  </si>
+  <si>
+    <t>60岁时快乐+2</t>
+  </si>
+  <si>
+    <t>AGE?[60]</t>
+  </si>
+  <si>
+    <t>从心所欲</t>
+  </si>
+  <si>
+    <t>70岁时快乐+3</t>
+  </si>
+  <si>
+    <t>AGE?[70]</t>
+  </si>
+  <si>
+    <t>老当益壮</t>
+  </si>
+  <si>
+    <t>60岁时体质+2</t>
+  </si>
+  <si>
+    <t>鹤发童颜</t>
+  </si>
+  <si>
+    <t>70岁时颜值+3</t>
+  </si>
+  <si>
+    <t>学前启蒙</t>
+  </si>
+  <si>
+    <t>5岁时智力+2</t>
+  </si>
+  <si>
+    <t>AGE?[5]</t>
+  </si>
+  <si>
+    <t>十八变</t>
+  </si>
+  <si>
+    <t>18岁时颜值+2</t>
+  </si>
+  <si>
+    <t>AGE?[18]</t>
+  </si>
+  <si>
+    <t>迟来之财</t>
+  </si>
+  <si>
+    <t>90岁时家境+4</t>
+  </si>
+  <si>
+    <t>AGE?[90]</t>
+  </si>
+  <si>
+    <t>理财达人</t>
+  </si>
+  <si>
+    <t>40岁时家境+3</t>
+  </si>
+  <si>
+    <t>成熟</t>
+  </si>
+  <si>
+    <t>18岁时智力+2</t>
+  </si>
+  <si>
+    <t>形象管理</t>
+  </si>
+  <si>
+    <t>24岁时颜值+2</t>
+  </si>
+  <si>
+    <t>AGE?[24]</t>
+  </si>
+  <si>
+    <t>成年礼</t>
+  </si>
+  <si>
+    <t>18岁时快乐+1</t>
+  </si>
+  <si>
+    <t>开光之胎</t>
+  </si>
+  <si>
+    <t>初始可用属性点+1</t>
+  </si>
+  <si>
+    <t>天命</t>
+  </si>
+  <si>
+    <t>初始可用属性点+8</t>
+  </si>
+  <si>
+    <t>祖传药丸</t>
+  </si>
+  <si>
+    <t>功能不明</t>
+  </si>
+  <si>
+    <t>精准扶贫</t>
+  </si>
+  <si>
+    <t>家境为0时家境+1</t>
+  </si>
+  <si>
+    <t>(MNY&lt;1)&amp;(MNY&gt;-1)</t>
+  </si>
+  <si>
+    <t>乐天派</t>
+  </si>
+  <si>
+    <t>快乐为0时快乐+1</t>
+  </si>
+  <si>
+    <t>(SPR&lt;1)&amp;(SPR&gt;-1)</t>
+  </si>
+  <si>
+    <t>命悬一线</t>
+  </si>
+  <si>
+    <t>体质为0时体质+1</t>
+  </si>
+  <si>
+    <t>(STR&lt;1)&amp;(STR&gt;-1)</t>
+  </si>
+  <si>
+    <t>智可生财</t>
+  </si>
+  <si>
+    <t>若20岁时智力&gt;8，家境+2</t>
+  </si>
+  <si>
+    <t>(AGE?[20])&amp;(INT&gt;8)</t>
+  </si>
+  <si>
+    <t>舔狗甚多</t>
+  </si>
+  <si>
+    <t>若20岁时颜值&gt;8，快乐+2</t>
+  </si>
+  <si>
+    <t>(AGE?[20])&amp;(CHR&gt;8)</t>
+  </si>
+  <si>
+    <t>保胎丸</t>
+  </si>
+  <si>
+    <t>你不会胎死腹中</t>
+  </si>
+  <si>
+    <t>白化病</t>
+  </si>
+  <si>
+    <t>你不会遭遇枪击</t>
+  </si>
+  <si>
+    <t>佛宗</t>
+  </si>
+  <si>
+    <t>考上哈佛大学的几率提高</t>
+  </si>
+  <si>
+    <t>悟道</t>
+  </si>
+  <si>
+    <t>智力&gt;10时快乐+3</t>
+  </si>
+  <si>
+    <t>INT&gt;10</t>
+  </si>
+  <si>
+    <t>驻颜</t>
+  </si>
+  <si>
+    <t>体质&gt;10时颜值+3</t>
+  </si>
+  <si>
+    <t>STR&gt;10</t>
+  </si>
+  <si>
+    <t>界限突破</t>
+  </si>
+  <si>
+    <t>体质&gt;10时快乐+3</t>
+  </si>
+  <si>
+    <t>倾城</t>
+  </si>
+  <si>
+    <t>颜值&gt;10时快乐+3</t>
+  </si>
+  <si>
+    <t>CHR&gt;10</t>
+  </si>
+  <si>
+    <t>训练有方</t>
+  </si>
+  <si>
+    <t>智力&gt;10时体质+3</t>
+  </si>
+  <si>
+    <t>相由心生</t>
+  </si>
+  <si>
+    <t>智力&gt;10时颜值+3</t>
+  </si>
+  <si>
+    <t>智多鑫</t>
+  </si>
+  <si>
+    <t>智力&gt;10时家境+3</t>
+  </si>
+  <si>
+    <t>灵光</t>
+  </si>
+  <si>
+    <t>快乐&gt;10时其他属性+1</t>
+  </si>
+  <si>
+    <t>SPR&gt;10</t>
+  </si>
+  <si>
+    <t>天启</t>
+  </si>
+  <si>
+    <t>快乐&gt;10时其他属性+2</t>
+  </si>
+  <si>
+    <t>神谕</t>
+  </si>
+  <si>
+    <t>快乐&gt;10时其他属性+3</t>
+  </si>
+  <si>
+    <t>献祭</t>
+  </si>
+  <si>
+    <t>初始可用属性点-2，快乐+2</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>幸运儿</t>
+  </si>
+  <si>
+    <t>初始可用属性点-3，快乐+5</t>
+  </si>
+  <si>
+    <t>挑战者</t>
+  </si>
+  <si>
+    <t>初始可用点-10</t>
+  </si>
+  <si>
+    <t>你不懂</t>
+  </si>
+  <si>
+    <t>家境&gt;10时快乐+3</t>
+  </si>
+  <si>
+    <t>MNY&gt;10</t>
+  </si>
+  <si>
+    <t>整容</t>
+  </si>
+  <si>
+    <t>家境&gt;10时颜值+3</t>
+  </si>
+  <si>
+    <t>钻石健身卡</t>
+  </si>
+  <si>
+    <t>家境&gt;10时体质+3</t>
+  </si>
+  <si>
+    <t>身残志坚</t>
+  </si>
+  <si>
+    <t>体质&lt;0时其他属性+1</t>
+  </si>
+  <si>
+    <t>STR&lt;0</t>
+  </si>
+  <si>
+    <t>活死人</t>
+  </si>
+  <si>
+    <t>体质&lt;0时其他属性+2</t>
+  </si>
+  <si>
+    <t>开一扇窗</t>
+  </si>
+  <si>
+    <t>颜值&lt;0时其他属性+1</t>
+  </si>
+  <si>
+    <t>CHR&lt;0</t>
+  </si>
+  <si>
+    <t>大额头</t>
+  </si>
+  <si>
+    <t>颜值-2，智力+2</t>
+  </si>
+  <si>
+    <t>痘痘脸</t>
+  </si>
+  <si>
+    <t>颜值-1</t>
+  </si>
+  <si>
+    <t>潜能</t>
+  </si>
+  <si>
+    <t>家境&lt;0时其他属性+1</t>
+  </si>
+  <si>
+    <t>MNY&lt;0</t>
+  </si>
+  <si>
+    <t>哀兵</t>
+  </si>
+  <si>
+    <t>快乐&lt;0时其他属性+1</t>
+  </si>
+  <si>
+    <t>SPR&lt;0</t>
+  </si>
+  <si>
+    <t>苦痛侍僧</t>
+  </si>
+  <si>
+    <t>快乐&lt;-1时其他属性+2</t>
+  </si>
+  <si>
+    <t>SPR&lt;-1</t>
+  </si>
+  <si>
+    <t>艰苦奋斗</t>
+  </si>
+  <si>
+    <t>家境&lt;-1时其他属性+2</t>
+  </si>
+  <si>
+    <t>MNY&lt;-1</t>
+  </si>
+  <si>
+    <t>抖M</t>
+  </si>
+  <si>
+    <t>家境-2，快乐+2</t>
+  </si>
+  <si>
+    <t>海的女儿</t>
+  </si>
+  <si>
+    <t>颜值-2，初始可用属性点+1</t>
+  </si>
+  <si>
+    <t>进阶</t>
+  </si>
+  <si>
+    <t>所有属性&gt;5时，所有属性+1</t>
+  </si>
+  <si>
+    <t>(SPR&gt;5)&amp;(MNY&gt;5)&amp;(CHR&gt;5)&amp;(STR&gt;5)&amp;(INT&gt;5)</t>
+  </si>
+  <si>
+    <t>超进化</t>
+  </si>
+  <si>
+    <t>所有属性&gt;5时，所有属性+2</t>
+  </si>
+  <si>
+    <t>白色胶囊</t>
+  </si>
+  <si>
+    <t>你10岁时无事发生</t>
+  </si>
+  <si>
+    <t>AGE?[10]</t>
+  </si>
+  <si>
+    <t>紫色胶囊</t>
+  </si>
+  <si>
+    <t>跳过你的40~50岁</t>
+  </si>
+  <si>
+    <t>蓝色胶囊</t>
+  </si>
+  <si>
+    <t>你20岁和30岁时无事发生</t>
+  </si>
+  <si>
+    <t>AGE?[20,30]</t>
+  </si>
+  <si>
+    <t>健康饮食</t>
+  </si>
+  <si>
+    <t>你不吃洋快餐</t>
+  </si>
+  <si>
+    <t>不想罢了</t>
+  </si>
+  <si>
+    <t>你不会上清华大学</t>
+  </si>
+  <si>
+    <t>挑衅</t>
+  </si>
+  <si>
+    <t>你喜欢没事找事</t>
+  </si>
+  <si>
+    <t>旅行者</t>
+  </si>
+  <si>
+    <t>你喜欢旅游</t>
+  </si>
+  <si>
+    <t>水仙</t>
+  </si>
+  <si>
+    <t>你比较自恋</t>
+  </si>
+  <si>
+    <t>缺一门</t>
+  </si>
+  <si>
+    <t>无效果</t>
+  </si>
+  <si>
+    <t>异界来客</t>
+  </si>
+  <si>
+    <t>你可能听到一些绝密消息</t>
+  </si>
+  <si>
+    <t>三胎人生</t>
+  </si>
+  <si>
+    <t>你尽可能生三胎</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>橙色胶囊</t>
+  </si>
+  <si>
+    <t>跳过你的60~90岁</t>
+  </si>
+  <si>
+    <t>宙斯</t>
+  </si>
+  <si>
+    <t>参加奥赛的几率提高</t>
+  </si>
+  <si>
+    <t>为人民服务</t>
+  </si>
+  <si>
+    <t>考公务员时一定能考上</t>
+  </si>
+  <si>
+    <t>表现良好</t>
+  </si>
+  <si>
+    <t>入狱会减刑</t>
+  </si>
+  <si>
+    <t>小吉</t>
+  </si>
+  <si>
+    <t>运气稍微提升</t>
+  </si>
+  <si>
+    <t>天秤座</t>
+  </si>
+  <si>
+    <t>据说做事很公平</t>
+  </si>
+  <si>
+    <t>万里挑一</t>
+  </si>
+  <si>
+    <t>你很攻</t>
+  </si>
+  <si>
+    <t>把握不住</t>
+  </si>
+  <si>
+    <t>你有强迫症</t>
+  </si>
+  <si>
+    <t>急了急了</t>
+  </si>
+  <si>
+    <t>赶着投胎，不要初始属性了</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>不离不弃</t>
+  </si>
+  <si>
+    <t>你不会离婚</t>
+  </si>
+  <si>
+    <t>足量</t>
+  </si>
+  <si>
+    <t>身高不矮</t>
+  </si>
+  <si>
+    <t>易胖体质</t>
+  </si>
+  <si>
+    <t>颜值更容易降低</t>
+  </si>
+  <si>
+    <t>偏见</t>
+  </si>
+  <si>
+    <t>种族主义者</t>
+  </si>
+  <si>
+    <t>左撇子</t>
+  </si>
+  <si>
+    <t>习惯使用左手</t>
+  </si>
+  <si>
+    <t>克苏鲁</t>
+  </si>
+  <si>
+    <t>&amp;▓▓▓◆▓▓▓￥#▓@■.◆</t>
+  </si>
+  <si>
+    <t>不连续存在</t>
+  </si>
+  <si>
+    <t>你还拥有其他人格</t>
+  </si>
+  <si>
+    <t>占位符</t>
+  </si>
+  <si>
+    <t>少一个可选天赋</t>
+  </si>
+  <si>
+    <t>魔法棒</t>
+  </si>
+  <si>
+    <t>不知道有什么用……</t>
+  </si>
+  <si>
+    <t>返老还童</t>
+  </si>
+  <si>
+    <t>可能会回到年轻的时候</t>
+  </si>
+  <si>
+    <t>时光倒流</t>
+  </si>
+  <si>
+    <t>或许时间会倒流</t>
+  </si>
+  <si>
+    <t>转世重修</t>
+  </si>
+  <si>
+    <t>渡劫失败重生</t>
+  </si>
+  <si>
+    <t>轮回之外</t>
+  </si>
+  <si>
+    <t>死后可能灵魂离体</t>
+  </si>
+  <si>
+    <t>贪婪</t>
+  </si>
+  <si>
+    <t>家境+10</t>
+  </si>
+  <si>
+    <t>百岁百世丸</t>
+  </si>
+  <si>
+    <t>某条件下所有属性+2</t>
+  </si>
+  <si>
+    <t>(AGE?[100])&amp;(TMS&gt;99)</t>
+  </si>
+  <si>
+    <t>意外之喜</t>
+  </si>
+  <si>
+    <t>随机属性+1</t>
+  </si>
+  <si>
+    <t>培养爱好</t>
+  </si>
+  <si>
+    <t>随机属性+2</t>
+  </si>
+  <si>
+    <t>觉醒</t>
+  </si>
+  <si>
+    <t>随机属性+4</t>
+  </si>
+  <si>
+    <t>阴间大会员</t>
+  </si>
+  <si>
+    <t>随机属性+8</t>
+  </si>
+  <si>
+    <t>蓝色转盘</t>
+  </si>
+  <si>
+    <t>变成随机蓝色天赋</t>
+  </si>
+  <si>
+    <t>紫色转盘</t>
+  </si>
+  <si>
+    <t>变成随机紫色天赋</t>
+  </si>
+  <si>
+    <t>橙色转盘</t>
+  </si>
+  <si>
+    <t>变成随机橙色天赋</t>
+  </si>
+  <si>
+    <t>阴间福袋</t>
+  </si>
+  <si>
+    <t>可能开出好天赋</t>
+  </si>
+  <si>
+    <t>轮盘赌</t>
+  </si>
+  <si>
+    <t>1/6几率变橙色天赋</t>
+  </si>
+  <si>
+    <t>1141*0.2</t>
+  </si>
+  <si>
+    <t>1135*0.2</t>
+  </si>
+  <si>
+    <t>1114*0.2</t>
+  </si>
+  <si>
+    <t>1023*0.2</t>
+  </si>
+  <si>
+    <t>1048*0.2</t>
+  </si>
+  <si>
+    <t>1033*5</t>
+  </si>
+  <si>
+    <t>1147*0.2</t>
+  </si>
+  <si>
+    <t>死者苏生</t>
+  </si>
+  <si>
+    <t>加一条命</t>
+  </si>
+  <si>
+    <t>恶魔的交易</t>
+  </si>
+  <si>
+    <t>所有属性-2，加一条命</t>
+  </si>
+  <si>
+    <t>霸王</t>
+  </si>
+  <si>
+    <t>体质+4</t>
+  </si>
+  <si>
+    <t>国色</t>
+  </si>
+  <si>
+    <t>颜值+4</t>
+  </si>
+  <si>
+    <t>兼爱</t>
+  </si>
+  <si>
+    <t>你很受</t>
+  </si>
+  <si>
+    <t>树人</t>
+  </si>
+  <si>
+    <t>你还有别的名字</t>
+  </si>
+  <si>
+    <t>圆周率</t>
+  </si>
+  <si>
+    <t>？</t>
+  </si>
+  <si>
+    <t>？？？</t>
+  </si>
+  <si>
+    <t>白色转盘</t>
+  </si>
+  <si>
+    <t>变成随机白色天赋</t>
+  </si>
+  <si>
+    <t>连续可导</t>
+  </si>
+  <si>
+    <t>你没有其他人格</t>
+  </si>
+  <si>
+    <t>绝妙的天赋</t>
+  </si>
+  <si>
+    <t>可惜这里写不下</t>
+  </si>
+  <si>
+    <t>叠加态</t>
+  </si>
+  <si>
+    <t>变成橙色天赋或死</t>
+  </si>
+  <si>
+    <t>1033*6</t>
+  </si>
+  <si>
+    <t>木大</t>
+  </si>
+  <si>
+    <t>遗言很有名</t>
+  </si>
+  <si>
+    <t>高产</t>
+  </si>
+  <si>
+    <t>60岁时体质-2</t>
+  </si>
+  <si>
+    <t>杠杆</t>
+  </si>
+  <si>
+    <t>理财天赋较高</t>
+  </si>
+  <si>
+    <t>AGE?[20]</t>
+  </si>
+  <si>
+    <t>物理</t>
+  </si>
+  <si>
+    <t>30岁时颜值-2</t>
+  </si>
+  <si>
+    <t>阳间福袋</t>
+  </si>
+  <si>
+    <t>更可能开出好天赋</t>
+  </si>
+  <si>
+    <t>1142</t>
+  </si>
+  <si>
+    <t>1139</t>
+  </si>
+  <si>
+    <t>1140</t>
+  </si>
+  <si>
+    <t>1141</t>
+  </si>
+  <si>
+    <t>1128</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>1135</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>1065</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>洞穴寓言</t>
+  </si>
+  <si>
+    <t>可能发现世界的真相</t>
+  </si>
+  <si>
+    <t>天赋综合判断</t>
+  </si>
+  <si>
+    <t>天赋不能多于5个</t>
+  </si>
+  <si>
+    <t>诺贝尔奖</t>
+  </si>
+  <si>
+    <t>得过诺贝尔奖可复活一次</t>
+  </si>
+  <si>
+    <t>二号橙色转盘</t>
+  </si>
+  <si>
+    <t>流芳</t>
+  </si>
+  <si>
+    <t>有悲剧时，所有属性+1</t>
+  </si>
+  <si>
+    <t>TLT?[2028,2029,2030,2031]</t>
+  </si>
+  <si>
+    <t>百世</t>
+  </si>
+  <si>
+    <t>随机抽一部剧</t>
+  </si>
+  <si>
+    <t>哈姆雷特</t>
+  </si>
+  <si>
+    <t>快乐-2</t>
+  </si>
+  <si>
+    <t>李尔王</t>
+  </si>
+  <si>
+    <t>麦克白</t>
+  </si>
+  <si>
+    <t>奥赛罗</t>
+  </si>
+  <si>
+    <t>仲夏夜之梦</t>
+  </si>
+  <si>
+    <t>快乐+114509</t>
+  </si>
+  <si>
+    <t>威尼斯商人</t>
+  </si>
+  <si>
+    <t>第十二夜</t>
+  </si>
+  <si>
+    <t>皆大欢喜</t>
+  </si>
+  <si>
+    <t>永不言弃</t>
+  </si>
+  <si>
+    <t>你永远不会放弃</t>
+  </si>
+  <si>
     <t>$id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>condition</t>
-  </si>
-  <si>
-    <t>grade</t>
-  </si>
-  <si>
-    <t>exclusive</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>effect:SPR</t>
-  </si>
-  <si>
-    <t>effect:MNY</t>
-  </si>
-  <si>
-    <t>effect:CHR</t>
-  </si>
-  <si>
-    <t>effect:STR</t>
-  </si>
-  <si>
-    <t>effect:INT</t>
-  </si>
-  <si>
-    <t>effect:RDM</t>
-  </si>
-  <si>
-    <t>replacement:grade[]</t>
-  </si>
-  <si>
-    <t>replacement:talent[]</t>
-  </si>
-  <si>
-    <t>exclude[]</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>天赋名</t>
-  </si>
-  <si>
-    <t>括号中的内容</t>
-  </si>
-  <si>
-    <t>触发条件</t>
-  </si>
-  <si>
-    <t>稀有度</t>
-  </si>
-  <si>
-    <t>专属天赋</t>
-  </si>
-  <si>
-    <t>初始可用属性点</t>
-  </si>
-  <si>
-    <t>额外快乐</t>
-  </si>
-  <si>
-    <t>额外家境</t>
-  </si>
-  <si>
-    <t>额外颜值</t>
-  </si>
-  <si>
-    <t>额外体质</t>
-  </si>
-  <si>
-    <t>额外智力</t>
-  </si>
-  <si>
-    <t>随机属性</t>
-  </si>
-  <si>
-    <t>替换成某稀有度的天赋</t>
-  </si>
-  <si>
-    <t>替换成某天赋</t>
-  </si>
-  <si>
-    <t>互斥天赋</t>
-  </si>
-  <si>
-    <t>随身玉佩</t>
-  </si>
-  <si>
-    <t>或许有护佑作用</t>
-  </si>
-  <si>
-    <t>红肚兜</t>
-  </si>
-  <si>
-    <t>小时候死亡率降低</t>
-  </si>
-  <si>
-    <t>生而为男</t>
-  </si>
-  <si>
-    <t>性别一定为男</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>生而为女</t>
-  </si>
-  <si>
-    <t>性别一定为女</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>动漫高手</t>
-  </si>
-  <si>
-    <t>入宅的可能性翻6倍</t>
-  </si>
-  <si>
-    <t>乐观</t>
-  </si>
-  <si>
-    <t>快乐+1</t>
-  </si>
-  <si>
-    <t>天赋异禀</t>
-  </si>
-  <si>
-    <t>初始可用属性点+2</t>
-  </si>
-  <si>
-    <t>天生抑郁</t>
-  </si>
-  <si>
-    <t>快乐-3</t>
-  </si>
-  <si>
-    <t>网络巨魔</t>
-  </si>
-  <si>
-    <t>快乐+2</t>
-  </si>
-  <si>
-    <t>天龙人</t>
-  </si>
-  <si>
-    <t>你拥有北京户口</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>独生子女</t>
-  </si>
-  <si>
-    <t>你没有兄弟姐妹</t>
-  </si>
-  <si>
-    <t>乡间微风</t>
-  </si>
-  <si>
-    <t>你出生在农村</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>城中高楼</t>
-  </si>
-  <si>
-    <t>你出生在城市</t>
-  </si>
-  <si>
-    <t>美籍华人</t>
-  </si>
-  <si>
-    <t>你有美国国籍</t>
-  </si>
-  <si>
-    <t>家中老大</t>
-  </si>
-  <si>
-    <t>你最受父母宠爱</t>
-  </si>
-  <si>
-    <t>水性良好</t>
-  </si>
-  <si>
-    <t>不会被淹死</t>
-  </si>
-  <si>
-    <t>先天免疫</t>
-  </si>
-  <si>
-    <t>你不会得艾滋病</t>
-  </si>
-  <si>
-    <t>人类进化</t>
-  </si>
-  <si>
-    <t>所有属性+1</t>
-  </si>
-  <si>
-    <t>超凡</t>
-  </si>
-  <si>
-    <t>初始可用属性点+4</t>
-  </si>
-  <si>
-    <t>父母美貌</t>
-  </si>
-  <si>
-    <t>颜值+2</t>
-  </si>
-  <si>
-    <t>红颜薄命</t>
-  </si>
-  <si>
-    <t>颜值+2，体质-2</t>
-  </si>
-  <si>
-    <t>属蛇</t>
-  </si>
-  <si>
-    <t>不会被蛇咬死</t>
-  </si>
-  <si>
-    <t>半神</t>
-  </si>
-  <si>
-    <t>所有属性+2</t>
-  </si>
-  <si>
-    <t>人中龙凤</t>
-  </si>
-  <si>
-    <t>天生双重性别</t>
-  </si>
-  <si>
-    <t>阴阳之外</t>
-  </si>
-  <si>
-    <t>天生无性别</t>
-  </si>
-  <si>
-    <t>彩虹之下</t>
-  </si>
-  <si>
-    <t>可能和同性交往</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>斩情证道</t>
-  </si>
-  <si>
-    <t>终生不恋爱结婚</t>
-  </si>
-  <si>
-    <t>桃花连连</t>
-  </si>
-  <si>
-    <t>恋爱机会提升</t>
-  </si>
-  <si>
-    <t>平安童年</t>
-  </si>
-  <si>
-    <t>12岁前父母都健在</t>
-  </si>
-  <si>
-    <t>宠物大师</t>
-  </si>
-  <si>
-    <t>宠物不会意外死亡</t>
-  </si>
-  <si>
-    <t>天生残疾</t>
-  </si>
-  <si>
-    <t>体质-2</t>
-  </si>
-  <si>
-    <t>早产儿</t>
-  </si>
-  <si>
-    <t>所有属性-1</t>
-  </si>
-  <si>
-    <t>十死无生</t>
-  </si>
-  <si>
-    <t>体质-10</t>
-  </si>
-  <si>
-    <t>家运不顺</t>
-  </si>
-  <si>
-    <t>家境-2</t>
-  </si>
-  <si>
-    <t>头着地</t>
-  </si>
-  <si>
-    <t>智力-2</t>
-  </si>
-  <si>
-    <t>胎教</t>
-  </si>
-  <si>
-    <t>智力+1</t>
-  </si>
-  <si>
-    <t>班中红人</t>
-  </si>
-  <si>
-    <t>和同学容易处好关系</t>
-  </si>
-  <si>
-    <t>骑士</t>
-  </si>
-  <si>
-    <t>能轻松学会骑车</t>
-  </si>
-  <si>
-    <t>永远的神</t>
-  </si>
-  <si>
-    <t>电竞天才</t>
-  </si>
-  <si>
-    <t>戒律</t>
-  </si>
-  <si>
-    <t>赌毒不沾</t>
-  </si>
-  <si>
-    <t>丁克</t>
-  </si>
-  <si>
-    <t>不生孩子</t>
-  </si>
-  <si>
-    <t>少数民族</t>
-  </si>
-  <si>
-    <t>高考+5分</t>
-  </si>
-  <si>
-    <t>老司机</t>
-  </si>
-  <si>
-    <t>你和家人不会发生车祸</t>
-  </si>
-  <si>
-    <t>低压</t>
-  </si>
-  <si>
-    <t>你的家人不会心脏病</t>
-  </si>
-  <si>
-    <t>战功</t>
-  </si>
-  <si>
-    <t>你退伍后会当官</t>
-  </si>
-  <si>
-    <t>不孕不育</t>
-  </si>
-  <si>
-    <t>你生不出孩子</t>
-  </si>
-  <si>
-    <t>白头偕老</t>
-  </si>
-  <si>
-    <t>爱人至少能活到70岁</t>
-  </si>
-  <si>
-    <t>神秘的小盒子</t>
-  </si>
-  <si>
-    <t>100岁时才能开启</t>
-  </si>
-  <si>
-    <t>三十而立</t>
-  </si>
-  <si>
-    <t>30岁时家境+2</t>
-  </si>
-  <si>
-    <t>AGE?[30]</t>
-  </si>
-  <si>
-    <t>四十不惑</t>
-  </si>
-  <si>
-    <t>40岁时智力+2</t>
-  </si>
-  <si>
-    <t>AGE?[40]</t>
-  </si>
-  <si>
-    <t>知天命</t>
-  </si>
-  <si>
-    <t>50岁时智力、快乐+1</t>
-  </si>
-  <si>
-    <t>AGE?[50]</t>
-  </si>
-  <si>
-    <t>耳顺</t>
-  </si>
-  <si>
-    <t>60岁时快乐+2</t>
-  </si>
-  <si>
-    <t>AGE?[60]</t>
-  </si>
-  <si>
-    <t>从心所欲</t>
-  </si>
-  <si>
-    <t>70岁时快乐+3</t>
-  </si>
-  <si>
-    <t>AGE?[70]</t>
-  </si>
-  <si>
-    <t>老当益壮</t>
-  </si>
-  <si>
-    <t>60岁时体质+2</t>
-  </si>
-  <si>
-    <t>鹤发童颜</t>
-  </si>
-  <si>
-    <t>70岁时颜值+3</t>
-  </si>
-  <si>
-    <t>学前启蒙</t>
-  </si>
-  <si>
-    <t>5岁时智力+2</t>
-  </si>
-  <si>
-    <t>AGE?[5]</t>
-  </si>
-  <si>
-    <t>十八变</t>
-  </si>
-  <si>
-    <t>18岁时颜值+2</t>
-  </si>
-  <si>
-    <t>AGE?[18]</t>
-  </si>
-  <si>
-    <t>迟来之财</t>
-  </si>
-  <si>
-    <t>90岁时家境+4</t>
-  </si>
-  <si>
-    <t>AGE?[90]</t>
-  </si>
-  <si>
-    <t>理财达人</t>
-  </si>
-  <si>
-    <t>40岁时家境+3</t>
-  </si>
-  <si>
-    <t>成熟</t>
-  </si>
-  <si>
-    <t>18岁时智力+2</t>
-  </si>
-  <si>
-    <t>形象管理</t>
-  </si>
-  <si>
-    <t>24岁时颜值+2</t>
-  </si>
-  <si>
-    <t>AGE?[24]</t>
-  </si>
-  <si>
-    <t>成年礼</t>
-  </si>
-  <si>
-    <t>18岁时快乐+1</t>
-  </si>
-  <si>
-    <t>开光之胎</t>
-  </si>
-  <si>
-    <t>初始可用属性点+1</t>
-  </si>
-  <si>
-    <t>天命</t>
-  </si>
-  <si>
-    <t>初始可用属性点+8</t>
-  </si>
-  <si>
-    <t>祖传药丸</t>
-  </si>
-  <si>
-    <t>功能不明</t>
-  </si>
-  <si>
-    <t>精准扶贫</t>
-  </si>
-  <si>
-    <t>家境为0时家境+1</t>
-  </si>
-  <si>
-    <t>(MNY&lt;1)&amp;(MNY&gt;-1)</t>
-  </si>
-  <si>
-    <t>乐天派</t>
-  </si>
-  <si>
-    <t>快乐为0时快乐+1</t>
-  </si>
-  <si>
-    <t>(SPR&lt;1)&amp;(SPR&gt;-1)</t>
-  </si>
-  <si>
-    <t>命悬一线</t>
-  </si>
-  <si>
-    <t>体质为0时体质+1</t>
-  </si>
-  <si>
-    <t>(STR&lt;1)&amp;(STR&gt;-1)</t>
-  </si>
-  <si>
-    <t>智可生财</t>
-  </si>
-  <si>
-    <t>若20岁时智力&gt;8，家境+2</t>
-  </si>
-  <si>
-    <t>(AGE?[20])&amp;(INT&gt;8)</t>
-  </si>
-  <si>
-    <t>舔狗甚多</t>
-  </si>
-  <si>
-    <t>若20岁时颜值&gt;8，快乐+2</t>
-  </si>
-  <si>
-    <t>(AGE?[20])&amp;(CHR&gt;8)</t>
-  </si>
-  <si>
-    <t>保胎丸</t>
-  </si>
-  <si>
-    <t>你不会胎死腹中</t>
-  </si>
-  <si>
-    <t>白化病</t>
-  </si>
-  <si>
-    <t>你不会遭遇枪击</t>
-  </si>
-  <si>
-    <t>佛宗</t>
-  </si>
-  <si>
-    <t>考上哈佛大学的几率提高</t>
-  </si>
-  <si>
-    <t>悟道</t>
-  </si>
-  <si>
-    <t>智力&gt;10时快乐+3</t>
-  </si>
-  <si>
-    <t>INT&gt;10</t>
-  </si>
-  <si>
-    <t>驻颜</t>
-  </si>
-  <si>
-    <t>体质&gt;10时颜值+3</t>
-  </si>
-  <si>
-    <t>STR&gt;10</t>
-  </si>
-  <si>
-    <t>界限突破</t>
-  </si>
-  <si>
-    <t>体质&gt;10时快乐+3</t>
-  </si>
-  <si>
-    <t>倾城</t>
-  </si>
-  <si>
-    <t>颜值&gt;10时快乐+3</t>
-  </si>
-  <si>
-    <t>CHR&gt;10</t>
-  </si>
-  <si>
-    <t>训练有方</t>
-  </si>
-  <si>
-    <t>智力&gt;10时体质+3</t>
-  </si>
-  <si>
-    <t>相由心生</t>
-  </si>
-  <si>
-    <t>智力&gt;10时颜值+3</t>
-  </si>
-  <si>
-    <t>智多鑫</t>
-  </si>
-  <si>
-    <t>智力&gt;10时家境+3</t>
-  </si>
-  <si>
-    <t>灵光</t>
-  </si>
-  <si>
-    <t>快乐&gt;10时其他属性+1</t>
-  </si>
-  <si>
-    <t>SPR&gt;10</t>
-  </si>
-  <si>
-    <t>天启</t>
-  </si>
-  <si>
-    <t>快乐&gt;10时其他属性+2</t>
-  </si>
-  <si>
-    <t>神谕</t>
-  </si>
-  <si>
-    <t>快乐&gt;10时其他属性+3</t>
-  </si>
-  <si>
-    <t>献祭</t>
-  </si>
-  <si>
-    <t>初始可用属性点-2，快乐+2</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>幸运儿</t>
-  </si>
-  <si>
-    <t>初始可用属性点-3，快乐+5</t>
-  </si>
-  <si>
-    <t>挑战者</t>
-  </si>
-  <si>
-    <t>初始可用点-10</t>
-  </si>
-  <si>
-    <t>你不懂</t>
-  </si>
-  <si>
-    <t>家境&gt;10时快乐+3</t>
-  </si>
-  <si>
-    <t>MNY&gt;10</t>
-  </si>
-  <si>
-    <t>整容</t>
-  </si>
-  <si>
-    <t>家境&gt;10时颜值+3</t>
-  </si>
-  <si>
-    <t>钻石健身卡</t>
-  </si>
-  <si>
-    <t>家境&gt;10时体质+3</t>
-  </si>
-  <si>
-    <t>身残志坚</t>
-  </si>
-  <si>
-    <t>体质&lt;0时其他属性+1</t>
-  </si>
-  <si>
-    <t>STR&lt;0</t>
-  </si>
-  <si>
-    <t>活死人</t>
-  </si>
-  <si>
-    <t>体质&lt;0时其他属性+2</t>
-  </si>
-  <si>
-    <t>开一扇窗</t>
-  </si>
-  <si>
-    <t>颜值&lt;0时其他属性+1</t>
-  </si>
-  <si>
-    <t>CHR&lt;0</t>
-  </si>
-  <si>
-    <t>大额头</t>
-  </si>
-  <si>
-    <t>颜值-2，智力+2</t>
-  </si>
-  <si>
-    <t>痘痘脸</t>
-  </si>
-  <si>
-    <t>颜值-1</t>
-  </si>
-  <si>
-    <t>潜能</t>
-  </si>
-  <si>
-    <t>家境&lt;0时其他属性+1</t>
-  </si>
-  <si>
-    <t>MNY&lt;0</t>
-  </si>
-  <si>
-    <t>哀兵</t>
-  </si>
-  <si>
-    <t>快乐&lt;0时其他属性+1</t>
-  </si>
-  <si>
-    <t>SPR&lt;0</t>
-  </si>
-  <si>
-    <t>苦痛侍僧</t>
-  </si>
-  <si>
-    <t>快乐&lt;-1时其他属性+2</t>
-  </si>
-  <si>
-    <t>SPR&lt;-1</t>
-  </si>
-  <si>
-    <t>艰苦奋斗</t>
-  </si>
-  <si>
-    <t>家境&lt;-1时其他属性+2</t>
-  </si>
-  <si>
-    <t>MNY&lt;-1</t>
-  </si>
-  <si>
-    <t>抖M</t>
-  </si>
-  <si>
-    <t>家境-2，快乐+2</t>
-  </si>
-  <si>
-    <t>海的女儿</t>
-  </si>
-  <si>
-    <t>颜值-2，初始可用属性点+1</t>
-  </si>
-  <si>
-    <t>进阶</t>
-  </si>
-  <si>
-    <t>所有属性&gt;5时，所有属性+1</t>
-  </si>
-  <si>
-    <t>(SPR&gt;5)&amp;(MNY&gt;5)&amp;(CHR&gt;5)&amp;(STR&gt;5)&amp;(INT&gt;5)</t>
-  </si>
-  <si>
-    <t>超进化</t>
-  </si>
-  <si>
-    <t>所有属性&gt;5时，所有属性+2</t>
-  </si>
-  <si>
-    <t>白色胶囊</t>
-  </si>
-  <si>
-    <t>你10岁时无事发生</t>
-  </si>
-  <si>
-    <t>AGE?[10]</t>
-  </si>
-  <si>
-    <t>紫色胶囊</t>
-  </si>
-  <si>
-    <t>跳过你的40~50岁</t>
-  </si>
-  <si>
-    <t>蓝色胶囊</t>
-  </si>
-  <si>
-    <t>你20岁和30岁时无事发生</t>
-  </si>
-  <si>
-    <t>AGE?[20,30]</t>
-  </si>
-  <si>
-    <t>健康饮食</t>
-  </si>
-  <si>
-    <t>你不吃洋快餐</t>
-  </si>
-  <si>
-    <t>不想罢了</t>
-  </si>
-  <si>
-    <t>你不会上清华大学</t>
-  </si>
-  <si>
-    <t>挑衅</t>
-  </si>
-  <si>
-    <t>你喜欢没事找事</t>
-  </si>
-  <si>
-    <t>旅行者</t>
-  </si>
-  <si>
-    <t>你喜欢旅游</t>
-  </si>
-  <si>
-    <t>水仙</t>
-  </si>
-  <si>
-    <t>你比较自恋</t>
-  </si>
-  <si>
-    <t>缺一门</t>
-  </si>
-  <si>
-    <t>无效果</t>
-  </si>
-  <si>
-    <t>异界来客</t>
-  </si>
-  <si>
-    <t>你可能听到一些绝密消息</t>
-  </si>
-  <si>
-    <t>三胎人生</t>
-  </si>
-  <si>
-    <t>你尽可能生三胎</t>
-  </si>
-  <si>
-    <t>1026</t>
-  </si>
-  <si>
-    <t>橙色胶囊</t>
-  </si>
-  <si>
-    <t>跳过你的60~90岁</t>
-  </si>
-  <si>
-    <t>宙斯</t>
-  </si>
-  <si>
-    <t>参加奥赛的几率提高</t>
-  </si>
-  <si>
-    <t>为人民服务</t>
-  </si>
-  <si>
-    <t>考公务员时一定能考上</t>
-  </si>
-  <si>
-    <t>表现良好</t>
-  </si>
-  <si>
-    <t>入狱会减刑</t>
-  </si>
-  <si>
-    <t>小吉</t>
-  </si>
-  <si>
-    <t>运气稍微提升</t>
-  </si>
-  <si>
-    <t>天秤座</t>
-  </si>
-  <si>
-    <t>据说做事很公平</t>
-  </si>
-  <si>
-    <t>万里挑一</t>
-  </si>
-  <si>
-    <t>你很攻</t>
-  </si>
-  <si>
-    <t>把握不住</t>
-  </si>
-  <si>
-    <t>你有强迫症</t>
-  </si>
-  <si>
-    <t>急了急了</t>
-  </si>
-  <si>
-    <t>赶着投胎，不要初始属性了</t>
-  </si>
-  <si>
-    <t>1084</t>
-  </si>
-  <si>
-    <t>1085</t>
-  </si>
-  <si>
-    <t>1086</t>
-  </si>
-  <si>
-    <t>不离不弃</t>
-  </si>
-  <si>
-    <t>你不会离婚</t>
-  </si>
-  <si>
-    <t>足量</t>
-  </si>
-  <si>
-    <t>身高不矮</t>
-  </si>
-  <si>
-    <t>易胖体质</t>
-  </si>
-  <si>
-    <t>颜值更容易降低</t>
-  </si>
-  <si>
-    <t>偏见</t>
-  </si>
-  <si>
-    <t>种族主义者</t>
-  </si>
-  <si>
-    <t>左撇子</t>
-  </si>
-  <si>
-    <t>习惯使用左手</t>
-  </si>
-  <si>
-    <t>克苏鲁</t>
-  </si>
-  <si>
-    <t>&amp;▓▓▓◆▓▓▓￥#▓@■.◆</t>
-  </si>
-  <si>
-    <t>不连续存在</t>
-  </si>
-  <si>
-    <t>你还拥有其他人格</t>
-  </si>
-  <si>
-    <t>占位符</t>
-  </si>
-  <si>
-    <t>少一个可选天赋</t>
-  </si>
-  <si>
-    <t>魔法棒</t>
-  </si>
-  <si>
-    <t>不知道有什么用……</t>
-  </si>
-  <si>
-    <t>返老还童</t>
-  </si>
-  <si>
-    <t>可能会回到年轻的时候</t>
-  </si>
-  <si>
-    <t>时光倒流</t>
-  </si>
-  <si>
-    <t>或许时间会倒流</t>
-  </si>
-  <si>
-    <t>转世重修</t>
-  </si>
-  <si>
-    <t>渡劫失败重生</t>
-  </si>
-  <si>
-    <t>轮回之外</t>
-  </si>
-  <si>
-    <t>死后可能灵魂离体</t>
-  </si>
-  <si>
-    <t>贪婪</t>
-  </si>
-  <si>
-    <t>家境+10</t>
-  </si>
-  <si>
-    <t>百岁百世丸</t>
-  </si>
-  <si>
-    <t>某条件下所有属性+2</t>
-  </si>
-  <si>
-    <t>(AGE?[100])&amp;(TMS&gt;99)</t>
-  </si>
-  <si>
-    <t>意外之喜</t>
-  </si>
-  <si>
-    <t>随机属性+1</t>
-  </si>
-  <si>
-    <t>培养爱好</t>
-  </si>
-  <si>
-    <t>随机属性+2</t>
-  </si>
-  <si>
-    <t>觉醒</t>
-  </si>
-  <si>
-    <t>随机属性+4</t>
-  </si>
-  <si>
-    <t>阴间大会员</t>
-  </si>
-  <si>
-    <t>随机属性+8</t>
-  </si>
-  <si>
-    <t>蓝色转盘</t>
-  </si>
-  <si>
-    <t>变成随机蓝色天赋</t>
-  </si>
-  <si>
-    <t>紫色转盘</t>
-  </si>
-  <si>
-    <t>变成随机紫色天赋</t>
-  </si>
-  <si>
-    <t>橙色转盘</t>
-  </si>
-  <si>
-    <t>变成随机橙色天赋</t>
-  </si>
-  <si>
-    <t>阴间福袋</t>
-  </si>
-  <si>
-    <t>可能开出好天赋</t>
-  </si>
-  <si>
-    <t>轮盘赌</t>
-  </si>
-  <si>
-    <t>1/6几率变橙色天赋</t>
-  </si>
-  <si>
-    <t>1141*0.2</t>
-  </si>
-  <si>
-    <t>1135*0.2</t>
-  </si>
-  <si>
-    <t>1114*0.2</t>
-  </si>
-  <si>
-    <t>1023*0.2</t>
-  </si>
-  <si>
-    <t>1048*0.2</t>
-  </si>
-  <si>
-    <t>1033*5</t>
-  </si>
-  <si>
-    <t>1147*0.2</t>
-  </si>
-  <si>
-    <t>死者苏生</t>
-  </si>
-  <si>
-    <t>加一条命</t>
-  </si>
-  <si>
-    <t>恶魔的交易</t>
-  </si>
-  <si>
-    <t>所有属性-2，加一条命</t>
-  </si>
-  <si>
-    <t>霸王</t>
-  </si>
-  <si>
-    <t>体质+4</t>
-  </si>
-  <si>
-    <t>国色</t>
-  </si>
-  <si>
-    <t>颜值+4</t>
-  </si>
-  <si>
-    <t>兼爱</t>
-  </si>
-  <si>
-    <t>你很受</t>
-  </si>
-  <si>
-    <t>树人</t>
-  </si>
-  <si>
-    <t>你还有别的名字</t>
-  </si>
-  <si>
-    <t>圆周率</t>
-  </si>
-  <si>
-    <t>？</t>
-  </si>
-  <si>
-    <t>？？？</t>
-  </si>
-  <si>
-    <t>白色转盘</t>
-  </si>
-  <si>
-    <t>变成随机白色天赋</t>
-  </si>
-  <si>
-    <t>连续可导</t>
-  </si>
-  <si>
-    <t>你没有其他人格</t>
-  </si>
-  <si>
-    <t>绝妙的天赋</t>
-  </si>
-  <si>
-    <t>可惜这里写不下</t>
-  </si>
-  <si>
-    <t>叠加态</t>
-  </si>
-  <si>
-    <t>变成橙色天赋或死</t>
-  </si>
-  <si>
-    <t>1033*6</t>
-  </si>
-  <si>
-    <t>木大</t>
-  </si>
-  <si>
-    <t>遗言很有名</t>
-  </si>
-  <si>
-    <t>高产</t>
-  </si>
-  <si>
-    <t>60岁时体质-2</t>
-  </si>
-  <si>
-    <t>杠杆</t>
-  </si>
-  <si>
-    <t>理财天赋较高</t>
-  </si>
-  <si>
-    <t>AGE?[20]</t>
-  </si>
-  <si>
-    <t>物理</t>
-  </si>
-  <si>
-    <t>30岁时颜值-2</t>
-  </si>
-  <si>
-    <t>阳间福袋</t>
-  </si>
-  <si>
-    <t>更可能开出好天赋</t>
-  </si>
-  <si>
-    <t>1142</t>
-  </si>
-  <si>
-    <t>1139</t>
-  </si>
-  <si>
-    <t>1140</t>
-  </si>
-  <si>
-    <t>1141</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>1048</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>1135</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>1080</t>
-  </si>
-  <si>
-    <t>1065</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>洞穴寓言</t>
-  </si>
-  <si>
-    <t>可能发现世界的真相</t>
-  </si>
-  <si>
-    <t>天赋综合判断</t>
-  </si>
-  <si>
-    <t>天赋不能多于5个</t>
-  </si>
-  <si>
-    <t>诺贝尔奖</t>
-  </si>
-  <si>
-    <t>得过诺贝尔奖可复活一次</t>
-  </si>
-  <si>
-    <t>二号橙色转盘</t>
-  </si>
-  <si>
-    <t>流芳</t>
-  </si>
-  <si>
-    <t>有悲剧时，所有属性+1</t>
-  </si>
-  <si>
-    <t>TLT?[2028,2029,2030,2031]</t>
-  </si>
-  <si>
-    <t>百世</t>
-  </si>
-  <si>
-    <t>随机抽一部剧</t>
-  </si>
-  <si>
-    <t>哈姆雷特</t>
-  </si>
-  <si>
-    <t>快乐-2</t>
-  </si>
-  <si>
-    <t>李尔王</t>
-  </si>
-  <si>
-    <t>麦克白</t>
-  </si>
-  <si>
-    <t>奥赛罗</t>
-  </si>
-  <si>
-    <t>仲夏夜之梦</t>
-  </si>
-  <si>
-    <t>快乐+114509</t>
-  </si>
-  <si>
-    <t>威尼斯商人</t>
-  </si>
-  <si>
-    <t>第十二夜</t>
-  </si>
-  <si>
-    <t>皆大欢喜</t>
-  </si>
-  <si>
-    <t>永不言弃</t>
-  </si>
-  <si>
-    <t>你永远不会放弃</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect:RND</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
       <family val="2"/>
     </font>
@@ -1400,6 +1412,13 @@
       <name val="微软雅黑"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1410,12 +1429,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3b3838"/>
+        <fgColor rgb="FF3B3838"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFafabab"/>
+        <fgColor rgb="FFAFABAB"/>
       </patternFill>
     </fill>
   </fills>
@@ -1429,16 +1448,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1454,85 +1473,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="24">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1543,10 +1557,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1584,71 +1598,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1676,7 +1690,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1699,11 +1713,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1712,13 +1726,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1728,7 +1742,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1737,7 +1751,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1746,7 +1760,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1754,10 +1768,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1822,294 +1836,271 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AL186"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="18" width="25.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="19" width="27.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="20" width="33.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="21" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="18" width="11.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="18" width="11.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="22" width="19.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="22" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="22" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="22" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="22" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="22" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="22" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="23" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="23" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="23" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="23" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="23" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="23" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="22" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="23" width="18.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="23" width="18.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="23" width="18.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="22" width="19.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="22" width="21.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="22" width="19.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="22" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="22" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="25.54296875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.81640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="13.54296875" style="22" bestFit="1" customWidth="1"/>
+    <col min="14" max="22" width="23.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="23" max="28" width="23.26953125" style="23" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="23.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="18.81640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.81640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.1796875" style="22" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="13.54296875" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="39.65">
+    <row r="1" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="AF1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE1" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="39.65">
-      <c r="A2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="P2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE2" s="8" t="s">
-        <v>31</v>
-      </c>
       <c r="AF2" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AG2" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AH2" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AI2" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AJ2" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AK2" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
         <v>1001</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="9">
@@ -2149,15 +2140,15 @@
       <c r="AK3" s="14"/>
       <c r="AL3" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="24">
+    <row r="4" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
         <v>1002</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="9">
@@ -2197,15 +2188,15 @@
       <c r="AK4" s="14"/>
       <c r="AL4" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="24">
+    <row r="5" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
         <v>1003</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="9">
@@ -2237,13 +2228,13 @@
       <c r="AC5" s="14"/>
       <c r="AD5" s="14"/>
       <c r="AE5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF5" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG5" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="AF5" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG5" s="15" t="s">
-        <v>40</v>
       </c>
       <c r="AH5" s="14"/>
       <c r="AI5" s="14"/>
@@ -2251,15 +2242,15 @@
       <c r="AK5" s="14"/>
       <c r="AL5" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="24">
+    <row r="6" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
         <v>1004</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="9">
@@ -2291,13 +2282,13 @@
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
       <c r="AE6" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF6" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG6" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AH6" s="14"/>
       <c r="AI6" s="14"/>
@@ -2305,15 +2296,15 @@
       <c r="AK6" s="14"/>
       <c r="AL6" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="24">
+    <row r="7" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
         <v>1005</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="9">
@@ -2353,15 +2344,15 @@
       <c r="AK7" s="14"/>
       <c r="AL7" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="24">
+    <row r="8" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
         <v>1006</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="9">
@@ -2403,15 +2394,15 @@
       <c r="AK8" s="14"/>
       <c r="AL8" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="24">
+    <row r="9" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
         <v>1007</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="9">
@@ -2453,15 +2444,15 @@
       <c r="AK9" s="14"/>
       <c r="AL9" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="24">
+    <row r="10" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
         <v>1008</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="9">
@@ -2503,15 +2494,15 @@
       <c r="AK10" s="14"/>
       <c r="AL10" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="24">
+    <row r="11" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
         <v>1009</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="9">
@@ -2553,15 +2544,15 @@
       <c r="AK11" s="14"/>
       <c r="AL11" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="24">
+    <row r="12" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
         <v>1010</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="9">
@@ -2595,13 +2586,13 @@
       <c r="AC12" s="14"/>
       <c r="AD12" s="14"/>
       <c r="AE12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG12" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF12" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG12" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH12" s="14"/>
       <c r="AI12" s="14"/>
@@ -2609,15 +2600,15 @@
       <c r="AK12" s="14"/>
       <c r="AL12" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="24">
+    <row r="13" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
         <v>1011</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="9">
@@ -2657,15 +2648,15 @@
       <c r="AK13" s="14"/>
       <c r="AL13" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="24">
+    <row r="14" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
         <v>1012</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="9">
@@ -2697,13 +2688,13 @@
       <c r="AC14" s="14"/>
       <c r="AD14" s="14"/>
       <c r="AE14" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AF14" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AG14" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AH14" s="14"/>
       <c r="AI14" s="14"/>
@@ -2711,15 +2702,15 @@
       <c r="AK14" s="14"/>
       <c r="AL14" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="24">
+    <row r="15" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
         <v>1013</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="9">
@@ -2751,13 +2742,13 @@
       <c r="AC15" s="14"/>
       <c r="AD15" s="14"/>
       <c r="AE15" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AF15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG15" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AG15" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH15" s="14"/>
       <c r="AI15" s="14"/>
@@ -2765,15 +2756,15 @@
       <c r="AK15" s="14"/>
       <c r="AL15" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="24">
+    <row r="16" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
         <v>1014</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="9">
@@ -2807,13 +2798,13 @@
       <c r="AC16" s="14"/>
       <c r="AD16" s="14"/>
       <c r="AE16" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AF16" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AG16" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AH16" s="14"/>
       <c r="AI16" s="14"/>
@@ -2821,15 +2812,15 @@
       <c r="AK16" s="14"/>
       <c r="AL16" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="24">
+    <row r="17" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
         <v>1015</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="9">
@@ -2869,15 +2860,15 @@
       <c r="AK17" s="14"/>
       <c r="AL17" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="24">
+    <row r="18" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
         <v>1016</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="9">
@@ -2917,15 +2908,15 @@
       <c r="AK18" s="14"/>
       <c r="AL18" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="24">
+    <row r="19" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
         <v>1017</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="9">
@@ -2965,15 +2956,15 @@
       <c r="AK19" s="14"/>
       <c r="AL19" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="24">
+    <row r="20" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
         <v>1018</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="9">
@@ -3023,15 +3014,15 @@
       <c r="AK20" s="14"/>
       <c r="AL20" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="24">
+    <row r="21" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
         <v>1019</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="9">
@@ -3073,15 +3064,15 @@
       <c r="AK21" s="14"/>
       <c r="AL21" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="24">
+    <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
         <v>1020</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="9">
@@ -3123,15 +3114,15 @@
       <c r="AK22" s="14"/>
       <c r="AL22" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="39.65">
+    <row r="23" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
         <v>1021</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="9">
@@ -3175,15 +3166,15 @@
       <c r="AK23" s="14"/>
       <c r="AL23" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="39.65">
+    <row r="24" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
         <v>1022</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="9">
@@ -3223,15 +3214,15 @@
       <c r="AK24" s="14"/>
       <c r="AL24" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="39.65">
+    <row r="25" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
         <v>1023</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="9">
@@ -3281,15 +3272,15 @@
       <c r="AK25" s="14"/>
       <c r="AL25" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="39.65">
+    <row r="26" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
         <v>1024</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="9">
@@ -3321,13 +3312,13 @@
       <c r="AC26" s="14"/>
       <c r="AD26" s="14"/>
       <c r="AE26" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF26" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG26" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AH26" s="14"/>
       <c r="AI26" s="14"/>
@@ -3335,15 +3326,15 @@
       <c r="AK26" s="14"/>
       <c r="AL26" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="39.65">
+    <row r="27" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
         <v>1025</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="9">
@@ -3375,13 +3366,13 @@
       <c r="AC27" s="14"/>
       <c r="AD27" s="14"/>
       <c r="AE27" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF27" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG27" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH27" s="9">
         <v>1113</v>
@@ -3391,15 +3382,15 @@
       <c r="AK27" s="14"/>
       <c r="AL27" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="39.65">
+    <row r="28" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
         <v>1026</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="9">
@@ -3431,7 +3422,7 @@
       <c r="AC28" s="14"/>
       <c r="AD28" s="14"/>
       <c r="AE28" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF28" s="14"/>
       <c r="AG28" s="14"/>
@@ -3441,15 +3432,15 @@
       <c r="AK28" s="14"/>
       <c r="AL28" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="39.65">
+    <row r="29" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
         <v>1027</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="9">
@@ -3481,7 +3472,7 @@
       <c r="AC29" s="14"/>
       <c r="AD29" s="14"/>
       <c r="AE29" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF29" s="14"/>
       <c r="AG29" s="14"/>
@@ -3491,15 +3482,15 @@
       <c r="AK29" s="14"/>
       <c r="AL29" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="39.65">
+    <row r="30" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
         <v>1028</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="9">
@@ -3539,15 +3530,15 @@
       <c r="AK30" s="14"/>
       <c r="AL30" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="39.65">
+    <row r="31" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
         <v>1029</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="9">
@@ -3587,15 +3578,15 @@
       <c r="AK31" s="14"/>
       <c r="AL31" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="39.65">
+    <row r="32" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
         <v>1030</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="9">
@@ -3635,15 +3626,15 @@
       <c r="AK32" s="14"/>
       <c r="AL32" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="39.65">
+    <row r="33" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
         <v>1031</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="9">
@@ -3685,15 +3676,15 @@
       <c r="AK33" s="14"/>
       <c r="AL33" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="39.65">
+    <row r="34" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
         <v>1032</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="9">
@@ -3743,15 +3734,15 @@
       <c r="AK34" s="14"/>
       <c r="AL34" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="39.65">
+    <row r="35" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
         <v>1033</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="9">
@@ -3793,15 +3784,15 @@
       <c r="AK35" s="14"/>
       <c r="AL35" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="39.65">
+    <row r="36" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
         <v>1034</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="9">
@@ -3843,15 +3834,15 @@
       <c r="AK36" s="14"/>
       <c r="AL36" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="39.65">
+    <row r="37" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
         <v>1035</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="9">
@@ -3893,15 +3884,15 @@
       <c r="AK37" s="14"/>
       <c r="AL37" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="39.65">
+    <row r="38" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
         <v>1036</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="9">
@@ -3943,15 +3934,15 @@
       <c r="AK38" s="14"/>
       <c r="AL38" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="39.65">
+    <row r="39" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
         <v>1037</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="9">
@@ -3991,15 +3982,15 @@
       <c r="AK39" s="14"/>
       <c r="AL39" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="39.65">
+    <row r="40" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
         <v>1038</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="9">
@@ -4039,15 +4030,15 @@
       <c r="AK40" s="14"/>
       <c r="AL40" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="39.65">
+    <row r="41" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
         <v>1039</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="9">
@@ -4087,15 +4078,15 @@
       <c r="AK41" s="14"/>
       <c r="AL41" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="39.65">
+    <row r="42" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
         <v>1040</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="9">
@@ -4135,15 +4126,15 @@
       <c r="AK42" s="14"/>
       <c r="AL42" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="39.65">
+    <row r="43" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
         <v>1041</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="9">
@@ -4175,7 +4166,7 @@
       <c r="AC43" s="14"/>
       <c r="AD43" s="14"/>
       <c r="AE43" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF43" s="14"/>
       <c r="AG43" s="14"/>
@@ -4185,15 +4176,15 @@
       <c r="AK43" s="14"/>
       <c r="AL43" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="39.65">
+    <row r="44" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
         <v>1042</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="9">
@@ -4233,15 +4224,15 @@
       <c r="AK44" s="14"/>
       <c r="AL44" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="39.65">
+    <row r="45" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
         <v>1043</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="9">
@@ -4281,15 +4272,15 @@
       <c r="AK45" s="14"/>
       <c r="AL45" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="39.65">
+    <row r="46" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
         <v>1044</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="9">
@@ -4329,15 +4320,15 @@
       <c r="AK46" s="14"/>
       <c r="AL46" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="39.65">
+    <row r="47" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="9">
         <v>1045</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="9">
@@ -4377,15 +4368,15 @@
       <c r="AK47" s="14"/>
       <c r="AL47" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="39.65">
+    <row r="48" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="9">
         <v>1046</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="9">
@@ -4417,7 +4408,7 @@
       <c r="AC48" s="14"/>
       <c r="AD48" s="14"/>
       <c r="AE48" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF48" s="14"/>
       <c r="AG48" s="14"/>
@@ -4427,15 +4418,15 @@
       <c r="AK48" s="14"/>
       <c r="AL48" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="39.65">
+    <row r="49" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="9">
         <v>1047</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="9">
@@ -4475,15 +4466,15 @@
       <c r="AK49" s="14"/>
       <c r="AL49" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="39.65">
+    <row r="50" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="9">
         <v>1048</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="9">
@@ -4523,18 +4514,18 @@
       <c r="AK50" s="14"/>
       <c r="AL50" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="39.65">
+    <row r="51" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="9">
         <v>1049</v>
       </c>
       <c r="B51" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="E51" s="9">
         <v>0</v>
@@ -4575,18 +4566,18 @@
       <c r="AK51" s="14"/>
       <c r="AL51" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="39.65">
+    <row r="52" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="9">
         <v>1050</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="E52" s="9">
         <v>0</v>
@@ -4627,18 +4618,18 @@
       <c r="AK52" s="14"/>
       <c r="AL52" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="39.65">
+    <row r="53" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="9">
         <v>1051</v>
       </c>
       <c r="B53" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>145</v>
       </c>
       <c r="E53" s="9">
         <v>0</v>
@@ -4681,18 +4672,18 @@
       <c r="AK53" s="14"/>
       <c r="AL53" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="39.65">
+    <row r="54" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="9">
         <v>1052</v>
       </c>
       <c r="B54" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="E54" s="9">
         <v>0</v>
@@ -4733,18 +4724,18 @@
       <c r="AK54" s="14"/>
       <c r="AL54" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="39.65">
+    <row r="55" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="9">
         <v>1053</v>
       </c>
       <c r="B55" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="E55" s="9">
         <v>0</v>
@@ -4785,18 +4776,18 @@
       <c r="AK55" s="14"/>
       <c r="AL55" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="39.65">
+    <row r="56" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="9">
         <v>1054</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E56" s="9">
         <v>1</v>
@@ -4837,18 +4828,18 @@
       <c r="AK56" s="14"/>
       <c r="AL56" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="39.65">
+    <row r="57" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="9">
         <v>1055</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E57" s="9">
         <v>0</v>
@@ -4889,18 +4880,18 @@
       <c r="AK57" s="14"/>
       <c r="AL57" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="39.65">
+    <row r="58" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="9">
         <v>1056</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="E58" s="9">
         <v>1</v>
@@ -4941,18 +4932,18 @@
       <c r="AK58" s="14"/>
       <c r="AL58" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="39.65">
+    <row r="59" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="9">
         <v>1057</v>
       </c>
       <c r="B59" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D59" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="E59" s="9">
         <v>1</v>
@@ -4993,18 +4984,18 @@
       <c r="AK59" s="14"/>
       <c r="AL59" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="39.65">
+    <row r="60" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="9">
         <v>1058</v>
       </c>
       <c r="B60" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>164</v>
       </c>
       <c r="E60" s="9">
         <v>0</v>
@@ -5045,18 +5036,18 @@
       <c r="AK60" s="14"/>
       <c r="AL60" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="39.65">
+    <row r="61" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="9">
         <v>1059</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E61" s="9">
         <v>0</v>
@@ -5097,18 +5088,18 @@
       <c r="AK61" s="14"/>
       <c r="AL61" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="39.65">
+    <row r="62" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="9">
         <v>1060</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E62" s="9">
         <v>1</v>
@@ -5149,18 +5140,18 @@
       <c r="AK62" s="14"/>
       <c r="AL62" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="39.65">
+    <row r="63" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="9">
         <v>1061</v>
       </c>
       <c r="B63" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D63" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="E63" s="9">
         <v>1</v>
@@ -5201,18 +5192,18 @@
       <c r="AK63" s="14"/>
       <c r="AL63" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="39.65">
+    <row r="64" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="9">
         <v>1062</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E64" s="9">
         <v>0</v>
@@ -5253,15 +5244,15 @@
       <c r="AK64" s="14"/>
       <c r="AL64" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="39.65">
+    <row r="65" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="9">
         <v>1063</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="9">
@@ -5303,15 +5294,15 @@
       <c r="AK65" s="14"/>
       <c r="AL65" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="39.65">
+    <row r="66" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="9">
         <v>1064</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="9">
@@ -5353,15 +5344,15 @@
       <c r="AK66" s="14"/>
       <c r="AL66" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="39.65">
+    <row r="67" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="9">
         <v>1065</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="9">
@@ -5401,18 +5392,18 @@
       <c r="AK67" s="14"/>
       <c r="AL67" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="39.65">
+    <row r="68" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="9">
         <v>1066</v>
       </c>
       <c r="B68" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="E68" s="9">
         <v>0</v>
@@ -5453,18 +5444,18 @@
       <c r="AK68" s="14"/>
       <c r="AL68" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="39.65">
+    <row r="69" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="9">
         <v>1067</v>
       </c>
       <c r="B69" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D69" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="E69" s="9">
         <v>1</v>
@@ -5505,18 +5496,18 @@
       <c r="AK69" s="14"/>
       <c r="AL69" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="39.65">
+    <row r="70" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="9">
         <v>1068</v>
       </c>
       <c r="B70" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D70" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="E70" s="9">
         <v>0</v>
@@ -5557,18 +5548,18 @@
       <c r="AK70" s="14"/>
       <c r="AL70" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="39.65">
+    <row r="71" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="9">
         <v>1069</v>
       </c>
       <c r="B71" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D71" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>191</v>
       </c>
       <c r="E71" s="9">
         <v>0</v>
@@ -5609,18 +5600,18 @@
       <c r="AK71" s="14"/>
       <c r="AL71" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="39.65">
+    <row r="72" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="9">
         <v>1070</v>
       </c>
       <c r="B72" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>194</v>
       </c>
       <c r="E72" s="9">
         <v>0</v>
@@ -5661,15 +5652,15 @@
       <c r="AK72" s="14"/>
       <c r="AL72" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="39.65">
+    <row r="73" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="9">
         <v>1071</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="9">
@@ -5709,15 +5700,15 @@
       <c r="AK73" s="14"/>
       <c r="AL73" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="39.65">
+    <row r="74" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="9">
         <v>1072</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D74" s="12"/>
       <c r="E74" s="9">
@@ -5757,15 +5748,15 @@
       <c r="AK74" s="14"/>
       <c r="AL74" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="39.65">
+    <row r="75" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="9">
         <v>1073</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="9">
@@ -5805,18 +5796,18 @@
       <c r="AK75" s="14"/>
       <c r="AL75" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="39.65">
+    <row r="76" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="9">
         <v>1074</v>
       </c>
       <c r="B76" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D76" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="E76" s="9">
         <v>1</v>
@@ -5857,18 +5848,18 @@
       <c r="AK76" s="14"/>
       <c r="AL76" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="39.65">
+    <row r="77" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="9">
         <v>1075</v>
       </c>
       <c r="B77" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D77" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>206</v>
       </c>
       <c r="E77" s="9">
         <v>0</v>
@@ -5909,18 +5900,18 @@
       <c r="AK77" s="14"/>
       <c r="AL77" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="39.65">
+    <row r="78" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="9">
         <v>1076</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E78" s="9">
         <v>1</v>
@@ -5961,18 +5952,18 @@
       <c r="AK78" s="14"/>
       <c r="AL78" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="39.65">
+    <row r="79" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="9">
         <v>1077</v>
       </c>
       <c r="B79" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D79" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="E79" s="9">
         <v>1</v>
@@ -6013,18 +6004,18 @@
       <c r="AK79" s="14"/>
       <c r="AL79" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="39.65">
+    <row r="80" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="9">
         <v>1078</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E80" s="9">
         <v>0</v>
@@ -6065,18 +6056,18 @@
       <c r="AK80" s="14"/>
       <c r="AL80" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="39.65">
+    <row r="81" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="9">
         <v>1079</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E81" s="9">
         <v>0</v>
@@ -6117,18 +6108,18 @@
       <c r="AK81" s="14"/>
       <c r="AL81" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="39.65">
+    <row r="82" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="9">
         <v>1080</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E82" s="9">
         <v>0</v>
@@ -6169,18 +6160,18 @@
       <c r="AK82" s="14"/>
       <c r="AL82" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="39.65">
+    <row r="83" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="9">
         <v>1081</v>
       </c>
       <c r="B83" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D83" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="E83" s="9">
         <v>0</v>
@@ -6227,18 +6218,18 @@
       <c r="AK83" s="14"/>
       <c r="AL83" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="39.65">
+    <row r="84" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="9">
         <v>1082</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E84" s="9">
         <v>1</v>
@@ -6285,18 +6276,18 @@
       <c r="AK84" s="14"/>
       <c r="AL84" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="39.65">
+    <row r="85" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="9">
         <v>1083</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E85" s="9">
         <v>2</v>
@@ -6343,15 +6334,15 @@
       <c r="AK85" s="14"/>
       <c r="AL85" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="39.65">
+    <row r="86" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="9">
         <v>1084</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D86" s="12"/>
       <c r="E86" s="9">
@@ -6387,7 +6378,7 @@
       <c r="AC86" s="14"/>
       <c r="AD86" s="14"/>
       <c r="AE86" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AF86" s="14"/>
       <c r="AG86" s="14"/>
@@ -6397,15 +6388,15 @@
       <c r="AK86" s="14"/>
       <c r="AL86" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="39.65">
+    <row r="87" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="9">
         <v>1085</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="9">
@@ -6441,7 +6432,7 @@
       <c r="AC87" s="14"/>
       <c r="AD87" s="14"/>
       <c r="AE87" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AF87" s="14"/>
       <c r="AG87" s="14"/>
@@ -6451,15 +6442,15 @@
       <c r="AK87" s="14"/>
       <c r="AL87" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="39.65">
+    <row r="88" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="9">
         <v>1086</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D88" s="12"/>
       <c r="E88" s="9">
@@ -6493,7 +6484,7 @@
       <c r="AC88" s="14"/>
       <c r="AD88" s="14"/>
       <c r="AE88" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AF88" s="14"/>
       <c r="AG88" s="14"/>
@@ -6503,18 +6494,18 @@
       <c r="AK88" s="14"/>
       <c r="AL88" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="39.65">
+    <row r="89" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="9">
         <v>1087</v>
       </c>
       <c r="B89" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D89" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="E89" s="9">
         <v>1</v>
@@ -6555,18 +6546,18 @@
       <c r="AK89" s="14"/>
       <c r="AL89" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="39.65">
+    <row r="90" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="9">
         <v>1088</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E90" s="9">
         <v>0</v>
@@ -6607,18 +6598,18 @@
       <c r="AK90" s="14"/>
       <c r="AL90" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="39.65">
+    <row r="91" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="9">
         <v>1089</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E91" s="9">
         <v>0</v>
@@ -6659,18 +6650,18 @@
       <c r="AK91" s="14"/>
       <c r="AL91" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="39.65">
+    <row r="92" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="9">
         <v>1090</v>
       </c>
       <c r="B92" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D92" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="E92" s="9">
         <v>0</v>
@@ -6717,18 +6708,18 @@
       <c r="AK92" s="14"/>
       <c r="AL92" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="39.65">
+    <row r="93" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="9">
         <v>1091</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E93" s="9">
         <v>1</v>
@@ -6775,18 +6766,18 @@
       <c r="AK93" s="14"/>
       <c r="AL93" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="39.65">
+    <row r="94" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="9">
         <v>1092</v>
       </c>
       <c r="B94" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D94" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="E94" s="9">
         <v>0</v>
@@ -6833,15 +6824,15 @@
       <c r="AK94" s="14"/>
       <c r="AL94" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="39.65">
+    <row r="95" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="9">
         <v>1093</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="9">
@@ -6885,15 +6876,15 @@
       <c r="AK95" s="14"/>
       <c r="AL95" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="39.65">
+    <row r="96" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="9">
         <v>1094</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="9">
@@ -6935,18 +6926,18 @@
       <c r="AK96" s="14"/>
       <c r="AL96" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="39.65">
+    <row r="97" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="9">
         <v>1095</v>
       </c>
       <c r="B97" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D97" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="E97" s="9">
         <v>0</v>
@@ -6993,18 +6984,18 @@
       <c r="AK97" s="14"/>
       <c r="AL97" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="39.65">
+    <row r="98" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="9">
         <v>1096</v>
       </c>
       <c r="B98" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D98" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="E98" s="9">
         <v>0</v>
@@ -7051,18 +7042,18 @@
       <c r="AK98" s="14"/>
       <c r="AL98" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="39.65">
+    <row r="99" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="9">
         <v>1097</v>
       </c>
       <c r="B99" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="D99" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>259</v>
       </c>
       <c r="E99" s="9">
         <v>1</v>
@@ -7109,18 +7100,18 @@
       <c r="AK99" s="14"/>
       <c r="AL99" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="39.65">
+    <row r="100" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="9">
         <v>1098</v>
       </c>
       <c r="B100" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D100" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>262</v>
       </c>
       <c r="E100" s="9">
         <v>1</v>
@@ -7167,15 +7158,15 @@
       <c r="AK100" s="14"/>
       <c r="AL100" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="39.65">
+    <row r="101" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="9">
         <v>1099</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="9">
@@ -7219,15 +7210,15 @@
       <c r="AK101" s="14"/>
       <c r="AL101" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="39.65">
+    <row r="102" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="9">
         <v>1100</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D102" s="12"/>
       <c r="E102" s="9">
@@ -7271,18 +7262,18 @@
       <c r="AK102" s="14"/>
       <c r="AL102" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="39.65">
+    <row r="103" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="9">
         <v>1101</v>
       </c>
       <c r="B103" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="D103" s="17" t="s">
         <v>267</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="D103" s="17" t="s">
-        <v>269</v>
       </c>
       <c r="E103" s="9">
         <v>0</v>
@@ -7331,18 +7322,18 @@
       <c r="AK103" s="14"/>
       <c r="AL103" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="39.65">
+    <row r="104" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="9">
         <v>1102</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E104" s="9">
         <v>1</v>
@@ -7391,18 +7382,18 @@
       <c r="AK104" s="14"/>
       <c r="AL104" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="39.65">
+    <row r="105" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="9">
         <v>1103</v>
       </c>
       <c r="B105" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="D105" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="E105" s="9">
         <v>0</v>
@@ -7441,18 +7432,18 @@
       <c r="AK105" s="14"/>
       <c r="AL105" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="39.65">
+    <row r="106" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="9">
         <v>1104</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E106" s="9">
         <v>2</v>
@@ -7491,18 +7482,18 @@
       <c r="AK106" s="14"/>
       <c r="AL106" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="39.65">
+    <row r="107" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="9">
         <v>1105</v>
       </c>
       <c r="B107" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D107" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="D107" s="10" t="s">
-        <v>279</v>
       </c>
       <c r="E107" s="9">
         <v>1</v>
@@ -7541,15 +7532,15 @@
       <c r="AK107" s="14"/>
       <c r="AL107" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="39.65">
+    <row r="108" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="9">
         <v>1106</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D108" s="12"/>
       <c r="E108" s="9">
@@ -7589,15 +7580,15 @@
       <c r="AK108" s="14"/>
       <c r="AL108" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="39.65">
+    <row r="109" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="9">
         <v>1107</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D109" s="12"/>
       <c r="E109" s="9">
@@ -7637,15 +7628,15 @@
       <c r="AK109" s="14"/>
       <c r="AL109" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="39.65">
+    <row r="110" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="9">
         <v>1108</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D110" s="12"/>
       <c r="E110" s="9">
@@ -7685,15 +7676,15 @@
       <c r="AK110" s="14"/>
       <c r="AL110" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="39.65">
+    <row r="111" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="9">
         <v>1109</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D111" s="12"/>
       <c r="E111" s="9">
@@ -7733,15 +7724,15 @@
       <c r="AK111" s="14"/>
       <c r="AL111" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="39.65">
+    <row r="112" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="9">
         <v>1110</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="9">
@@ -7781,15 +7772,15 @@
       <c r="AK112" s="14"/>
       <c r="AL112" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="39.65">
+    <row r="113" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="9">
         <v>1111</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D113" s="12"/>
       <c r="E113" s="9">
@@ -7829,15 +7820,15 @@
       <c r="AK113" s="14"/>
       <c r="AL113" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="39.65">
+    <row r="114" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="9">
         <v>1112</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D114" s="12"/>
       <c r="E114" s="9">
@@ -7877,15 +7868,15 @@
       <c r="AK114" s="14"/>
       <c r="AL114" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="39.65">
+    <row r="115" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="9">
         <v>1113</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="9">
@@ -7917,13 +7908,13 @@
       <c r="AC115" s="14"/>
       <c r="AD115" s="14"/>
       <c r="AE115" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF115" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AG115" s="15" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AH115" s="9">
         <v>1027</v>
@@ -7937,18 +7928,18 @@
       <c r="AK115" s="14"/>
       <c r="AL115" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="39.65">
+    <row r="116" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="9">
         <v>1114</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E116" s="9">
         <v>3</v>
@@ -7987,15 +7978,15 @@
       <c r="AK116" s="14"/>
       <c r="AL116" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="39.65">
+    <row r="117" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="9">
         <v>1115</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D117" s="12"/>
       <c r="E117" s="9">
@@ -8035,15 +8026,15 @@
       <c r="AK117" s="14"/>
       <c r="AL117" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="39.65">
+    <row r="118" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="9">
         <v>1116</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D118" s="12"/>
       <c r="E118" s="9">
@@ -8083,15 +8074,15 @@
       <c r="AK118" s="14"/>
       <c r="AL118" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="39.65">
+    <row r="119" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="9">
         <v>1117</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D119" s="12"/>
       <c r="E119" s="9">
@@ -8131,15 +8122,15 @@
       <c r="AK119" s="14"/>
       <c r="AL119" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="39.65">
+    <row r="120" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="9">
         <v>1118</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D120" s="12"/>
       <c r="E120" s="9">
@@ -8179,15 +8170,15 @@
       <c r="AK120" s="14"/>
       <c r="AL120" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="39.65">
+    <row r="121" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="9">
         <v>1119</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D121" s="12"/>
       <c r="E121" s="9">
@@ -8227,15 +8218,15 @@
       <c r="AK121" s="14"/>
       <c r="AL121" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="39.65">
+    <row r="122" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="9">
         <v>1120</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D122" s="12"/>
       <c r="E122" s="9">
@@ -8275,15 +8266,15 @@
       <c r="AK122" s="14"/>
       <c r="AL122" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="39.65">
+    <row r="123" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="9">
         <v>1121</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D123" s="12"/>
       <c r="E123" s="9">
@@ -8323,15 +8314,15 @@
       <c r="AK123" s="14"/>
       <c r="AL123" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="39.65">
+    <row r="124" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="9">
         <v>1122</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D124" s="12"/>
       <c r="E124" s="9">
@@ -8365,13 +8356,13 @@
       <c r="AC124" s="14"/>
       <c r="AD124" s="14"/>
       <c r="AE124" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="AF124" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="AG124" s="15" t="s">
         <v>315</v>
-      </c>
-      <c r="AF124" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="AG124" s="15" t="s">
-        <v>317</v>
       </c>
       <c r="AH124" s="14"/>
       <c r="AI124" s="14"/>
@@ -8379,15 +8370,15 @@
       <c r="AK124" s="14"/>
       <c r="AL124" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="39.65">
+    <row r="125" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="9">
         <v>1123</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D125" s="12"/>
       <c r="E125" s="9">
@@ -8427,15 +8418,15 @@
       <c r="AK125" s="14"/>
       <c r="AL125" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="39.65">
+    <row r="126" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="9">
         <v>1124</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D126" s="12"/>
       <c r="E126" s="9">
@@ -8475,15 +8466,15 @@
       <c r="AK126" s="14"/>
       <c r="AL126" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="39.65">
+    <row r="127" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="9">
         <v>1125</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D127" s="12"/>
       <c r="E127" s="9">
@@ -8523,15 +8514,15 @@
       <c r="AK127" s="14"/>
       <c r="AL127" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="39.65">
+    <row r="128" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="9">
         <v>1126</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D128" s="12"/>
       <c r="E128" s="9">
@@ -8571,15 +8562,15 @@
       <c r="AK128" s="14"/>
       <c r="AL128" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="39.65">
+    <row r="129" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="9">
         <v>1127</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D129" s="12"/>
       <c r="E129" s="9">
@@ -8619,15 +8610,15 @@
       <c r="AK129" s="14"/>
       <c r="AL129" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="39.65">
+    <row r="130" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="9">
         <v>1128</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D130" s="12"/>
       <c r="E130" s="9">
@@ -8667,15 +8658,15 @@
       <c r="AK130" s="14"/>
       <c r="AL130" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="39.65">
+    <row r="131" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="9">
         <v>1129</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D131" s="12"/>
       <c r="E131" s="9">
@@ -8715,15 +8706,15 @@
       <c r="AK131" s="14"/>
       <c r="AL131" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="39.65">
+    <row r="132" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="9">
         <v>1130</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="9">
@@ -8763,15 +8754,15 @@
       <c r="AK132" s="14"/>
       <c r="AL132" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="39.65">
+    <row r="133" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A133" s="9">
         <v>1131</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D133" s="12"/>
       <c r="E133" s="9">
@@ -8811,15 +8802,15 @@
       <c r="AK133" s="14"/>
       <c r="AL133" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="39.65">
+    <row r="134" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="9">
         <v>1132</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D134" s="12"/>
       <c r="E134" s="9">
@@ -8859,15 +8850,15 @@
       <c r="AK134" s="14"/>
       <c r="AL134" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="39.65">
+    <row r="135" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="9">
         <v>1133</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D135" s="12"/>
       <c r="E135" s="9">
@@ -8907,15 +8898,15 @@
       <c r="AK135" s="14"/>
       <c r="AL135" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="39.65">
+    <row r="136" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A136" s="9">
         <v>1134</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D136" s="12"/>
       <c r="E136" s="9">
@@ -8955,15 +8946,15 @@
       <c r="AK136" s="14"/>
       <c r="AL136" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="39.65">
+    <row r="137" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="9">
         <v>1135</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D137" s="12"/>
       <c r="E137" s="9">
@@ -9003,15 +8994,15 @@
       <c r="AK137" s="14"/>
       <c r="AL137" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="39.65">
+    <row r="138" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="9">
         <v>1136</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D138" s="12"/>
       <c r="E138" s="9">
@@ -9053,18 +9044,18 @@
       <c r="AK138" s="14"/>
       <c r="AL138" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="39.65">
+    <row r="139" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="9">
         <v>1137</v>
       </c>
       <c r="B139" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D139" s="10" t="s">
         <v>346</v>
-      </c>
-      <c r="C139" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>348</v>
       </c>
       <c r="E139" s="9">
         <v>1</v>
@@ -9113,15 +9104,15 @@
       <c r="AK139" s="14"/>
       <c r="AL139" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="39.65">
+    <row r="140" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A140" s="9">
         <v>1138</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D140" s="12"/>
       <c r="E140" s="9">
@@ -9163,15 +9154,15 @@
       <c r="AK140" s="14"/>
       <c r="AL140" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="39.65">
+    <row r="141" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="9">
         <v>1139</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D141" s="12"/>
       <c r="E141" s="9">
@@ -9213,15 +9204,15 @@
       <c r="AK141" s="14"/>
       <c r="AL141" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="39.65">
+    <row r="142" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A142" s="9">
         <v>1140</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D142" s="12"/>
       <c r="E142" s="9">
@@ -9263,15 +9254,15 @@
       <c r="AK142" s="14"/>
       <c r="AL142" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="39.65">
+    <row r="143" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="9">
         <v>1141</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D143" s="12"/>
       <c r="E143" s="9">
@@ -9313,15 +9304,15 @@
       <c r="AK143" s="14"/>
       <c r="AL143" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="39.65">
+    <row r="144" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A144" s="9">
         <v>1142</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D144" s="12"/>
       <c r="E144" s="9">
@@ -9355,13 +9346,13 @@
       <c r="AC144" s="14"/>
       <c r="AD144" s="14"/>
       <c r="AE144" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF144" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG144" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF144" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG144" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH144" s="9">
         <v>1110</v>
@@ -9379,15 +9370,15 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="39.65">
+    <row r="145" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A145" s="9">
         <v>1143</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D145" s="12"/>
       <c r="E145" s="9">
@@ -9421,13 +9412,13 @@
       <c r="AC145" s="14"/>
       <c r="AD145" s="14"/>
       <c r="AE145" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF145" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG145" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF145" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG145" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH145" s="9">
         <v>1110</v>
@@ -9445,15 +9436,15 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="39.65">
+    <row r="146" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A146" s="9">
         <v>1144</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D146" s="12"/>
       <c r="E146" s="9">
@@ -9495,15 +9486,15 @@
       <c r="AK146" s="14"/>
       <c r="AL146" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="39.65">
+    <row r="147" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="9">
         <v>1145</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D147" s="12"/>
       <c r="E147" s="9">
@@ -9575,15 +9566,15 @@
       <c r="AK147" s="14"/>
       <c r="AL147" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="39.65">
+    <row r="148" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="9">
         <v>1146</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D148" s="12"/>
       <c r="E148" s="9">
@@ -9599,25 +9590,25 @@
       <c r="M148" s="14"/>
       <c r="N148" s="14"/>
       <c r="O148" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="P148" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q148" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="P148" s="9" t="s">
+      <c r="R148" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="Q148" s="9" t="s">
+      <c r="S148" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="R148" s="9" t="s">
+      <c r="T148" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="S148" s="9" t="s">
+      <c r="U148" s="9" t="s">
         <v>371</v>
-      </c>
-      <c r="T148" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="U148" s="9" t="s">
-        <v>373</v>
       </c>
       <c r="V148" s="14"/>
       <c r="W148" s="14"/>
@@ -9637,15 +9628,15 @@
       <c r="AK148" s="14"/>
       <c r="AL148" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="39.65">
+    <row r="149" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A149" s="9">
         <v>1147</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D149" s="12"/>
       <c r="E149" s="9">
@@ -9685,15 +9676,15 @@
       <c r="AK149" s="14"/>
       <c r="AL149" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="39.65">
+    <row r="150" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A150" s="9">
         <v>1148</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D150" s="12"/>
       <c r="E150" s="9">
@@ -9743,15 +9734,15 @@
       <c r="AK150" s="14"/>
       <c r="AL150" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="39.65">
+    <row r="151" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="9">
         <v>2001</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D151" s="12"/>
       <c r="E151" s="9">
@@ -9795,15 +9786,15 @@
       <c r="AK151" s="14"/>
       <c r="AL151" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="39.65">
+    <row r="152" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="9">
         <v>2002</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D152" s="12"/>
       <c r="E152" s="9">
@@ -9847,15 +9838,15 @@
       <c r="AK152" s="14"/>
       <c r="AL152" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="39.65">
+    <row r="153" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="9">
         <v>2003</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D153" s="12"/>
       <c r="E153" s="9">
@@ -9897,15 +9888,15 @@
       <c r="AK153" s="14"/>
       <c r="AL153" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="39.65">
+    <row r="154" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A154" s="9">
         <v>2004</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D154" s="12"/>
       <c r="E154" s="9">
@@ -9947,15 +9938,15 @@
       <c r="AK154" s="14"/>
       <c r="AL154" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="39.65">
+    <row r="155" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A155" s="9">
         <v>2005</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C155" s="11">
-        <v>3.1415926</v>
+        <v>3.1415926000000001</v>
       </c>
       <c r="D155" s="12"/>
       <c r="E155" s="9">
@@ -9997,15 +9988,15 @@
       <c r="AK155" s="14"/>
       <c r="AL155" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="39.65">
+    <row r="156" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A156" s="9">
         <v>2006</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D156" s="12"/>
       <c r="E156" s="9">
@@ -10041,13 +10032,13 @@
       <c r="AC156" s="14"/>
       <c r="AD156" s="14"/>
       <c r="AE156" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF156" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG156" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF156" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG156" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH156" s="9">
         <v>1110</v>
@@ -10065,18 +10056,18 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="39.65">
+    <row r="157" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A157" s="9">
         <v>2007</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E157" s="9">
         <v>0</v>
@@ -10125,18 +10116,18 @@
       <c r="AK157" s="14"/>
       <c r="AL157" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="39.65">
+    <row r="158" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A158" s="9">
         <v>2008</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E158" s="9">
         <v>0</v>
@@ -10187,15 +10178,15 @@
       <c r="AK158" s="14"/>
       <c r="AL158" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="39.65">
+    <row r="159" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A159" s="9">
         <v>2009</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D159" s="12"/>
       <c r="E159" s="9">
@@ -10231,13 +10222,13 @@
       <c r="AC159" s="14"/>
       <c r="AD159" s="14"/>
       <c r="AE159" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF159" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG159" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF159" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG159" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH159" s="9">
         <v>1110</v>
@@ -10255,15 +10246,15 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="39.65">
+    <row r="160" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A160" s="9">
         <v>2010</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D160" s="12"/>
       <c r="E160" s="9">
@@ -10299,13 +10290,13 @@
       <c r="AC160" s="14"/>
       <c r="AD160" s="14"/>
       <c r="AE160" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF160" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG160" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF160" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG160" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH160" s="9">
         <v>1110</v>
@@ -10323,15 +10314,15 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="39.65">
+    <row r="161" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A161" s="9">
         <v>2011</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D161" s="12"/>
       <c r="E161" s="9">
@@ -10367,13 +10358,13 @@
       <c r="AC161" s="14"/>
       <c r="AD161" s="14"/>
       <c r="AE161" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF161" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG161" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF161" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG161" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH161" s="9">
         <v>1110</v>
@@ -10391,15 +10382,15 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="39.65">
+    <row r="162" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A162" s="9">
         <v>2012</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D162" s="12"/>
       <c r="E162" s="9">
@@ -10435,13 +10426,13 @@
       <c r="AC162" s="14"/>
       <c r="AD162" s="14"/>
       <c r="AE162" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF162" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG162" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF162" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG162" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH162" s="9">
         <v>1110</v>
@@ -10459,15 +10450,15 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="39.65">
+    <row r="163" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A163" s="9">
         <v>2013</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D163" s="12"/>
       <c r="E163" s="9">
@@ -10503,13 +10494,13 @@
       <c r="AC163" s="14"/>
       <c r="AD163" s="14"/>
       <c r="AE163" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF163" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG163" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="AF163" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG163" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="AH163" s="9">
         <v>1110</v>
@@ -10527,15 +10518,15 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="39.65">
+    <row r="164" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A164" s="9">
         <v>2014</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D164" s="12"/>
       <c r="E164" s="9">
@@ -10577,15 +10568,15 @@
       <c r="AK164" s="14"/>
       <c r="AL164" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="39.65">
+    <row r="165" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A165" s="9">
         <v>2015</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D165" s="12"/>
       <c r="E165" s="9">
@@ -10641,15 +10632,15 @@
       <c r="AK165" s="14"/>
       <c r="AL165" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="39.65">
+    <row r="166" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A166" s="9">
         <v>2016</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D166" s="12"/>
       <c r="E166" s="9">
@@ -10682,7 +10673,7 @@
         <v>1048</v>
       </c>
       <c r="T166" s="9" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="U166" s="9">
         <v>1147</v>
@@ -10705,15 +10696,15 @@
       <c r="AK166" s="14"/>
       <c r="AL166" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="39.65">
+    <row r="167" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A167" s="9">
         <v>2017</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D167" s="12"/>
       <c r="E167" s="9">
@@ -10755,18 +10746,18 @@
       <c r="AK167" s="14"/>
       <c r="AL167" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="39.65">
+    <row r="168" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A168" s="9">
         <v>2018</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E168" s="9">
         <v>0</v>
@@ -10809,18 +10800,18 @@
       <c r="AK168" s="14"/>
       <c r="AL168" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="39.65">
+    <row r="169" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A169" s="9">
         <v>2019</v>
       </c>
       <c r="B169" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D169" s="10" t="s">
         <v>402</v>
-      </c>
-      <c r="C169" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="D169" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="E169" s="9">
         <v>1</v>
@@ -10863,18 +10854,18 @@
       <c r="AK169" s="14"/>
       <c r="AL169" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="39.65">
+    <row r="170" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A170" s="9">
         <v>2020</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E170" s="9">
         <v>0</v>
@@ -10917,15 +10908,15 @@
       <c r="AK170" s="14"/>
       <c r="AL170" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="39.65">
+    <row r="171" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="9">
         <v>2021</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D171" s="12"/>
       <c r="E171" s="9">
@@ -10943,46 +10934,46 @@
       <c r="M171" s="14"/>
       <c r="N171" s="14"/>
       <c r="O171" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="P171" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q171" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="P171" s="15" t="s">
+      <c r="R171" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="Q171" s="15" t="s">
+      <c r="S171" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="R171" s="15" t="s">
+      <c r="T171" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="S171" s="15" t="s">
+      <c r="U171" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="T171" s="15" t="s">
+      <c r="V171" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="U171" s="15" t="s">
+      <c r="W171" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="V171" s="15" t="s">
+      <c r="X171" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="W171" s="15" t="s">
+      <c r="Y171" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="X171" s="15" t="s">
+      <c r="Z171" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="Y171" s="15" t="s">
+      <c r="AA171" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="Z171" s="15" t="s">
+      <c r="AB171" s="15" t="s">
         <v>420</v>
-      </c>
-      <c r="AA171" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="AB171" s="15" t="s">
-        <v>422</v>
       </c>
       <c r="AC171" s="9"/>
       <c r="AD171" s="9"/>
@@ -10995,15 +10986,15 @@
       <c r="AK171" s="14"/>
       <c r="AL171" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="39.65">
+    <row r="172" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="9">
         <v>2022</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D172" s="12"/>
       <c r="E172" s="9">
@@ -11045,15 +11036,15 @@
       <c r="AK172" s="14"/>
       <c r="AL172" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="39.65">
+    <row r="173" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="9">
         <v>2023</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D173" s="12"/>
       <c r="E173" s="9">
@@ -11095,15 +11086,15 @@
       <c r="AK173" s="14"/>
       <c r="AL173" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="39.65">
+    <row r="174" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="9">
         <v>2024</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D174" s="12"/>
       <c r="E174" s="9">
@@ -11145,15 +11136,15 @@
       <c r="AK174" s="14"/>
       <c r="AL174" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="39.65">
+    <row r="175" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="9">
         <v>2025</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D175" s="12"/>
       <c r="E175" s="9">
@@ -11197,18 +11188,18 @@
       <c r="AK175" s="14"/>
       <c r="AL175" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="39.65">
+    <row r="176" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="9">
         <v>2026</v>
       </c>
       <c r="B176" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="D176" s="10" t="s">
         <v>430</v>
-      </c>
-      <c r="C176" s="11" t="s">
-        <v>431</v>
-      </c>
-      <c r="D176" s="10" t="s">
-        <v>432</v>
       </c>
       <c r="E176" s="9">
         <v>1</v>
@@ -11259,15 +11250,15 @@
       <c r="AK176" s="14"/>
       <c r="AL176" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="39.65">
+    <row r="177" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="9">
         <v>2027</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D177" s="12"/>
       <c r="E177" s="9">
@@ -11325,15 +11316,15 @@
       <c r="AK177" s="14"/>
       <c r="AL177" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="39.65">
+    <row r="178" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="9">
         <v>2028</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D178" s="12"/>
       <c r="E178" s="9">
@@ -11377,15 +11368,15 @@
       <c r="AK178" s="14"/>
       <c r="AL178" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="39.65">
+    <row r="179" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="9">
         <v>2029</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D179" s="12"/>
       <c r="E179" s="9">
@@ -11429,15 +11420,15 @@
       <c r="AK179" s="14"/>
       <c r="AL179" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="39.65">
+    <row r="180" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="9">
         <v>2030</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D180" s="12"/>
       <c r="E180" s="9">
@@ -11481,15 +11472,15 @@
       <c r="AK180" s="14"/>
       <c r="AL180" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="39.65">
+    <row r="181" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="9">
         <v>2031</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D181" s="12"/>
       <c r="E181" s="9">
@@ -11533,15 +11524,15 @@
       <c r="AK181" s="14"/>
       <c r="AL181" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="39.65">
+    <row r="182" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="9">
         <v>2032</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D182" s="12"/>
       <c r="E182" s="9">
@@ -11585,15 +11576,15 @@
       <c r="AK182" s="14"/>
       <c r="AL182" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="39.65">
+    <row r="183" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="9">
         <v>2033</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D183" s="12"/>
       <c r="E183" s="9">
@@ -11637,15 +11628,15 @@
       <c r="AK183" s="14"/>
       <c r="AL183" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="39.65">
+    <row r="184" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="9">
         <v>2034</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D184" s="12"/>
       <c r="E184" s="9">
@@ -11689,15 +11680,15 @@
       <c r="AK184" s="14"/>
       <c r="AL184" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="39.65">
+    <row r="185" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="9">
         <v>2035</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D185" s="12"/>
       <c r="E185" s="9">
@@ -11741,15 +11732,15 @@
       <c r="AK185" s="14"/>
       <c r="AL185" s="14"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="39.65">
+    <row r="186" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="9">
         <v>2036</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D186" s="12"/>
       <c r="E186" s="9">
@@ -11792,6 +11783,7 @@
       <c r="AL186" s="14"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/packages/data/src/talent.xlsx
+++ b/packages/data/src/talent.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vick\dev\lifeRestart\packages\data\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vick\dev\remake\packages\data\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA48E9A-8385-4104-9854-1D99E52CEA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C3C39B-4118-4EED-A7A7-0B5A65F809DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="1460" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="talent" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="449">
   <si>
     <t>name</t>
   </si>
@@ -42,9 +42,6 @@
     <t>exclusive</t>
   </si>
   <si>
-    <t>status</t>
-  </si>
-  <si>
     <t>effect:SPR</t>
   </si>
   <si>
@@ -58,9 +55,6 @@
   </si>
   <si>
     <t>effect:INT</t>
-  </si>
-  <si>
-    <t>replacement:grade[]</t>
   </si>
   <si>
     <t>replacement:talent[]</t>
@@ -1367,6 +1361,22 @@
   </si>
   <si>
     <t>effect:RND</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>points</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大触发次数，默认1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>max</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>replacement:grade</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1840,29 +1850,31 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AL186"/>
+  <dimension ref="A1:AM186"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.54296875" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.54296875" style="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.81640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.1796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.26953125" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="13.54296875" style="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="22" width="23.26953125" style="22" bestFit="1" customWidth="1"/>
-    <col min="23" max="28" width="23.26953125" style="23" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="23.26953125" style="22" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="18.81640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.26953125" style="22" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="21.81640625" style="22" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.1796875" style="22" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="13.54296875" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.6328125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="26.26953125" style="21" customWidth="1"/>
+    <col min="6" max="7" width="11.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="13.54296875" style="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.08984375" style="22" customWidth="1"/>
+    <col min="16" max="23" width="23.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="24" max="29" width="23.26953125" style="23" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="23.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="18.81640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="21.81640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.1796875" style="22" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="13.54296875" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1873,241 +1885,246 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="AG2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="AI2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="AM2" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
         <v>1001</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="12"/>
-      <c r="E3" s="9">
+      <c r="F3" s="9">
         <v>0</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="14"/>
+      <c r="G3" s="13"/>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
@@ -2139,23 +2156,23 @@
       <c r="AJ3" s="14"/>
       <c r="AK3" s="14"/>
       <c r="AL3" s="14"/>
-    </row>
-    <row r="4" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM3" s="14"/>
+    </row>
+    <row r="4" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
         <v>1002</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" s="12"/>
-      <c r="E4" s="9">
+      <c r="F4" s="9">
         <v>0</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
@@ -2187,23 +2204,23 @@
       <c r="AJ4" s="14"/>
       <c r="AK4" s="14"/>
       <c r="AL4" s="14"/>
-    </row>
-    <row r="5" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM4" s="14"/>
+    </row>
+    <row r="5" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
         <v>1003</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" s="12"/>
-      <c r="E5" s="9">
-        <v>1</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14"/>
+      <c r="F5" s="9">
+        <v>1</v>
+      </c>
+      <c r="G5" s="13"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
@@ -2227,37 +2244,37 @@
       <c r="AB5" s="14"/>
       <c r="AC5" s="14"/>
       <c r="AD5" s="14"/>
-      <c r="AE5" s="15" t="s">
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG5" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH5" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AF5" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG5" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH5" s="14"/>
       <c r="AI5" s="14"/>
       <c r="AJ5" s="14"/>
       <c r="AK5" s="14"/>
       <c r="AL5" s="14"/>
-    </row>
-    <row r="6" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM5" s="14"/>
+    </row>
+    <row r="6" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
         <v>1004</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" s="12"/>
-      <c r="E6" s="9">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="14"/>
+      <c r="F6" s="9">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
@@ -2281,37 +2298,37 @@
       <c r="AB6" s="14"/>
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
-      <c r="AE6" s="15" t="s">
-        <v>41</v>
-      </c>
+      <c r="AE6" s="14"/>
       <c r="AF6" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AG6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH6" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="AH6" s="15" t="s">
+        <v>35</v>
+      </c>
       <c r="AI6" s="14"/>
       <c r="AJ6" s="14"/>
       <c r="AK6" s="14"/>
       <c r="AL6" s="14"/>
-    </row>
-    <row r="7" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM6" s="14"/>
+    </row>
+    <row r="7" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
         <v>1005</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" s="12"/>
-      <c r="E7" s="9">
+      <c r="F7" s="9">
         <v>2</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14"/>
+      <c r="G7" s="13"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
@@ -2343,27 +2360,27 @@
       <c r="AJ7" s="14"/>
       <c r="AK7" s="14"/>
       <c r="AL7" s="14"/>
-    </row>
-    <row r="8" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM7" s="14"/>
+    </row>
+    <row r="8" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
         <v>1006</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="9">
+      <c r="F8" s="9">
         <v>0</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="9">
-        <v>1</v>
-      </c>
-      <c r="I8" s="14"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="9">
+        <v>1</v>
+      </c>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
       <c r="L8" s="14"/>
@@ -2393,26 +2410,26 @@
       <c r="AJ8" s="14"/>
       <c r="AK8" s="14"/>
       <c r="AL8" s="14"/>
-    </row>
-    <row r="9" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM8" s="14"/>
+    </row>
+    <row r="9" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
         <v>1007</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="12"/>
-      <c r="E9" s="9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="9">
+      <c r="F9" s="9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="9">
         <v>2</v>
       </c>
-      <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
       <c r="K9" s="14"/>
@@ -2443,27 +2460,27 @@
       <c r="AJ9" s="14"/>
       <c r="AK9" s="14"/>
       <c r="AL9" s="14"/>
-    </row>
-    <row r="10" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM9" s="14"/>
+    </row>
+    <row r="10" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
         <v>1008</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="9">
+      <c r="F10" s="9">
         <v>0</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="9">
+      <c r="G10" s="13"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="9">
         <v>-3</v>
       </c>
-      <c r="I10" s="14"/>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
       <c r="L10" s="14"/>
@@ -2493,27 +2510,27 @@
       <c r="AJ10" s="14"/>
       <c r="AK10" s="14"/>
       <c r="AL10" s="14"/>
-    </row>
-    <row r="11" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM10" s="14"/>
+    </row>
+    <row r="11" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
         <v>1009</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" s="12"/>
-      <c r="E11" s="9">
-        <v>1</v>
-      </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="9">
+      <c r="F11" s="9">
+        <v>1</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="9">
         <v>2</v>
       </c>
-      <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
@@ -2543,28 +2560,28 @@
       <c r="AJ11" s="14"/>
       <c r="AK11" s="14"/>
       <c r="AL11" s="14"/>
-    </row>
-    <row r="12" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM11" s="14"/>
+    </row>
+    <row r="12" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
         <v>1010</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="12"/>
-      <c r="E12" s="9">
+      <c r="F12" s="9">
         <v>2</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
+      <c r="G12" s="13"/>
       <c r="H12" s="14"/>
-      <c r="I12" s="9">
-        <v>1</v>
-      </c>
-      <c r="J12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="9">
+        <v>1</v>
+      </c>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
@@ -2585,37 +2602,37 @@
       <c r="AB12" s="14"/>
       <c r="AC12" s="14"/>
       <c r="AD12" s="14"/>
-      <c r="AE12" s="15" t="s">
+      <c r="AE12" s="14"/>
+      <c r="AF12" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH12" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF12" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG12" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH12" s="14"/>
       <c r="AI12" s="14"/>
       <c r="AJ12" s="14"/>
       <c r="AK12" s="14"/>
       <c r="AL12" s="14"/>
-    </row>
-    <row r="13" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM12" s="14"/>
+    </row>
+    <row r="13" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
         <v>1011</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="9">
+      <c r="F13" s="9">
         <v>0</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14"/>
+      <c r="G13" s="13"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -2647,23 +2664,23 @@
       <c r="AJ13" s="14"/>
       <c r="AK13" s="14"/>
       <c r="AL13" s="14"/>
-    </row>
-    <row r="14" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM13" s="14"/>
+    </row>
+    <row r="14" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
         <v>1012</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D14" s="12"/>
-      <c r="E14" s="9">
+      <c r="F14" s="9">
         <v>0</v>
       </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="14"/>
+      <c r="G14" s="13"/>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
@@ -2687,37 +2704,37 @@
       <c r="AB14" s="14"/>
       <c r="AC14" s="14"/>
       <c r="AD14" s="14"/>
-      <c r="AE14" s="15" t="s">
-        <v>61</v>
-      </c>
+      <c r="AE14" s="14"/>
       <c r="AF14" s="15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AG14" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH14" s="14"/>
+        <v>53</v>
+      </c>
+      <c r="AH14" s="15" t="s">
+        <v>54</v>
+      </c>
       <c r="AI14" s="14"/>
       <c r="AJ14" s="14"/>
       <c r="AK14" s="14"/>
       <c r="AL14" s="14"/>
-    </row>
-    <row r="15" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM14" s="14"/>
+    </row>
+    <row r="15" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
         <v>1013</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" s="12"/>
-      <c r="E15" s="9">
+      <c r="F15" s="9">
         <v>0</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
+      <c r="G15" s="13"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
@@ -2741,42 +2758,42 @@
       <c r="AB15" s="14"/>
       <c r="AC15" s="14"/>
       <c r="AD15" s="14"/>
-      <c r="AE15" s="15" t="s">
-        <v>61</v>
-      </c>
+      <c r="AE15" s="14"/>
       <c r="AF15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG15" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH15" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AG15" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH15" s="14"/>
       <c r="AI15" s="14"/>
       <c r="AJ15" s="14"/>
       <c r="AK15" s="14"/>
       <c r="AL15" s="14"/>
-    </row>
-    <row r="16" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM15" s="14"/>
+    </row>
+    <row r="16" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
         <v>1014</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D16" s="12"/>
-      <c r="E16" s="9">
+      <c r="F16" s="9">
         <v>2</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
+      <c r="G16" s="13"/>
       <c r="H16" s="14"/>
-      <c r="I16" s="9">
-        <v>1</v>
-      </c>
-      <c r="J16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="9">
+        <v>1</v>
+      </c>
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="14"/>
@@ -2797,37 +2814,37 @@
       <c r="AB16" s="14"/>
       <c r="AC16" s="14"/>
       <c r="AD16" s="14"/>
-      <c r="AE16" s="15" t="s">
-        <v>61</v>
-      </c>
+      <c r="AE16" s="14"/>
       <c r="AF16" s="15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AG16" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH16" s="14"/>
+        <v>52</v>
+      </c>
+      <c r="AH16" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="AI16" s="14"/>
       <c r="AJ16" s="14"/>
       <c r="AK16" s="14"/>
       <c r="AL16" s="14"/>
-    </row>
-    <row r="17" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM16" s="14"/>
+    </row>
+    <row r="17" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
         <v>1015</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D17" s="12"/>
-      <c r="E17" s="9">
-        <v>1</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
+      <c r="F17" s="9">
+        <v>1</v>
+      </c>
+      <c r="G17" s="13"/>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -2859,23 +2876,23 @@
       <c r="AJ17" s="14"/>
       <c r="AK17" s="14"/>
       <c r="AL17" s="14"/>
-    </row>
-    <row r="18" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM17" s="14"/>
+    </row>
+    <row r="18" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
         <v>1016</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D18" s="12"/>
-      <c r="E18" s="9">
+      <c r="F18" s="9">
         <v>0</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
+      <c r="G18" s="13"/>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
@@ -2907,23 +2924,23 @@
       <c r="AJ18" s="14"/>
       <c r="AK18" s="14"/>
       <c r="AL18" s="14"/>
-    </row>
-    <row r="19" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM18" s="14"/>
+    </row>
+    <row r="19" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
         <v>1017</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D19" s="12"/>
-      <c r="E19" s="9">
+      <c r="F19" s="9">
         <v>0</v>
       </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
@@ -2955,26 +2972,24 @@
       <c r="AJ19" s="14"/>
       <c r="AK19" s="14"/>
       <c r="AL19" s="14"/>
-    </row>
-    <row r="20" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM19" s="14"/>
+    </row>
+    <row r="20" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
         <v>1018</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D20" s="12"/>
-      <c r="E20" s="9">
+      <c r="F20" s="9">
         <v>2</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="9">
-        <v>1</v>
-      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14"/>
       <c r="I20" s="9">
         <v>1</v>
       </c>
@@ -2987,7 +3002,9 @@
       <c r="L20" s="9">
         <v>1</v>
       </c>
-      <c r="M20" s="14"/>
+      <c r="M20" s="9">
+        <v>1</v>
+      </c>
       <c r="N20" s="14"/>
       <c r="O20" s="14"/>
       <c r="P20" s="14"/>
@@ -3013,26 +3030,26 @@
       <c r="AJ20" s="14"/>
       <c r="AK20" s="14"/>
       <c r="AL20" s="14"/>
-    </row>
-    <row r="21" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM20" s="14"/>
+    </row>
+    <row r="21" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
         <v>1019</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D21" s="12"/>
-      <c r="E21" s="9">
+      <c r="F21" s="9">
         <v>2</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="9">
+      <c r="G21" s="13"/>
+      <c r="H21" s="9">
         <v>4</v>
       </c>
-      <c r="H21" s="14"/>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
       <c r="K21" s="14"/>
@@ -3063,29 +3080,29 @@
       <c r="AJ21" s="14"/>
       <c r="AK21" s="14"/>
       <c r="AL21" s="14"/>
-    </row>
-    <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM21" s="14"/>
+    </row>
+    <row r="22" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
         <v>1020</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22" s="12"/>
-      <c r="E22" s="9">
-        <v>1</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="14"/>
+      <c r="F22" s="9">
+        <v>1</v>
+      </c>
+      <c r="G22" s="13"/>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
-      <c r="J22" s="9">
+      <c r="J22" s="14"/>
+      <c r="K22" s="9">
         <v>2</v>
       </c>
-      <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
@@ -3113,32 +3130,32 @@
       <c r="AJ22" s="14"/>
       <c r="AK22" s="14"/>
       <c r="AL22" s="14"/>
-    </row>
-    <row r="23" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM22" s="14"/>
+    </row>
+    <row r="23" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
         <v>1021</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D23" s="12"/>
-      <c r="E23" s="9">
+      <c r="F23" s="9">
         <v>0</v>
       </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="14"/>
+      <c r="G23" s="13"/>
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
-      <c r="J23" s="9">
+      <c r="J23" s="14"/>
+      <c r="K23" s="9">
         <v>2</v>
       </c>
-      <c r="K23" s="9">
+      <c r="L23" s="9">
         <v>-2</v>
       </c>
-      <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
@@ -3165,23 +3182,23 @@
       <c r="AJ23" s="14"/>
       <c r="AK23" s="14"/>
       <c r="AL23" s="14"/>
-    </row>
-    <row r="24" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM23" s="14"/>
+    </row>
+    <row r="24" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
         <v>1022</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D24" s="12"/>
-      <c r="E24" s="9">
+      <c r="F24" s="9">
         <v>0</v>
       </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
+      <c r="G24" s="13"/>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
@@ -3213,26 +3230,24 @@
       <c r="AJ24" s="14"/>
       <c r="AK24" s="14"/>
       <c r="AL24" s="14"/>
-    </row>
-    <row r="25" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM24" s="14"/>
+    </row>
+    <row r="25" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
         <v>1023</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D25" s="12"/>
-      <c r="E25" s="9">
+      <c r="F25" s="9">
         <v>3</v>
       </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="9">
-        <v>2</v>
-      </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="14"/>
       <c r="I25" s="9">
         <v>2</v>
       </c>
@@ -3245,7 +3260,9 @@
       <c r="L25" s="9">
         <v>2</v>
       </c>
-      <c r="M25" s="14"/>
+      <c r="M25" s="9">
+        <v>2</v>
+      </c>
       <c r="N25" s="14"/>
       <c r="O25" s="14"/>
       <c r="P25" s="14"/>
@@ -3271,23 +3288,23 @@
       <c r="AJ25" s="14"/>
       <c r="AK25" s="14"/>
       <c r="AL25" s="14"/>
-    </row>
-    <row r="26" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM25" s="14"/>
+    </row>
+    <row r="26" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
         <v>1024</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D26" s="12"/>
-      <c r="E26" s="9">
+      <c r="F26" s="9">
         <v>2</v>
       </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="14"/>
+      <c r="G26" s="13"/>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
@@ -3311,37 +3328,37 @@
       <c r="AB26" s="14"/>
       <c r="AC26" s="14"/>
       <c r="AD26" s="14"/>
-      <c r="AE26" s="15" t="s">
-        <v>41</v>
-      </c>
+      <c r="AE26" s="14"/>
       <c r="AF26" s="15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AG26" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH26" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="AH26" s="15" t="s">
+        <v>35</v>
+      </c>
       <c r="AI26" s="14"/>
       <c r="AJ26" s="14"/>
       <c r="AK26" s="14"/>
       <c r="AL26" s="14"/>
-    </row>
-    <row r="27" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM26" s="14"/>
+    </row>
+    <row r="27" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
         <v>1025</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D27" s="12"/>
-      <c r="E27" s="9">
+      <c r="F27" s="9">
         <v>2</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="14"/>
+      <c r="G27" s="13"/>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
@@ -3365,39 +3382,39 @@
       <c r="AB27" s="14"/>
       <c r="AC27" s="14"/>
       <c r="AD27" s="14"/>
-      <c r="AE27" s="15" t="s">
-        <v>41</v>
-      </c>
+      <c r="AE27" s="14"/>
       <c r="AF27" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AG27" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AH27" s="9">
+      <c r="AH27" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI27" s="9">
         <v>1113</v>
       </c>
-      <c r="AI27" s="14"/>
       <c r="AJ27" s="14"/>
       <c r="AK27" s="14"/>
       <c r="AL27" s="14"/>
-    </row>
-    <row r="28" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM27" s="14"/>
+    </row>
+    <row r="28" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
         <v>1026</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="9">
+      <c r="F28" s="9">
         <v>0</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="14"/>
+      <c r="G28" s="13"/>
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
@@ -3421,33 +3438,33 @@
       <c r="AB28" s="14"/>
       <c r="AC28" s="14"/>
       <c r="AD28" s="14"/>
-      <c r="AE28" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF28" s="14"/>
+      <c r="AE28" s="14"/>
+      <c r="AF28" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="AG28" s="14"/>
       <c r="AH28" s="14"/>
       <c r="AI28" s="14"/>
       <c r="AJ28" s="14"/>
       <c r="AK28" s="14"/>
       <c r="AL28" s="14"/>
-    </row>
-    <row r="29" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM28" s="14"/>
+    </row>
+    <row r="29" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
         <v>1027</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D29" s="12"/>
-      <c r="E29" s="9">
-        <v>1</v>
-      </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="14"/>
+      <c r="F29" s="9">
+        <v>1</v>
+      </c>
+      <c r="G29" s="13"/>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
@@ -3471,33 +3488,33 @@
       <c r="AB29" s="14"/>
       <c r="AC29" s="14"/>
       <c r="AD29" s="14"/>
-      <c r="AE29" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF29" s="14"/>
+      <c r="AE29" s="14"/>
+      <c r="AF29" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="AG29" s="14"/>
       <c r="AH29" s="14"/>
       <c r="AI29" s="14"/>
       <c r="AJ29" s="14"/>
       <c r="AK29" s="14"/>
       <c r="AL29" s="14"/>
-    </row>
-    <row r="30" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM29" s="14"/>
+    </row>
+    <row r="30" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
         <v>1028</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D30" s="12"/>
-      <c r="E30" s="9">
+      <c r="F30" s="9">
         <v>0</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="14"/>
+      <c r="G30" s="13"/>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
@@ -3529,23 +3546,23 @@
       <c r="AJ30" s="14"/>
       <c r="AK30" s="14"/>
       <c r="AL30" s="14"/>
-    </row>
-    <row r="31" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM30" s="14"/>
+    </row>
+    <row r="31" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
         <v>1029</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D31" s="12"/>
-      <c r="E31" s="9">
-        <v>1</v>
-      </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="14"/>
+      <c r="F31" s="9">
+        <v>1</v>
+      </c>
+      <c r="G31" s="13"/>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
@@ -3577,23 +3594,23 @@
       <c r="AJ31" s="14"/>
       <c r="AK31" s="14"/>
       <c r="AL31" s="14"/>
-    </row>
-    <row r="32" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM31" s="14"/>
+    </row>
+    <row r="32" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
         <v>1030</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D32" s="12"/>
-      <c r="E32" s="9">
+      <c r="F32" s="9">
         <v>0</v>
       </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="14"/>
+      <c r="G32" s="13"/>
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
       <c r="J32" s="14"/>
@@ -3625,30 +3642,30 @@
       <c r="AJ32" s="14"/>
       <c r="AK32" s="14"/>
       <c r="AL32" s="14"/>
-    </row>
-    <row r="33" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM32" s="14"/>
+    </row>
+    <row r="33" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
         <v>1031</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D33" s="12"/>
-      <c r="E33" s="9">
+      <c r="F33" s="9">
         <v>0</v>
       </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14"/>
+      <c r="G33" s="13"/>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
-      <c r="K33" s="9">
+      <c r="K33" s="14"/>
+      <c r="L33" s="9">
         <v>-2</v>
       </c>
-      <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
@@ -3675,26 +3692,24 @@
       <c r="AJ33" s="14"/>
       <c r="AK33" s="14"/>
       <c r="AL33" s="14"/>
-    </row>
-    <row r="34" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM33" s="14"/>
+    </row>
+    <row r="34" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
         <v>1032</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D34" s="12"/>
-      <c r="E34" s="9">
+      <c r="F34" s="9">
         <v>0</v>
       </c>
-      <c r="F34" s="13"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="9">
-        <v>-1</v>
-      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
       <c r="I34" s="9">
         <v>-1</v>
       </c>
@@ -3707,7 +3722,9 @@
       <c r="L34" s="9">
         <v>-1</v>
       </c>
-      <c r="M34" s="14"/>
+      <c r="M34" s="9">
+        <v>-1</v>
+      </c>
       <c r="N34" s="14"/>
       <c r="O34" s="14"/>
       <c r="P34" s="14"/>
@@ -3733,30 +3750,30 @@
       <c r="AJ34" s="14"/>
       <c r="AK34" s="14"/>
       <c r="AL34" s="14"/>
-    </row>
-    <row r="35" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM34" s="14"/>
+    </row>
+    <row r="35" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
         <v>1033</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D35" s="12"/>
-      <c r="E35" s="9">
+      <c r="F35" s="9">
         <v>0</v>
       </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="14"/>
+      <c r="G35" s="13"/>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
-      <c r="K35" s="9">
+      <c r="K35" s="14"/>
+      <c r="L35" s="9">
         <v>-10</v>
       </c>
-      <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
@@ -3783,28 +3800,28 @@
       <c r="AJ35" s="14"/>
       <c r="AK35" s="14"/>
       <c r="AL35" s="14"/>
-    </row>
-    <row r="36" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM35" s="14"/>
+    </row>
+    <row r="36" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
         <v>1034</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D36" s="12"/>
-      <c r="E36" s="9">
+      <c r="F36" s="9">
         <v>0</v>
       </c>
-      <c r="F36" s="13"/>
-      <c r="G36" s="14"/>
+      <c r="G36" s="13"/>
       <c r="H36" s="14"/>
-      <c r="I36" s="9">
+      <c r="I36" s="14"/>
+      <c r="J36" s="9">
         <v>-2</v>
       </c>
-      <c r="J36" s="14"/>
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
@@ -3833,31 +3850,31 @@
       <c r="AJ36" s="14"/>
       <c r="AK36" s="14"/>
       <c r="AL36" s="14"/>
-    </row>
-    <row r="37" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM36" s="14"/>
+    </row>
+    <row r="37" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
         <v>1035</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D37" s="12"/>
-      <c r="E37" s="9">
+      <c r="F37" s="9">
         <v>0</v>
       </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="14"/>
+      <c r="G37" s="13"/>
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
       <c r="K37" s="14"/>
-      <c r="L37" s="9">
+      <c r="L37" s="14"/>
+      <c r="M37" s="9">
         <v>-2</v>
       </c>
-      <c r="M37" s="14"/>
       <c r="N37" s="14"/>
       <c r="O37" s="14"/>
       <c r="P37" s="14"/>
@@ -3883,31 +3900,31 @@
       <c r="AJ37" s="14"/>
       <c r="AK37" s="14"/>
       <c r="AL37" s="14"/>
-    </row>
-    <row r="38" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM37" s="14"/>
+    </row>
+    <row r="38" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
         <v>1036</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D38" s="12"/>
-      <c r="E38" s="9">
+      <c r="F38" s="9">
         <v>0</v>
       </c>
-      <c r="F38" s="13"/>
-      <c r="G38" s="14"/>
+      <c r="G38" s="13"/>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
       <c r="K38" s="14"/>
-      <c r="L38" s="9">
-        <v>1</v>
-      </c>
-      <c r="M38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="9">
+        <v>1</v>
+      </c>
       <c r="N38" s="14"/>
       <c r="O38" s="14"/>
       <c r="P38" s="14"/>
@@ -3933,23 +3950,23 @@
       <c r="AJ38" s="14"/>
       <c r="AK38" s="14"/>
       <c r="AL38" s="14"/>
-    </row>
-    <row r="39" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM38" s="14"/>
+    </row>
+    <row r="39" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
         <v>1037</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D39" s="12"/>
-      <c r="E39" s="9">
+      <c r="F39" s="9">
         <v>0</v>
       </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="14"/>
+      <c r="G39" s="13"/>
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
@@ -3981,23 +3998,23 @@
       <c r="AJ39" s="14"/>
       <c r="AK39" s="14"/>
       <c r="AL39" s="14"/>
-    </row>
-    <row r="40" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM39" s="14"/>
+    </row>
+    <row r="40" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
         <v>1038</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D40" s="12"/>
-      <c r="E40" s="9">
+      <c r="F40" s="9">
         <v>0</v>
       </c>
-      <c r="F40" s="13"/>
-      <c r="G40" s="14"/>
+      <c r="G40" s="13"/>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
@@ -4029,23 +4046,23 @@
       <c r="AJ40" s="14"/>
       <c r="AK40" s="14"/>
       <c r="AL40" s="14"/>
-    </row>
-    <row r="41" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM40" s="14"/>
+    </row>
+    <row r="41" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
         <v>1039</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D41" s="12"/>
-      <c r="E41" s="9">
-        <v>1</v>
-      </c>
-      <c r="F41" s="13"/>
-      <c r="G41" s="14"/>
+      <c r="F41" s="9">
+        <v>1</v>
+      </c>
+      <c r="G41" s="13"/>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
       <c r="J41" s="14"/>
@@ -4077,23 +4094,23 @@
       <c r="AJ41" s="14"/>
       <c r="AK41" s="14"/>
       <c r="AL41" s="14"/>
-    </row>
-    <row r="42" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM41" s="14"/>
+    </row>
+    <row r="42" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
         <v>1040</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D42" s="12"/>
-      <c r="E42" s="9">
+      <c r="F42" s="9">
         <v>0</v>
       </c>
-      <c r="F42" s="13"/>
-      <c r="G42" s="14"/>
+      <c r="G42" s="13"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="14"/>
@@ -4125,23 +4142,23 @@
       <c r="AJ42" s="14"/>
       <c r="AK42" s="14"/>
       <c r="AL42" s="14"/>
-    </row>
-    <row r="43" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM42" s="14"/>
+    </row>
+    <row r="43" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
         <v>1041</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D43" s="12"/>
-      <c r="E43" s="9">
-        <v>1</v>
-      </c>
-      <c r="F43" s="13"/>
-      <c r="G43" s="14"/>
+      <c r="F43" s="9">
+        <v>1</v>
+      </c>
+      <c r="G43" s="13"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
@@ -4165,33 +4182,33 @@
       <c r="AB43" s="14"/>
       <c r="AC43" s="14"/>
       <c r="AD43" s="14"/>
-      <c r="AE43" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF43" s="14"/>
+      <c r="AE43" s="14"/>
+      <c r="AF43" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="AG43" s="14"/>
       <c r="AH43" s="14"/>
       <c r="AI43" s="14"/>
       <c r="AJ43" s="14"/>
       <c r="AK43" s="14"/>
       <c r="AL43" s="14"/>
-    </row>
-    <row r="44" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM43" s="14"/>
+    </row>
+    <row r="44" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
         <v>1042</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D44" s="12"/>
-      <c r="E44" s="9">
+      <c r="F44" s="9">
         <v>0</v>
       </c>
-      <c r="F44" s="13"/>
-      <c r="G44" s="14"/>
+      <c r="G44" s="13"/>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
@@ -4223,23 +4240,23 @@
       <c r="AJ44" s="14"/>
       <c r="AK44" s="14"/>
       <c r="AL44" s="14"/>
-    </row>
-    <row r="45" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM44" s="14"/>
+    </row>
+    <row r="45" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
         <v>1043</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D45" s="12"/>
-      <c r="E45" s="9">
+      <c r="F45" s="9">
         <v>0</v>
       </c>
-      <c r="F45" s="13"/>
-      <c r="G45" s="14"/>
+      <c r="G45" s="13"/>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
@@ -4271,23 +4288,23 @@
       <c r="AJ45" s="14"/>
       <c r="AK45" s="14"/>
       <c r="AL45" s="14"/>
-    </row>
-    <row r="46" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM45" s="14"/>
+    </row>
+    <row r="46" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
         <v>1044</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D46" s="12"/>
-      <c r="E46" s="9">
+      <c r="F46" s="9">
         <v>0</v>
       </c>
-      <c r="F46" s="13"/>
-      <c r="G46" s="14"/>
+      <c r="G46" s="13"/>
       <c r="H46" s="14"/>
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
@@ -4319,23 +4336,23 @@
       <c r="AJ46" s="14"/>
       <c r="AK46" s="14"/>
       <c r="AL46" s="14"/>
-    </row>
-    <row r="47" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM46" s="14"/>
+    </row>
+    <row r="47" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="9">
         <v>1045</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D47" s="12"/>
-      <c r="E47" s="9">
+      <c r="F47" s="9">
         <v>0</v>
       </c>
-      <c r="F47" s="13"/>
-      <c r="G47" s="14"/>
+      <c r="G47" s="13"/>
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
@@ -4367,23 +4384,23 @@
       <c r="AJ47" s="14"/>
       <c r="AK47" s="14"/>
       <c r="AL47" s="14"/>
-    </row>
-    <row r="48" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM47" s="14"/>
+    </row>
+    <row r="48" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="9">
         <v>1046</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D48" s="12"/>
-      <c r="E48" s="9">
-        <v>1</v>
-      </c>
-      <c r="F48" s="13"/>
-      <c r="G48" s="14"/>
+      <c r="F48" s="9">
+        <v>1</v>
+      </c>
+      <c r="G48" s="13"/>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
       <c r="J48" s="14"/>
@@ -4407,33 +4424,33 @@
       <c r="AB48" s="14"/>
       <c r="AC48" s="14"/>
       <c r="AD48" s="14"/>
-      <c r="AE48" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF48" s="14"/>
+      <c r="AE48" s="14"/>
+      <c r="AF48" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="AG48" s="14"/>
       <c r="AH48" s="14"/>
       <c r="AI48" s="14"/>
       <c r="AJ48" s="14"/>
       <c r="AK48" s="14"/>
       <c r="AL48" s="14"/>
-    </row>
-    <row r="49" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM48" s="14"/>
+    </row>
+    <row r="49" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="9">
         <v>1047</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D49" s="12"/>
-      <c r="E49" s="9">
-        <v>1</v>
-      </c>
-      <c r="F49" s="13"/>
-      <c r="G49" s="14"/>
+      <c r="F49" s="9">
+        <v>1</v>
+      </c>
+      <c r="G49" s="13"/>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
       <c r="J49" s="14"/>
@@ -4465,23 +4482,23 @@
       <c r="AJ49" s="14"/>
       <c r="AK49" s="14"/>
       <c r="AL49" s="14"/>
-    </row>
-    <row r="50" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM49" s="14"/>
+    </row>
+    <row r="50" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="9">
         <v>1048</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D50" s="12"/>
-      <c r="E50" s="9">
+      <c r="F50" s="9">
         <v>3</v>
       </c>
-      <c r="F50" s="13"/>
-      <c r="G50" s="14"/>
+      <c r="G50" s="13"/>
       <c r="H50" s="14"/>
       <c r="I50" s="14"/>
       <c r="J50" s="14"/>
@@ -4513,30 +4530,31 @@
       <c r="AJ50" s="14"/>
       <c r="AK50" s="14"/>
       <c r="AL50" s="14"/>
-    </row>
-    <row r="51" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM50" s="14"/>
+    </row>
+    <row r="51" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="9">
         <v>1049</v>
       </c>
       <c r="B51" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" s="9">
+      <c r="E51" s="10"/>
+      <c r="F51" s="9">
         <v>0</v>
       </c>
-      <c r="F51" s="13"/>
-      <c r="G51" s="14"/>
+      <c r="G51" s="13"/>
       <c r="H51" s="14"/>
-      <c r="I51" s="9">
+      <c r="I51" s="14"/>
+      <c r="J51" s="9">
         <v>2</v>
       </c>
-      <c r="J51" s="14"/>
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
@@ -4565,33 +4583,34 @@
       <c r="AJ51" s="14"/>
       <c r="AK51" s="14"/>
       <c r="AL51" s="14"/>
-    </row>
-    <row r="52" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM51" s="14"/>
+    </row>
+    <row r="52" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="9">
         <v>1050</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="9">
+      <c r="E52" s="10"/>
+      <c r="F52" s="9">
         <v>0</v>
       </c>
-      <c r="F52" s="13"/>
-      <c r="G52" s="14"/>
+      <c r="G52" s="13"/>
       <c r="H52" s="14"/>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
       <c r="K52" s="14"/>
-      <c r="L52" s="9">
+      <c r="L52" s="14"/>
+      <c r="M52" s="9">
         <v>2</v>
       </c>
-      <c r="M52" s="14"/>
       <c r="N52" s="14"/>
       <c r="O52" s="14"/>
       <c r="P52" s="14"/>
@@ -4617,35 +4636,36 @@
       <c r="AJ52" s="14"/>
       <c r="AK52" s="14"/>
       <c r="AL52" s="14"/>
-    </row>
-    <row r="53" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM52" s="14"/>
+    </row>
+    <row r="53" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="9">
         <v>1051</v>
       </c>
       <c r="B53" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D53" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="C53" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" s="9">
+      <c r="E53" s="10"/>
+      <c r="F53" s="9">
         <v>0</v>
       </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="9">
-        <v>1</v>
-      </c>
-      <c r="I53" s="14"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="9">
+        <v>1</v>
+      </c>
       <c r="J53" s="14"/>
       <c r="K53" s="14"/>
-      <c r="L53" s="9">
-        <v>1</v>
-      </c>
-      <c r="M53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="9">
+        <v>1</v>
+      </c>
       <c r="N53" s="14"/>
       <c r="O53" s="14"/>
       <c r="P53" s="14"/>
@@ -4671,29 +4691,30 @@
       <c r="AJ53" s="14"/>
       <c r="AK53" s="14"/>
       <c r="AL53" s="14"/>
-    </row>
-    <row r="54" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM53" s="14"/>
+    </row>
+    <row r="54" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="9">
         <v>1052</v>
       </c>
       <c r="B54" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C54" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" s="9">
+      <c r="E54" s="10"/>
+      <c r="F54" s="9">
         <v>0</v>
       </c>
-      <c r="F54" s="13"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="9">
+      <c r="G54" s="13"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="9">
         <v>2</v>
       </c>
-      <c r="I54" s="14"/>
       <c r="J54" s="14"/>
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
@@ -4723,29 +4744,30 @@
       <c r="AJ54" s="14"/>
       <c r="AK54" s="14"/>
       <c r="AL54" s="14"/>
-    </row>
-    <row r="55" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM54" s="14"/>
+    </row>
+    <row r="55" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="9">
         <v>1053</v>
       </c>
       <c r="B55" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C55" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E55" s="9">
+      <c r="E55" s="10"/>
+      <c r="F55" s="9">
         <v>0</v>
       </c>
-      <c r="F55" s="13"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="9">
+      <c r="G55" s="13"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="9">
         <v>3</v>
       </c>
-      <c r="I55" s="14"/>
       <c r="J55" s="14"/>
       <c r="K55" s="14"/>
       <c r="L55" s="14"/>
@@ -4775,32 +4797,33 @@
       <c r="AJ55" s="14"/>
       <c r="AK55" s="14"/>
       <c r="AL55" s="14"/>
-    </row>
-    <row r="56" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM55" s="14"/>
+    </row>
+    <row r="56" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="9">
         <v>1054</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" s="9">
-        <v>1</v>
-      </c>
-      <c r="F56" s="13"/>
-      <c r="G56" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="E56" s="10"/>
+      <c r="F56" s="9">
+        <v>1</v>
+      </c>
+      <c r="G56" s="13"/>
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
-      <c r="K56" s="9">
+      <c r="K56" s="14"/>
+      <c r="L56" s="9">
         <v>2</v>
       </c>
-      <c r="L56" s="14"/>
       <c r="M56" s="14"/>
       <c r="N56" s="14"/>
       <c r="O56" s="14"/>
@@ -4827,31 +4850,32 @@
       <c r="AJ56" s="14"/>
       <c r="AK56" s="14"/>
       <c r="AL56" s="14"/>
-    </row>
-    <row r="57" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM56" s="14"/>
+    </row>
+    <row r="57" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="9">
         <v>1055</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E57" s="9">
+        <v>147</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="9">
         <v>0</v>
       </c>
-      <c r="F57" s="13"/>
-      <c r="G57" s="14"/>
+      <c r="G57" s="13"/>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
-      <c r="J57" s="9">
+      <c r="J57" s="14"/>
+      <c r="K57" s="9">
         <v>3</v>
       </c>
-      <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
       <c r="N57" s="14"/>
@@ -4879,33 +4903,34 @@
       <c r="AJ57" s="14"/>
       <c r="AK57" s="14"/>
       <c r="AL57" s="14"/>
-    </row>
-    <row r="58" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM57" s="14"/>
+    </row>
+    <row r="58" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="9">
         <v>1056</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C58" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" s="9">
-        <v>1</v>
-      </c>
-      <c r="F58" s="13"/>
-      <c r="G58" s="14"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="9">
+        <v>1</v>
+      </c>
+      <c r="G58" s="13"/>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
       <c r="K58" s="14"/>
-      <c r="L58" s="9">
+      <c r="L58" s="14"/>
+      <c r="M58" s="9">
         <v>2</v>
       </c>
-      <c r="M58" s="14"/>
       <c r="N58" s="14"/>
       <c r="O58" s="14"/>
       <c r="P58" s="14"/>
@@ -4931,31 +4956,32 @@
       <c r="AJ58" s="14"/>
       <c r="AK58" s="14"/>
       <c r="AL58" s="14"/>
-    </row>
-    <row r="59" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM58" s="14"/>
+    </row>
+    <row r="59" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="9">
         <v>1057</v>
       </c>
       <c r="B59" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D59" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E59" s="9">
-        <v>1</v>
-      </c>
-      <c r="F59" s="13"/>
-      <c r="G59" s="14"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="9">
+        <v>1</v>
+      </c>
+      <c r="G59" s="13"/>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
-      <c r="J59" s="9">
+      <c r="J59" s="14"/>
+      <c r="K59" s="9">
         <v>2</v>
       </c>
-      <c r="K59" s="14"/>
       <c r="L59" s="14"/>
       <c r="M59" s="14"/>
       <c r="N59" s="14"/>
@@ -4983,30 +5009,31 @@
       <c r="AJ59" s="14"/>
       <c r="AK59" s="14"/>
       <c r="AL59" s="14"/>
-    </row>
-    <row r="60" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM59" s="14"/>
+    </row>
+    <row r="60" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="9">
         <v>1058</v>
       </c>
       <c r="B60" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E60" s="9">
+      <c r="E60" s="10"/>
+      <c r="F60" s="9">
         <v>0</v>
       </c>
-      <c r="F60" s="13"/>
-      <c r="G60" s="14"/>
+      <c r="G60" s="13"/>
       <c r="H60" s="14"/>
-      <c r="I60" s="9">
+      <c r="I60" s="14"/>
+      <c r="J60" s="9">
         <v>4</v>
       </c>
-      <c r="J60" s="14"/>
       <c r="K60" s="14"/>
       <c r="L60" s="14"/>
       <c r="M60" s="14"/>
@@ -5035,30 +5062,31 @@
       <c r="AJ60" s="14"/>
       <c r="AK60" s="14"/>
       <c r="AL60" s="14"/>
-    </row>
-    <row r="61" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM60" s="14"/>
+    </row>
+    <row r="61" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="9">
         <v>1059</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E61" s="9">
+        <v>138</v>
+      </c>
+      <c r="E61" s="10"/>
+      <c r="F61" s="9">
         <v>0</v>
       </c>
-      <c r="F61" s="13"/>
-      <c r="G61" s="14"/>
+      <c r="G61" s="13"/>
       <c r="H61" s="14"/>
-      <c r="I61" s="9">
+      <c r="I61" s="14"/>
+      <c r="J61" s="9">
         <v>3</v>
       </c>
-      <c r="J61" s="14"/>
       <c r="K61" s="14"/>
       <c r="L61" s="14"/>
       <c r="M61" s="14"/>
@@ -5087,33 +5115,34 @@
       <c r="AJ61" s="14"/>
       <c r="AK61" s="14"/>
       <c r="AL61" s="14"/>
-    </row>
-    <row r="62" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM61" s="14"/>
+    </row>
+    <row r="62" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="9">
         <v>1060</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E62" s="9">
-        <v>1</v>
-      </c>
-      <c r="F62" s="13"/>
-      <c r="G62" s="14"/>
+        <v>157</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="9">
+        <v>1</v>
+      </c>
+      <c r="G62" s="13"/>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="14"/>
       <c r="K62" s="14"/>
-      <c r="L62" s="9">
+      <c r="L62" s="14"/>
+      <c r="M62" s="9">
         <v>2</v>
       </c>
-      <c r="M62" s="14"/>
       <c r="N62" s="14"/>
       <c r="O62" s="14"/>
       <c r="P62" s="14"/>
@@ -5139,31 +5168,32 @@
       <c r="AJ62" s="14"/>
       <c r="AK62" s="14"/>
       <c r="AL62" s="14"/>
-    </row>
-    <row r="63" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM62" s="14"/>
+    </row>
+    <row r="63" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="9">
         <v>1061</v>
       </c>
       <c r="B63" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D63" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C63" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E63" s="9">
-        <v>1</v>
-      </c>
-      <c r="F63" s="13"/>
-      <c r="G63" s="14"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="9">
+        <v>1</v>
+      </c>
+      <c r="G63" s="13"/>
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
-      <c r="J63" s="9">
+      <c r="J63" s="14"/>
+      <c r="K63" s="9">
         <v>2</v>
       </c>
-      <c r="K63" s="14"/>
       <c r="L63" s="14"/>
       <c r="M63" s="14"/>
       <c r="N63" s="14"/>
@@ -5191,29 +5221,30 @@
       <c r="AJ63" s="14"/>
       <c r="AK63" s="14"/>
       <c r="AL63" s="14"/>
-    </row>
-    <row r="64" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM63" s="14"/>
+    </row>
+    <row r="64" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="9">
         <v>1062</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E64" s="9">
+        <v>157</v>
+      </c>
+      <c r="E64" s="10"/>
+      <c r="F64" s="9">
         <v>0</v>
       </c>
-      <c r="F64" s="13"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="9">
-        <v>1</v>
-      </c>
-      <c r="I64" s="14"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="9">
+        <v>1</v>
+      </c>
       <c r="J64" s="14"/>
       <c r="K64" s="14"/>
       <c r="L64" s="14"/>
@@ -5243,26 +5274,26 @@
       <c r="AJ64" s="14"/>
       <c r="AK64" s="14"/>
       <c r="AL64" s="14"/>
-    </row>
-    <row r="65" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM64" s="14"/>
+    </row>
+    <row r="65" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="9">
         <v>1063</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D65" s="12"/>
-      <c r="E65" s="9">
+      <c r="F65" s="9">
         <v>0</v>
       </c>
-      <c r="F65" s="13"/>
-      <c r="G65" s="9">
-        <v>1</v>
-      </c>
-      <c r="H65" s="14"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="9">
+        <v>1</v>
+      </c>
       <c r="I65" s="14"/>
       <c r="J65" s="14"/>
       <c r="K65" s="14"/>
@@ -5293,26 +5324,26 @@
       <c r="AJ65" s="14"/>
       <c r="AK65" s="14"/>
       <c r="AL65" s="14"/>
-    </row>
-    <row r="66" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM65" s="14"/>
+    </row>
+    <row r="66" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="9">
         <v>1064</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D66" s="12"/>
-      <c r="E66" s="9">
+      <c r="F66" s="9">
         <v>3</v>
       </c>
-      <c r="F66" s="13"/>
-      <c r="G66" s="9">
+      <c r="G66" s="13"/>
+      <c r="H66" s="9">
         <v>8</v>
       </c>
-      <c r="H66" s="14"/>
       <c r="I66" s="14"/>
       <c r="J66" s="14"/>
       <c r="K66" s="14"/>
@@ -5343,23 +5374,23 @@
       <c r="AJ66" s="14"/>
       <c r="AK66" s="14"/>
       <c r="AL66" s="14"/>
-    </row>
-    <row r="67" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM66" s="14"/>
+    </row>
+    <row r="67" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="9">
         <v>1065</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D67" s="12"/>
-      <c r="E67" s="9">
-        <v>1</v>
-      </c>
-      <c r="F67" s="13"/>
-      <c r="G67" s="14"/>
+      <c r="F67" s="9">
+        <v>1</v>
+      </c>
+      <c r="G67" s="13"/>
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
@@ -5391,30 +5422,31 @@
       <c r="AJ67" s="14"/>
       <c r="AK67" s="14"/>
       <c r="AL67" s="14"/>
-    </row>
-    <row r="68" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM67" s="14"/>
+    </row>
+    <row r="68" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="9">
         <v>1066</v>
       </c>
       <c r="B68" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E68" s="9">
+      <c r="E68" s="10"/>
+      <c r="F68" s="9">
         <v>0</v>
       </c>
-      <c r="F68" s="13"/>
-      <c r="G68" s="14"/>
+      <c r="G68" s="13"/>
       <c r="H68" s="14"/>
-      <c r="I68" s="9">
-        <v>1</v>
-      </c>
-      <c r="J68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="9">
+        <v>1</v>
+      </c>
       <c r="K68" s="14"/>
       <c r="L68" s="14"/>
       <c r="M68" s="14"/>
@@ -5443,29 +5475,30 @@
       <c r="AJ68" s="14"/>
       <c r="AK68" s="14"/>
       <c r="AL68" s="14"/>
-    </row>
-    <row r="69" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM68" s="14"/>
+    </row>
+    <row r="69" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="9">
         <v>1067</v>
       </c>
       <c r="B69" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D69" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C69" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E69" s="9">
-        <v>1</v>
-      </c>
-      <c r="F69" s="13"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="9">
-        <v>1</v>
-      </c>
-      <c r="I69" s="14"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="9">
+        <v>1</v>
+      </c>
+      <c r="G69" s="13"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="9">
+        <v>1</v>
+      </c>
       <c r="J69" s="14"/>
       <c r="K69" s="14"/>
       <c r="L69" s="14"/>
@@ -5495,32 +5528,33 @@
       <c r="AJ69" s="14"/>
       <c r="AK69" s="14"/>
       <c r="AL69" s="14"/>
-    </row>
-    <row r="70" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM69" s="14"/>
+    </row>
+    <row r="70" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="9">
         <v>1068</v>
       </c>
       <c r="B70" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D70" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E70" s="9">
+      <c r="E70" s="10"/>
+      <c r="F70" s="9">
         <v>0</v>
       </c>
-      <c r="F70" s="13"/>
-      <c r="G70" s="14"/>
+      <c r="G70" s="13"/>
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
-      <c r="K70" s="9">
-        <v>1</v>
-      </c>
-      <c r="L70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="9">
+        <v>1</v>
+      </c>
       <c r="M70" s="14"/>
       <c r="N70" s="14"/>
       <c r="O70" s="14"/>
@@ -5547,30 +5581,31 @@
       <c r="AJ70" s="14"/>
       <c r="AK70" s="14"/>
       <c r="AL70" s="14"/>
-    </row>
-    <row r="71" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM70" s="14"/>
+    </row>
+    <row r="71" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="9">
         <v>1069</v>
       </c>
       <c r="B71" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D71" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C71" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="E71" s="9">
+      <c r="E71" s="16"/>
+      <c r="F71" s="9">
         <v>0</v>
       </c>
-      <c r="F71" s="13"/>
-      <c r="G71" s="14"/>
+      <c r="G71" s="13"/>
       <c r="H71" s="14"/>
-      <c r="I71" s="9">
+      <c r="I71" s="14"/>
+      <c r="J71" s="9">
         <v>2</v>
       </c>
-      <c r="J71" s="14"/>
       <c r="K71" s="14"/>
       <c r="L71" s="14"/>
       <c r="M71" s="14"/>
@@ -5599,29 +5634,30 @@
       <c r="AJ71" s="14"/>
       <c r="AK71" s="14"/>
       <c r="AL71" s="14"/>
-    </row>
-    <row r="72" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM71" s="14"/>
+    </row>
+    <row r="72" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="9">
         <v>1070</v>
       </c>
       <c r="B72" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E72" s="9">
+      <c r="E72" s="16"/>
+      <c r="F72" s="9">
         <v>0</v>
       </c>
-      <c r="F72" s="13"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="9">
+      <c r="G72" s="13"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="9">
         <v>2</v>
       </c>
-      <c r="I72" s="14"/>
       <c r="J72" s="14"/>
       <c r="K72" s="14"/>
       <c r="L72" s="14"/>
@@ -5651,23 +5687,23 @@
       <c r="AJ72" s="14"/>
       <c r="AK72" s="14"/>
       <c r="AL72" s="14"/>
-    </row>
-    <row r="73" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM72" s="14"/>
+    </row>
+    <row r="73" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="9">
         <v>1071</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D73" s="12"/>
-      <c r="E73" s="9">
+      <c r="F73" s="9">
         <v>0</v>
       </c>
-      <c r="F73" s="13"/>
-      <c r="G73" s="14"/>
+      <c r="G73" s="13"/>
       <c r="H73" s="14"/>
       <c r="I73" s="14"/>
       <c r="J73" s="14"/>
@@ -5699,23 +5735,23 @@
       <c r="AJ73" s="14"/>
       <c r="AK73" s="14"/>
       <c r="AL73" s="14"/>
-    </row>
-    <row r="74" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM73" s="14"/>
+    </row>
+    <row r="74" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="9">
         <v>1072</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D74" s="12"/>
-      <c r="E74" s="9">
+      <c r="F74" s="9">
         <v>0</v>
       </c>
-      <c r="F74" s="13"/>
-      <c r="G74" s="14"/>
+      <c r="G74" s="13"/>
       <c r="H74" s="14"/>
       <c r="I74" s="14"/>
       <c r="J74" s="14"/>
@@ -5747,23 +5783,23 @@
       <c r="AJ74" s="14"/>
       <c r="AK74" s="14"/>
       <c r="AL74" s="14"/>
-    </row>
-    <row r="75" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM74" s="14"/>
+    </row>
+    <row r="75" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="9">
         <v>1073</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D75" s="12"/>
-      <c r="E75" s="9">
+      <c r="F75" s="9">
         <v>0</v>
       </c>
-      <c r="F75" s="13"/>
-      <c r="G75" s="14"/>
+      <c r="G75" s="13"/>
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
       <c r="J75" s="14"/>
@@ -5795,29 +5831,30 @@
       <c r="AJ75" s="14"/>
       <c r="AK75" s="14"/>
       <c r="AL75" s="14"/>
-    </row>
-    <row r="76" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM75" s="14"/>
+    </row>
+    <row r="76" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="9">
         <v>1074</v>
       </c>
       <c r="B76" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D76" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C76" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="E76" s="9">
-        <v>1</v>
-      </c>
-      <c r="F76" s="13"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="9">
+      <c r="E76" s="10"/>
+      <c r="F76" s="9">
+        <v>1</v>
+      </c>
+      <c r="G76" s="13"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="9">
         <v>3</v>
       </c>
-      <c r="I76" s="14"/>
       <c r="J76" s="14"/>
       <c r="K76" s="14"/>
       <c r="L76" s="14"/>
@@ -5847,31 +5884,32 @@
       <c r="AJ76" s="14"/>
       <c r="AK76" s="14"/>
       <c r="AL76" s="14"/>
-    </row>
-    <row r="77" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM76" s="14"/>
+    </row>
+    <row r="77" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="9">
         <v>1075</v>
       </c>
       <c r="B77" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D77" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C77" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E77" s="9">
+      <c r="E77" s="10"/>
+      <c r="F77" s="9">
         <v>0</v>
       </c>
-      <c r="F77" s="13"/>
-      <c r="G77" s="14"/>
+      <c r="G77" s="13"/>
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
-      <c r="J77" s="9">
+      <c r="J77" s="14"/>
+      <c r="K77" s="9">
         <v>3</v>
       </c>
-      <c r="K77" s="14"/>
       <c r="L77" s="14"/>
       <c r="M77" s="14"/>
       <c r="N77" s="14"/>
@@ -5899,29 +5937,30 @@
       <c r="AJ77" s="14"/>
       <c r="AK77" s="14"/>
       <c r="AL77" s="14"/>
-    </row>
-    <row r="78" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM77" s="14"/>
+    </row>
+    <row r="78" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="9">
         <v>1076</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E78" s="9">
-        <v>1</v>
-      </c>
-      <c r="F78" s="13"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="9">
+        <v>202</v>
+      </c>
+      <c r="E78" s="10"/>
+      <c r="F78" s="9">
+        <v>1</v>
+      </c>
+      <c r="G78" s="13"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="9">
         <v>3</v>
       </c>
-      <c r="I78" s="14"/>
       <c r="J78" s="14"/>
       <c r="K78" s="14"/>
       <c r="L78" s="14"/>
@@ -5951,29 +5990,30 @@
       <c r="AJ78" s="14"/>
       <c r="AK78" s="14"/>
       <c r="AL78" s="14"/>
-    </row>
-    <row r="79" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM78" s="14"/>
+    </row>
+    <row r="79" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="9">
         <v>1077</v>
       </c>
       <c r="B79" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C79" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="E79" s="9">
-        <v>1</v>
-      </c>
-      <c r="F79" s="13"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="9">
+      <c r="E79" s="10"/>
+      <c r="F79" s="9">
+        <v>1</v>
+      </c>
+      <c r="G79" s="13"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="9">
         <v>3</v>
       </c>
-      <c r="I79" s="14"/>
       <c r="J79" s="14"/>
       <c r="K79" s="14"/>
       <c r="L79" s="14"/>
@@ -6003,32 +6043,33 @@
       <c r="AJ79" s="14"/>
       <c r="AK79" s="14"/>
       <c r="AL79" s="14"/>
-    </row>
-    <row r="80" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM79" s="14"/>
+    </row>
+    <row r="80" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="9">
         <v>1078</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="E80" s="9">
+        <v>199</v>
+      </c>
+      <c r="E80" s="10"/>
+      <c r="F80" s="9">
         <v>0</v>
       </c>
-      <c r="F80" s="13"/>
-      <c r="G80" s="14"/>
+      <c r="G80" s="13"/>
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
       <c r="J80" s="14"/>
-      <c r="K80" s="9">
+      <c r="K80" s="14"/>
+      <c r="L80" s="9">
         <v>3</v>
       </c>
-      <c r="L80" s="14"/>
       <c r="M80" s="14"/>
       <c r="N80" s="14"/>
       <c r="O80" s="14"/>
@@ -6055,31 +6096,32 @@
       <c r="AJ80" s="14"/>
       <c r="AK80" s="14"/>
       <c r="AL80" s="14"/>
-    </row>
-    <row r="81" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM80" s="14"/>
+    </row>
+    <row r="81" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="9">
         <v>1079</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="E81" s="9">
+        <v>199</v>
+      </c>
+      <c r="E81" s="10"/>
+      <c r="F81" s="9">
         <v>0</v>
       </c>
-      <c r="F81" s="13"/>
-      <c r="G81" s="14"/>
+      <c r="G81" s="13"/>
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
-      <c r="J81" s="9">
+      <c r="J81" s="14"/>
+      <c r="K81" s="9">
         <v>3</v>
       </c>
-      <c r="K81" s="14"/>
       <c r="L81" s="14"/>
       <c r="M81" s="14"/>
       <c r="N81" s="14"/>
@@ -6107,30 +6149,31 @@
       <c r="AJ81" s="14"/>
       <c r="AK81" s="14"/>
       <c r="AL81" s="14"/>
-    </row>
-    <row r="82" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM81" s="14"/>
+    </row>
+    <row r="82" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="9">
         <v>1080</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="E82" s="9">
+        <v>199</v>
+      </c>
+      <c r="E82" s="10"/>
+      <c r="F82" s="9">
         <v>0</v>
       </c>
-      <c r="F82" s="13"/>
-      <c r="G82" s="14"/>
+      <c r="G82" s="13"/>
       <c r="H82" s="14"/>
-      <c r="I82" s="9">
+      <c r="I82" s="14"/>
+      <c r="J82" s="9">
         <v>3</v>
       </c>
-      <c r="J82" s="14"/>
       <c r="K82" s="14"/>
       <c r="L82" s="14"/>
       <c r="M82" s="14"/>
@@ -6159,29 +6202,28 @@
       <c r="AJ82" s="14"/>
       <c r="AK82" s="14"/>
       <c r="AL82" s="14"/>
-    </row>
-    <row r="83" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM82" s="14"/>
+    </row>
+    <row r="83" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="9">
         <v>1081</v>
       </c>
       <c r="B83" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="D83" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C83" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="E83" s="9">
+      <c r="E83" s="10"/>
+      <c r="F83" s="9">
         <v>0</v>
       </c>
-      <c r="F83" s="13"/>
-      <c r="G83" s="14"/>
+      <c r="G83" s="13"/>
       <c r="H83" s="14"/>
-      <c r="I83" s="9">
-        <v>1</v>
-      </c>
+      <c r="I83" s="14"/>
       <c r="J83" s="9">
         <v>1</v>
       </c>
@@ -6191,7 +6233,9 @@
       <c r="L83" s="9">
         <v>1</v>
       </c>
-      <c r="M83" s="14"/>
+      <c r="M83" s="9">
+        <v>1</v>
+      </c>
       <c r="N83" s="14"/>
       <c r="O83" s="14"/>
       <c r="P83" s="14"/>
@@ -6217,29 +6261,28 @@
       <c r="AJ83" s="14"/>
       <c r="AK83" s="14"/>
       <c r="AL83" s="14"/>
-    </row>
-    <row r="84" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM83" s="14"/>
+    </row>
+    <row r="84" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="9">
         <v>1082</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="E84" s="9">
-        <v>1</v>
-      </c>
-      <c r="F84" s="13"/>
-      <c r="G84" s="14"/>
+        <v>216</v>
+      </c>
+      <c r="E84" s="10"/>
+      <c r="F84" s="9">
+        <v>1</v>
+      </c>
+      <c r="G84" s="13"/>
       <c r="H84" s="14"/>
-      <c r="I84" s="9">
-        <v>2</v>
-      </c>
+      <c r="I84" s="14"/>
       <c r="J84" s="9">
         <v>2</v>
       </c>
@@ -6249,7 +6292,9 @@
       <c r="L84" s="9">
         <v>2</v>
       </c>
-      <c r="M84" s="14"/>
+      <c r="M84" s="9">
+        <v>2</v>
+      </c>
       <c r="N84" s="14"/>
       <c r="O84" s="14"/>
       <c r="P84" s="14"/>
@@ -6275,29 +6320,28 @@
       <c r="AJ84" s="14"/>
       <c r="AK84" s="14"/>
       <c r="AL84" s="14"/>
-    </row>
-    <row r="85" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM84" s="14"/>
+    </row>
+    <row r="85" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="9">
         <v>1083</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="E85" s="9">
+        <v>216</v>
+      </c>
+      <c r="E85" s="10"/>
+      <c r="F85" s="9">
         <v>2</v>
       </c>
-      <c r="F85" s="13"/>
-      <c r="G85" s="14"/>
+      <c r="G85" s="13"/>
       <c r="H85" s="14"/>
-      <c r="I85" s="9">
-        <v>3</v>
-      </c>
+      <c r="I85" s="14"/>
       <c r="J85" s="9">
         <v>3</v>
       </c>
@@ -6307,7 +6351,9 @@
       <c r="L85" s="9">
         <v>3</v>
       </c>
-      <c r="M85" s="14"/>
+      <c r="M85" s="9">
+        <v>3</v>
+      </c>
       <c r="N85" s="14"/>
       <c r="O85" s="14"/>
       <c r="P85" s="14"/>
@@ -6333,29 +6379,29 @@
       <c r="AJ85" s="14"/>
       <c r="AK85" s="14"/>
       <c r="AL85" s="14"/>
-    </row>
-    <row r="86" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM85" s="14"/>
+    </row>
+    <row r="86" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="9">
         <v>1084</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D86" s="12"/>
-      <c r="E86" s="9">
+      <c r="F86" s="9">
         <v>0</v>
       </c>
-      <c r="F86" s="13"/>
-      <c r="G86" s="9">
+      <c r="G86" s="13"/>
+      <c r="H86" s="9">
         <v>-2</v>
       </c>
-      <c r="H86" s="9">
+      <c r="I86" s="9">
         <v>2</v>
       </c>
-      <c r="I86" s="14"/>
       <c r="J86" s="14"/>
       <c r="K86" s="14"/>
       <c r="L86" s="14"/>
@@ -6377,39 +6423,39 @@
       <c r="AB86" s="14"/>
       <c r="AC86" s="14"/>
       <c r="AD86" s="14"/>
-      <c r="AE86" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="AF86" s="14"/>
+      <c r="AE86" s="14"/>
+      <c r="AF86" s="15" t="s">
+        <v>223</v>
+      </c>
       <c r="AG86" s="14"/>
       <c r="AH86" s="14"/>
       <c r="AI86" s="14"/>
       <c r="AJ86" s="14"/>
       <c r="AK86" s="14"/>
       <c r="AL86" s="14"/>
-    </row>
-    <row r="87" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM86" s="14"/>
+    </row>
+    <row r="87" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="9">
         <v>1085</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D87" s="12"/>
-      <c r="E87" s="9">
-        <v>1</v>
-      </c>
-      <c r="F87" s="13"/>
-      <c r="G87" s="9">
+      <c r="F87" s="9">
+        <v>1</v>
+      </c>
+      <c r="G87" s="13"/>
+      <c r="H87" s="9">
         <v>-3</v>
       </c>
-      <c r="H87" s="9">
+      <c r="I87" s="9">
         <v>5</v>
       </c>
-      <c r="I87" s="14"/>
       <c r="J87" s="14"/>
       <c r="K87" s="14"/>
       <c r="L87" s="14"/>
@@ -6431,36 +6477,36 @@
       <c r="AB87" s="14"/>
       <c r="AC87" s="14"/>
       <c r="AD87" s="14"/>
-      <c r="AE87" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="AF87" s="14"/>
+      <c r="AE87" s="14"/>
+      <c r="AF87" s="15" t="s">
+        <v>223</v>
+      </c>
       <c r="AG87" s="14"/>
       <c r="AH87" s="14"/>
       <c r="AI87" s="14"/>
       <c r="AJ87" s="14"/>
       <c r="AK87" s="14"/>
       <c r="AL87" s="14"/>
-    </row>
-    <row r="88" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM87" s="14"/>
+    </row>
+    <row r="88" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="9">
         <v>1086</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D88" s="12"/>
-      <c r="E88" s="9">
+      <c r="F88" s="9">
         <v>0</v>
       </c>
-      <c r="F88" s="13"/>
-      <c r="G88" s="9">
+      <c r="G88" s="13"/>
+      <c r="H88" s="9">
         <v>-10</v>
       </c>
-      <c r="H88" s="14"/>
       <c r="I88" s="14"/>
       <c r="J88" s="14"/>
       <c r="K88" s="14"/>
@@ -6483,39 +6529,40 @@
       <c r="AB88" s="14"/>
       <c r="AC88" s="14"/>
       <c r="AD88" s="14"/>
-      <c r="AE88" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="AF88" s="14"/>
+      <c r="AE88" s="14"/>
+      <c r="AF88" s="15" t="s">
+        <v>223</v>
+      </c>
       <c r="AG88" s="14"/>
       <c r="AH88" s="14"/>
       <c r="AI88" s="14"/>
       <c r="AJ88" s="14"/>
       <c r="AK88" s="14"/>
       <c r="AL88" s="14"/>
-    </row>
-    <row r="89" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM88" s="14"/>
+    </row>
+    <row r="89" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="9">
         <v>1087</v>
       </c>
       <c r="B89" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D89" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="C89" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="E89" s="9">
-        <v>1</v>
-      </c>
-      <c r="F89" s="13"/>
-      <c r="G89" s="14"/>
-      <c r="H89" s="9">
+      <c r="E89" s="10"/>
+      <c r="F89" s="9">
+        <v>1</v>
+      </c>
+      <c r="G89" s="13"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="9">
         <v>3</v>
       </c>
-      <c r="I89" s="14"/>
       <c r="J89" s="14"/>
       <c r="K89" s="14"/>
       <c r="L89" s="14"/>
@@ -6545,31 +6592,32 @@
       <c r="AJ89" s="14"/>
       <c r="AK89" s="14"/>
       <c r="AL89" s="14"/>
-    </row>
-    <row r="90" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM89" s="14"/>
+    </row>
+    <row r="90" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="9">
         <v>1088</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="E90" s="9">
+        <v>230</v>
+      </c>
+      <c r="E90" s="10"/>
+      <c r="F90" s="9">
         <v>0</v>
       </c>
-      <c r="F90" s="13"/>
-      <c r="G90" s="14"/>
+      <c r="G90" s="13"/>
       <c r="H90" s="14"/>
       <c r="I90" s="14"/>
-      <c r="J90" s="9">
+      <c r="J90" s="14"/>
+      <c r="K90" s="9">
         <v>3</v>
       </c>
-      <c r="K90" s="14"/>
       <c r="L90" s="14"/>
       <c r="M90" s="14"/>
       <c r="N90" s="14"/>
@@ -6597,32 +6645,33 @@
       <c r="AJ90" s="14"/>
       <c r="AK90" s="14"/>
       <c r="AL90" s="14"/>
-    </row>
-    <row r="91" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM90" s="14"/>
+    </row>
+    <row r="91" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="9">
         <v>1089</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="E91" s="9">
+        <v>230</v>
+      </c>
+      <c r="E91" s="10"/>
+      <c r="F91" s="9">
         <v>0</v>
       </c>
-      <c r="F91" s="13"/>
-      <c r="G91" s="14"/>
+      <c r="G91" s="13"/>
       <c r="H91" s="14"/>
       <c r="I91" s="14"/>
       <c r="J91" s="14"/>
-      <c r="K91" s="9">
+      <c r="K91" s="14"/>
+      <c r="L91" s="9">
         <v>3</v>
       </c>
-      <c r="L91" s="14"/>
       <c r="M91" s="14"/>
       <c r="N91" s="14"/>
       <c r="O91" s="14"/>
@@ -6649,39 +6698,40 @@
       <c r="AJ91" s="14"/>
       <c r="AK91" s="14"/>
       <c r="AL91" s="14"/>
-    </row>
-    <row r="92" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM91" s="14"/>
+    </row>
+    <row r="92" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="9">
         <v>1090</v>
       </c>
       <c r="B92" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D92" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="C92" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="E92" s="9">
+      <c r="E92" s="10"/>
+      <c r="F92" s="9">
         <v>0</v>
       </c>
-      <c r="F92" s="13"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="9">
-        <v>1</v>
-      </c>
+      <c r="G92" s="13"/>
+      <c r="H92" s="14"/>
       <c r="I92" s="9">
         <v>1</v>
       </c>
       <c r="J92" s="9">
         <v>1</v>
       </c>
-      <c r="K92" s="14"/>
-      <c r="L92" s="9">
-        <v>1</v>
-      </c>
-      <c r="M92" s="14"/>
+      <c r="K92" s="9">
+        <v>1</v>
+      </c>
+      <c r="L92" s="14"/>
+      <c r="M92" s="9">
+        <v>1</v>
+      </c>
       <c r="N92" s="14"/>
       <c r="O92" s="14"/>
       <c r="P92" s="14"/>
@@ -6707,39 +6757,40 @@
       <c r="AJ92" s="14"/>
       <c r="AK92" s="14"/>
       <c r="AL92" s="14"/>
-    </row>
-    <row r="93" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM92" s="14"/>
+    </row>
+    <row r="93" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="9">
         <v>1091</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="E93" s="9">
-        <v>1</v>
-      </c>
-      <c r="F93" s="13"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="9">
-        <v>2</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="E93" s="10"/>
+      <c r="F93" s="9">
+        <v>1</v>
+      </c>
+      <c r="G93" s="13"/>
+      <c r="H93" s="14"/>
       <c r="I93" s="9">
         <v>2</v>
       </c>
       <c r="J93" s="9">
         <v>2</v>
       </c>
-      <c r="K93" s="14"/>
-      <c r="L93" s="9">
+      <c r="K93" s="9">
         <v>2</v>
       </c>
-      <c r="M93" s="14"/>
+      <c r="L93" s="14"/>
+      <c r="M93" s="9">
+        <v>2</v>
+      </c>
       <c r="N93" s="14"/>
       <c r="O93" s="14"/>
       <c r="P93" s="14"/>
@@ -6765,39 +6816,40 @@
       <c r="AJ93" s="14"/>
       <c r="AK93" s="14"/>
       <c r="AL93" s="14"/>
-    </row>
-    <row r="94" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM93" s="14"/>
+    </row>
+    <row r="94" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="9">
         <v>1092</v>
       </c>
       <c r="B94" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D94" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="C94" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="E94" s="9">
+      <c r="E94" s="10"/>
+      <c r="F94" s="9">
         <v>0</v>
       </c>
-      <c r="F94" s="13"/>
-      <c r="G94" s="14"/>
-      <c r="H94" s="9">
-        <v>1</v>
-      </c>
+      <c r="G94" s="13"/>
+      <c r="H94" s="14"/>
       <c r="I94" s="9">
         <v>1</v>
       </c>
-      <c r="J94" s="14"/>
-      <c r="K94" s="9">
-        <v>1</v>
-      </c>
+      <c r="J94" s="9">
+        <v>1</v>
+      </c>
+      <c r="K94" s="14"/>
       <c r="L94" s="9">
         <v>1</v>
       </c>
-      <c r="M94" s="14"/>
+      <c r="M94" s="9">
+        <v>1</v>
+      </c>
       <c r="N94" s="14"/>
       <c r="O94" s="14"/>
       <c r="P94" s="14"/>
@@ -6823,33 +6875,33 @@
       <c r="AJ94" s="14"/>
       <c r="AK94" s="14"/>
       <c r="AL94" s="14"/>
-    </row>
-    <row r="95" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM94" s="14"/>
+    </row>
+    <row r="95" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="9">
         <v>1093</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D95" s="12"/>
-      <c r="E95" s="9">
+      <c r="F95" s="9">
         <v>0</v>
       </c>
-      <c r="F95" s="13"/>
-      <c r="G95" s="14"/>
+      <c r="G95" s="13"/>
       <c r="H95" s="14"/>
       <c r="I95" s="14"/>
-      <c r="J95" s="9">
+      <c r="J95" s="14"/>
+      <c r="K95" s="9">
         <v>-2</v>
       </c>
-      <c r="K95" s="14"/>
-      <c r="L95" s="9">
+      <c r="L95" s="14"/>
+      <c r="M95" s="9">
         <v>2</v>
       </c>
-      <c r="M95" s="14"/>
       <c r="N95" s="14"/>
       <c r="O95" s="14"/>
       <c r="P95" s="14"/>
@@ -6875,29 +6927,29 @@
       <c r="AJ95" s="14"/>
       <c r="AK95" s="14"/>
       <c r="AL95" s="14"/>
-    </row>
-    <row r="96" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM95" s="14"/>
+    </row>
+    <row r="96" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="9">
         <v>1094</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D96" s="12"/>
-      <c r="E96" s="9">
+      <c r="F96" s="9">
         <v>0</v>
       </c>
-      <c r="F96" s="13"/>
-      <c r="G96" s="14"/>
+      <c r="G96" s="13"/>
       <c r="H96" s="14"/>
       <c r="I96" s="14"/>
-      <c r="J96" s="9">
+      <c r="J96" s="14"/>
+      <c r="K96" s="9">
         <v>-1</v>
       </c>
-      <c r="K96" s="14"/>
       <c r="L96" s="14"/>
       <c r="M96" s="14"/>
       <c r="N96" s="14"/>
@@ -6925,39 +6977,40 @@
       <c r="AJ96" s="14"/>
       <c r="AK96" s="14"/>
       <c r="AL96" s="14"/>
-    </row>
-    <row r="97" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM96" s="14"/>
+    </row>
+    <row r="97" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="9">
         <v>1095</v>
       </c>
       <c r="B97" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D97" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C97" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="E97" s="9">
+      <c r="E97" s="10"/>
+      <c r="F97" s="9">
         <v>0</v>
       </c>
-      <c r="F97" s="13"/>
-      <c r="G97" s="14"/>
-      <c r="H97" s="9">
-        <v>1</v>
-      </c>
-      <c r="I97" s="14"/>
-      <c r="J97" s="9">
-        <v>1</v>
-      </c>
+      <c r="G97" s="13"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="9">
+        <v>1</v>
+      </c>
+      <c r="J97" s="14"/>
       <c r="K97" s="9">
         <v>1</v>
       </c>
       <c r="L97" s="9">
         <v>1</v>
       </c>
-      <c r="M97" s="14"/>
+      <c r="M97" s="9">
+        <v>1</v>
+      </c>
       <c r="N97" s="14"/>
       <c r="O97" s="14"/>
       <c r="P97" s="14"/>
@@ -6983,29 +7036,28 @@
       <c r="AJ97" s="14"/>
       <c r="AK97" s="14"/>
       <c r="AL97" s="14"/>
-    </row>
-    <row r="98" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM97" s="14"/>
+    </row>
+    <row r="98" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="9">
         <v>1096</v>
       </c>
       <c r="B98" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D98" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="C98" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="E98" s="9">
+      <c r="E98" s="10"/>
+      <c r="F98" s="9">
         <v>0</v>
       </c>
-      <c r="F98" s="13"/>
-      <c r="G98" s="14"/>
+      <c r="G98" s="13"/>
       <c r="H98" s="14"/>
-      <c r="I98" s="9">
-        <v>1</v>
-      </c>
+      <c r="I98" s="14"/>
       <c r="J98" s="9">
         <v>1</v>
       </c>
@@ -7015,7 +7067,9 @@
       <c r="L98" s="9">
         <v>1</v>
       </c>
-      <c r="M98" s="14"/>
+      <c r="M98" s="9">
+        <v>1</v>
+      </c>
       <c r="N98" s="14"/>
       <c r="O98" s="14"/>
       <c r="P98" s="14"/>
@@ -7041,29 +7095,28 @@
       <c r="AJ98" s="14"/>
       <c r="AK98" s="14"/>
       <c r="AL98" s="14"/>
-    </row>
-    <row r="99" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM98" s="14"/>
+    </row>
+    <row r="99" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="9">
         <v>1097</v>
       </c>
       <c r="B99" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D99" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="C99" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="E99" s="9">
-        <v>1</v>
-      </c>
-      <c r="F99" s="13"/>
-      <c r="G99" s="14"/>
+      <c r="E99" s="10"/>
+      <c r="F99" s="9">
+        <v>1</v>
+      </c>
+      <c r="G99" s="13"/>
       <c r="H99" s="14"/>
-      <c r="I99" s="9">
-        <v>2</v>
-      </c>
+      <c r="I99" s="14"/>
       <c r="J99" s="9">
         <v>2</v>
       </c>
@@ -7073,7 +7126,9 @@
       <c r="L99" s="9">
         <v>2</v>
       </c>
-      <c r="M99" s="14"/>
+      <c r="M99" s="9">
+        <v>2</v>
+      </c>
       <c r="N99" s="14"/>
       <c r="O99" s="14"/>
       <c r="P99" s="14"/>
@@ -7099,39 +7154,40 @@
       <c r="AJ99" s="14"/>
       <c r="AK99" s="14"/>
       <c r="AL99" s="14"/>
-    </row>
-    <row r="100" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM99" s="14"/>
+    </row>
+    <row r="100" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="9">
         <v>1098</v>
       </c>
       <c r="B100" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D100" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="C100" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="E100" s="9">
-        <v>1</v>
-      </c>
-      <c r="F100" s="13"/>
-      <c r="G100" s="14"/>
-      <c r="H100" s="9">
+      <c r="E100" s="10"/>
+      <c r="F100" s="9">
+        <v>1</v>
+      </c>
+      <c r="G100" s="13"/>
+      <c r="H100" s="14"/>
+      <c r="I100" s="9">
         <v>2</v>
       </c>
-      <c r="I100" s="14"/>
-      <c r="J100" s="9">
-        <v>2</v>
-      </c>
+      <c r="J100" s="14"/>
       <c r="K100" s="9">
         <v>2</v>
       </c>
       <c r="L100" s="9">
         <v>2</v>
       </c>
-      <c r="M100" s="14"/>
+      <c r="M100" s="9">
+        <v>2</v>
+      </c>
       <c r="N100" s="14"/>
       <c r="O100" s="14"/>
       <c r="P100" s="14"/>
@@ -7157,30 +7213,30 @@
       <c r="AJ100" s="14"/>
       <c r="AK100" s="14"/>
       <c r="AL100" s="14"/>
-    </row>
-    <row r="101" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM100" s="14"/>
+    </row>
+    <row r="101" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="9">
         <v>1099</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D101" s="12"/>
-      <c r="E101" s="9">
+      <c r="F101" s="9">
         <v>0</v>
       </c>
-      <c r="F101" s="13"/>
-      <c r="G101" s="14"/>
-      <c r="H101" s="9">
+      <c r="G101" s="13"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="9">
         <v>2</v>
       </c>
-      <c r="I101" s="9">
+      <c r="J101" s="9">
         <v>-2</v>
       </c>
-      <c r="J101" s="14"/>
       <c r="K101" s="14"/>
       <c r="L101" s="14"/>
       <c r="M101" s="14"/>
@@ -7209,31 +7265,31 @@
       <c r="AJ101" s="14"/>
       <c r="AK101" s="14"/>
       <c r="AL101" s="14"/>
-    </row>
-    <row r="102" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM101" s="14"/>
+    </row>
+    <row r="102" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="9">
         <v>1100</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D102" s="12"/>
-      <c r="E102" s="9">
+      <c r="F102" s="9">
         <v>0</v>
       </c>
-      <c r="F102" s="13"/>
-      <c r="G102" s="9">
-        <v>1</v>
-      </c>
-      <c r="H102" s="14"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="9">
+        <v>1</v>
+      </c>
       <c r="I102" s="14"/>
-      <c r="J102" s="9">
+      <c r="J102" s="14"/>
+      <c r="K102" s="9">
         <v>-2</v>
       </c>
-      <c r="K102" s="14"/>
       <c r="L102" s="14"/>
       <c r="M102" s="14"/>
       <c r="N102" s="14"/>
@@ -7261,28 +7317,27 @@
       <c r="AJ102" s="14"/>
       <c r="AK102" s="14"/>
       <c r="AL102" s="14"/>
-    </row>
-    <row r="103" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM102" s="14"/>
+    </row>
+    <row r="103" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="9">
         <v>1101</v>
       </c>
       <c r="B103" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="D103" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="C103" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D103" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="E103" s="9">
+      <c r="E103" s="17"/>
+      <c r="F103" s="9">
         <v>0</v>
       </c>
-      <c r="F103" s="13"/>
-      <c r="G103" s="14"/>
-      <c r="H103" s="9">
-        <v>1</v>
-      </c>
+      <c r="G103" s="13"/>
+      <c r="H103" s="14"/>
       <c r="I103" s="9">
         <v>1</v>
       </c>
@@ -7295,7 +7350,9 @@
       <c r="L103" s="9">
         <v>1</v>
       </c>
-      <c r="M103" s="14"/>
+      <c r="M103" s="9">
+        <v>1</v>
+      </c>
       <c r="N103" s="14"/>
       <c r="O103" s="14"/>
       <c r="P103" s="14"/>
@@ -7321,28 +7378,27 @@
       <c r="AJ103" s="14"/>
       <c r="AK103" s="14"/>
       <c r="AL103" s="14"/>
-    </row>
-    <row r="104" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM103" s="14"/>
+    </row>
+    <row r="104" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="9">
         <v>1102</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="E104" s="9">
-        <v>1</v>
-      </c>
-      <c r="F104" s="13"/>
-      <c r="G104" s="14"/>
-      <c r="H104" s="9">
-        <v>2</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="E104" s="17"/>
+      <c r="F104" s="9">
+        <v>1</v>
+      </c>
+      <c r="G104" s="13"/>
+      <c r="H104" s="14"/>
       <c r="I104" s="9">
         <v>2</v>
       </c>
@@ -7355,7 +7411,9 @@
       <c r="L104" s="9">
         <v>2</v>
       </c>
-      <c r="M104" s="14"/>
+      <c r="M104" s="9">
+        <v>2</v>
+      </c>
       <c r="N104" s="14"/>
       <c r="O104" s="14"/>
       <c r="P104" s="14"/>
@@ -7381,25 +7439,26 @@
       <c r="AJ104" s="14"/>
       <c r="AK104" s="14"/>
       <c r="AL104" s="14"/>
-    </row>
-    <row r="105" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM104" s="14"/>
+    </row>
+    <row r="105" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="9">
         <v>1103</v>
       </c>
       <c r="B105" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D105" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C105" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="E105" s="9">
+      <c r="E105" s="10"/>
+      <c r="F105" s="9">
         <v>0</v>
       </c>
-      <c r="F105" s="13"/>
-      <c r="G105" s="14"/>
+      <c r="G105" s="13"/>
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
       <c r="J105" s="14"/>
@@ -7431,25 +7490,26 @@
       <c r="AJ105" s="14"/>
       <c r="AK105" s="14"/>
       <c r="AL105" s="14"/>
-    </row>
-    <row r="106" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM105" s="14"/>
+    </row>
+    <row r="106" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="9">
         <v>1104</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E106" s="9">
+        <v>138</v>
+      </c>
+      <c r="E106" s="10"/>
+      <c r="F106" s="9">
         <v>2</v>
       </c>
-      <c r="F106" s="13"/>
-      <c r="G106" s="14"/>
+      <c r="G106" s="13"/>
       <c r="H106" s="14"/>
       <c r="I106" s="14"/>
       <c r="J106" s="14"/>
@@ -7481,25 +7541,28 @@
       <c r="AJ106" s="14"/>
       <c r="AK106" s="14"/>
       <c r="AL106" s="14"/>
-    </row>
-    <row r="107" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM106" s="14"/>
+    </row>
+    <row r="107" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="9">
         <v>1105</v>
       </c>
       <c r="B107" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D107" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C107" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="D107" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="E107" s="9">
-        <v>1</v>
-      </c>
-      <c r="F107" s="13"/>
-      <c r="G107" s="14"/>
+      <c r="E107" s="10">
+        <v>2</v>
+      </c>
+      <c r="F107" s="9">
+        <v>1</v>
+      </c>
+      <c r="G107" s="13"/>
       <c r="H107" s="14"/>
       <c r="I107" s="14"/>
       <c r="J107" s="14"/>
@@ -7531,23 +7594,23 @@
       <c r="AJ107" s="14"/>
       <c r="AK107" s="14"/>
       <c r="AL107" s="14"/>
-    </row>
-    <row r="108" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM107" s="14"/>
+    </row>
+    <row r="108" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="9">
         <v>1106</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D108" s="12"/>
-      <c r="E108" s="9">
+      <c r="F108" s="9">
         <v>0</v>
       </c>
-      <c r="F108" s="13"/>
-      <c r="G108" s="14"/>
+      <c r="G108" s="13"/>
       <c r="H108" s="14"/>
       <c r="I108" s="14"/>
       <c r="J108" s="14"/>
@@ -7579,23 +7642,23 @@
       <c r="AJ108" s="14"/>
       <c r="AK108" s="14"/>
       <c r="AL108" s="14"/>
-    </row>
-    <row r="109" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM108" s="14"/>
+    </row>
+    <row r="109" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="9">
         <v>1107</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D109" s="12"/>
-      <c r="E109" s="9">
+      <c r="F109" s="9">
         <v>0</v>
       </c>
-      <c r="F109" s="13"/>
-      <c r="G109" s="14"/>
+      <c r="G109" s="13"/>
       <c r="H109" s="14"/>
       <c r="I109" s="14"/>
       <c r="J109" s="14"/>
@@ -7627,23 +7690,23 @@
       <c r="AJ109" s="14"/>
       <c r="AK109" s="14"/>
       <c r="AL109" s="14"/>
-    </row>
-    <row r="110" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM109" s="14"/>
+    </row>
+    <row r="110" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="9">
         <v>1108</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D110" s="12"/>
-      <c r="E110" s="9">
+      <c r="F110" s="9">
         <v>0</v>
       </c>
-      <c r="F110" s="13"/>
-      <c r="G110" s="14"/>
+      <c r="G110" s="13"/>
       <c r="H110" s="14"/>
       <c r="I110" s="14"/>
       <c r="J110" s="14"/>
@@ -7675,23 +7738,23 @@
       <c r="AJ110" s="14"/>
       <c r="AK110" s="14"/>
       <c r="AL110" s="14"/>
-    </row>
-    <row r="111" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM110" s="14"/>
+    </row>
+    <row r="111" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="9">
         <v>1109</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D111" s="12"/>
-      <c r="E111" s="9">
+      <c r="F111" s="9">
         <v>0</v>
       </c>
-      <c r="F111" s="13"/>
-      <c r="G111" s="14"/>
+      <c r="G111" s="13"/>
       <c r="H111" s="14"/>
       <c r="I111" s="14"/>
       <c r="J111" s="14"/>
@@ -7723,23 +7786,23 @@
       <c r="AJ111" s="14"/>
       <c r="AK111" s="14"/>
       <c r="AL111" s="14"/>
-    </row>
-    <row r="112" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM111" s="14"/>
+    </row>
+    <row r="112" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="9">
         <v>1110</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D112" s="12"/>
-      <c r="E112" s="9">
+      <c r="F112" s="9">
         <v>0</v>
       </c>
-      <c r="F112" s="13"/>
-      <c r="G112" s="14"/>
+      <c r="G112" s="13"/>
       <c r="H112" s="14"/>
       <c r="I112" s="14"/>
       <c r="J112" s="14"/>
@@ -7771,23 +7834,23 @@
       <c r="AJ112" s="14"/>
       <c r="AK112" s="14"/>
       <c r="AL112" s="14"/>
-    </row>
-    <row r="113" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM112" s="14"/>
+    </row>
+    <row r="113" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="9">
         <v>1111</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D113" s="12"/>
-      <c r="E113" s="9">
+      <c r="F113" s="9">
         <v>0</v>
       </c>
-      <c r="F113" s="13"/>
-      <c r="G113" s="14"/>
+      <c r="G113" s="13"/>
       <c r="H113" s="14"/>
       <c r="I113" s="14"/>
       <c r="J113" s="14"/>
@@ -7819,23 +7882,23 @@
       <c r="AJ113" s="14"/>
       <c r="AK113" s="14"/>
       <c r="AL113" s="14"/>
-    </row>
-    <row r="114" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM113" s="14"/>
+    </row>
+    <row r="114" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="9">
         <v>1112</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D114" s="12"/>
-      <c r="E114" s="9">
+      <c r="F114" s="9">
         <v>2</v>
       </c>
-      <c r="F114" s="13"/>
-      <c r="G114" s="14"/>
+      <c r="G114" s="13"/>
       <c r="H114" s="14"/>
       <c r="I114" s="14"/>
       <c r="J114" s="14"/>
@@ -7867,23 +7930,23 @@
       <c r="AJ114" s="14"/>
       <c r="AK114" s="14"/>
       <c r="AL114" s="14"/>
-    </row>
-    <row r="115" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM114" s="14"/>
+    </row>
+    <row r="115" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="9">
         <v>1113</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D115" s="12"/>
-      <c r="E115" s="9">
-        <v>1</v>
-      </c>
-      <c r="F115" s="13"/>
-      <c r="G115" s="14"/>
+      <c r="F115" s="9">
+        <v>1</v>
+      </c>
+      <c r="G115" s="13"/>
       <c r="H115" s="14"/>
       <c r="I115" s="14"/>
       <c r="J115" s="14"/>
@@ -7907,45 +7970,46 @@
       <c r="AB115" s="14"/>
       <c r="AC115" s="14"/>
       <c r="AD115" s="14"/>
-      <c r="AE115" s="15" t="s">
-        <v>41</v>
-      </c>
+      <c r="AE115" s="14"/>
       <c r="AF115" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG115" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="AH115" s="9">
+        <v>35</v>
+      </c>
+      <c r="AH115" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="AI115" s="9">
         <v>1027</v>
       </c>
-      <c r="AI115" s="9">
+      <c r="AJ115" s="9">
         <v>1041</v>
       </c>
-      <c r="AJ115" s="9">
+      <c r="AK115" s="9">
         <v>1046</v>
       </c>
-      <c r="AK115" s="14"/>
       <c r="AL115" s="14"/>
-    </row>
-    <row r="116" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM115" s="14"/>
+    </row>
+    <row r="116" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="9">
         <v>1114</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E116" s="9">
+        <v>144</v>
+      </c>
+      <c r="E116" s="10"/>
+      <c r="F116" s="9">
         <v>3</v>
       </c>
-      <c r="F116" s="13"/>
-      <c r="G116" s="14"/>
+      <c r="G116" s="13"/>
       <c r="H116" s="14"/>
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
@@ -7977,23 +8041,23 @@
       <c r="AJ116" s="14"/>
       <c r="AK116" s="14"/>
       <c r="AL116" s="14"/>
-    </row>
-    <row r="117" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM116" s="14"/>
+    </row>
+    <row r="117" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="9">
         <v>1115</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D117" s="12"/>
-      <c r="E117" s="9">
+      <c r="F117" s="9">
         <v>0</v>
       </c>
-      <c r="F117" s="13"/>
-      <c r="G117" s="14"/>
+      <c r="G117" s="13"/>
       <c r="H117" s="14"/>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
@@ -8025,23 +8089,23 @@
       <c r="AJ117" s="14"/>
       <c r="AK117" s="14"/>
       <c r="AL117" s="14"/>
-    </row>
-    <row r="118" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM117" s="14"/>
+    </row>
+    <row r="118" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="9">
         <v>1116</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D118" s="12"/>
-      <c r="E118" s="9">
+      <c r="F118" s="9">
         <v>0</v>
       </c>
-      <c r="F118" s="13"/>
-      <c r="G118" s="14"/>
+      <c r="G118" s="13"/>
       <c r="H118" s="14"/>
       <c r="I118" s="14"/>
       <c r="J118" s="14"/>
@@ -8073,23 +8137,23 @@
       <c r="AJ118" s="14"/>
       <c r="AK118" s="14"/>
       <c r="AL118" s="14"/>
-    </row>
-    <row r="119" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM118" s="14"/>
+    </row>
+    <row r="119" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="9">
         <v>1117</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D119" s="12"/>
-      <c r="E119" s="9">
+      <c r="F119" s="9">
         <v>0</v>
       </c>
-      <c r="F119" s="13"/>
-      <c r="G119" s="14"/>
+      <c r="G119" s="13"/>
       <c r="H119" s="14"/>
       <c r="I119" s="14"/>
       <c r="J119" s="14"/>
@@ -8121,23 +8185,23 @@
       <c r="AJ119" s="14"/>
       <c r="AK119" s="14"/>
       <c r="AL119" s="14"/>
-    </row>
-    <row r="120" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM119" s="14"/>
+    </row>
+    <row r="120" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="9">
         <v>1118</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D120" s="12"/>
-      <c r="E120" s="9">
+      <c r="F120" s="9">
         <v>0</v>
       </c>
-      <c r="F120" s="13"/>
-      <c r="G120" s="14"/>
+      <c r="G120" s="13"/>
       <c r="H120" s="14"/>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
@@ -8169,23 +8233,23 @@
       <c r="AJ120" s="14"/>
       <c r="AK120" s="14"/>
       <c r="AL120" s="14"/>
-    </row>
-    <row r="121" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM120" s="14"/>
+    </row>
+    <row r="121" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="9">
         <v>1119</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D121" s="12"/>
-      <c r="E121" s="9">
+      <c r="F121" s="9">
         <v>0</v>
       </c>
-      <c r="F121" s="13"/>
-      <c r="G121" s="14"/>
+      <c r="G121" s="13"/>
       <c r="H121" s="14"/>
       <c r="I121" s="14"/>
       <c r="J121" s="14"/>
@@ -8217,23 +8281,23 @@
       <c r="AJ121" s="14"/>
       <c r="AK121" s="14"/>
       <c r="AL121" s="14"/>
-    </row>
-    <row r="122" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM121" s="14"/>
+    </row>
+    <row r="122" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="9">
         <v>1120</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D122" s="12"/>
-      <c r="E122" s="9">
+      <c r="F122" s="9">
         <v>0</v>
       </c>
-      <c r="F122" s="13"/>
-      <c r="G122" s="14"/>
+      <c r="G122" s="13"/>
       <c r="H122" s="14"/>
       <c r="I122" s="14"/>
       <c r="J122" s="14"/>
@@ -8265,23 +8329,23 @@
       <c r="AJ122" s="14"/>
       <c r="AK122" s="14"/>
       <c r="AL122" s="14"/>
-    </row>
-    <row r="123" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM122" s="14"/>
+    </row>
+    <row r="123" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="9">
         <v>1121</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D123" s="12"/>
-      <c r="E123" s="9">
+      <c r="F123" s="9">
         <v>0</v>
       </c>
-      <c r="F123" s="13"/>
-      <c r="G123" s="14"/>
+      <c r="G123" s="13"/>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
@@ -8313,26 +8377,26 @@
       <c r="AJ123" s="14"/>
       <c r="AK123" s="14"/>
       <c r="AL123" s="14"/>
-    </row>
-    <row r="124" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM123" s="14"/>
+    </row>
+    <row r="124" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="9">
         <v>1122</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D124" s="12"/>
-      <c r="E124" s="9">
-        <v>1</v>
-      </c>
-      <c r="F124" s="13"/>
-      <c r="G124" s="9">
+      <c r="F124" s="9">
+        <v>1</v>
+      </c>
+      <c r="G124" s="13"/>
+      <c r="H124" s="9">
         <v>-20</v>
       </c>
-      <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
       <c r="K124" s="14"/>
@@ -8355,37 +8419,37 @@
       <c r="AB124" s="14"/>
       <c r="AC124" s="14"/>
       <c r="AD124" s="14"/>
-      <c r="AE124" s="15" t="s">
+      <c r="AE124" s="14"/>
+      <c r="AF124" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="AG124" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="AH124" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="AF124" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="AG124" s="15" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH124" s="14"/>
       <c r="AI124" s="14"/>
       <c r="AJ124" s="14"/>
       <c r="AK124" s="14"/>
       <c r="AL124" s="14"/>
-    </row>
-    <row r="125" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM124" s="14"/>
+    </row>
+    <row r="125" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="9">
         <v>1123</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D125" s="12"/>
-      <c r="E125" s="9">
+      <c r="F125" s="9">
         <v>0</v>
       </c>
-      <c r="F125" s="13"/>
-      <c r="G125" s="14"/>
+      <c r="G125" s="13"/>
       <c r="H125" s="14"/>
       <c r="I125" s="14"/>
       <c r="J125" s="14"/>
@@ -8417,23 +8481,23 @@
       <c r="AJ125" s="14"/>
       <c r="AK125" s="14"/>
       <c r="AL125" s="14"/>
-    </row>
-    <row r="126" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM125" s="14"/>
+    </row>
+    <row r="126" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="9">
         <v>1124</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D126" s="12"/>
-      <c r="E126" s="9">
+      <c r="F126" s="9">
         <v>0</v>
       </c>
-      <c r="F126" s="13"/>
-      <c r="G126" s="14"/>
+      <c r="G126" s="13"/>
       <c r="H126" s="14"/>
       <c r="I126" s="14"/>
       <c r="J126" s="14"/>
@@ -8465,23 +8529,23 @@
       <c r="AJ126" s="14"/>
       <c r="AK126" s="14"/>
       <c r="AL126" s="14"/>
-    </row>
-    <row r="127" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM126" s="14"/>
+    </row>
+    <row r="127" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="9">
         <v>1125</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D127" s="12"/>
-      <c r="E127" s="9">
+      <c r="F127" s="9">
         <v>0</v>
       </c>
-      <c r="F127" s="13"/>
-      <c r="G127" s="14"/>
+      <c r="G127" s="13"/>
       <c r="H127" s="14"/>
       <c r="I127" s="14"/>
       <c r="J127" s="14"/>
@@ -8513,23 +8577,23 @@
       <c r="AJ127" s="14"/>
       <c r="AK127" s="14"/>
       <c r="AL127" s="14"/>
-    </row>
-    <row r="128" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM127" s="14"/>
+    </row>
+    <row r="128" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="9">
         <v>1126</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D128" s="12"/>
-      <c r="E128" s="9">
+      <c r="F128" s="9">
         <v>0</v>
       </c>
-      <c r="F128" s="13"/>
-      <c r="G128" s="14"/>
+      <c r="G128" s="13"/>
       <c r="H128" s="14"/>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
@@ -8561,23 +8625,23 @@
       <c r="AJ128" s="14"/>
       <c r="AK128" s="14"/>
       <c r="AL128" s="14"/>
-    </row>
-    <row r="129" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM128" s="14"/>
+    </row>
+    <row r="129" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="9">
         <v>1127</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D129" s="12"/>
-      <c r="E129" s="9">
+      <c r="F129" s="9">
         <v>0</v>
       </c>
-      <c r="F129" s="13"/>
-      <c r="G129" s="14"/>
+      <c r="G129" s="13"/>
       <c r="H129" s="14"/>
       <c r="I129" s="14"/>
       <c r="J129" s="14"/>
@@ -8609,23 +8673,23 @@
       <c r="AJ129" s="14"/>
       <c r="AK129" s="14"/>
       <c r="AL129" s="14"/>
-    </row>
-    <row r="130" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM129" s="14"/>
+    </row>
+    <row r="130" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="9">
         <v>1128</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D130" s="12"/>
-      <c r="E130" s="9">
+      <c r="F130" s="9">
         <v>2</v>
       </c>
-      <c r="F130" s="13"/>
-      <c r="G130" s="14"/>
+      <c r="G130" s="13"/>
       <c r="H130" s="14"/>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
@@ -8657,23 +8721,23 @@
       <c r="AJ130" s="14"/>
       <c r="AK130" s="14"/>
       <c r="AL130" s="14"/>
-    </row>
-    <row r="131" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM130" s="14"/>
+    </row>
+    <row r="131" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="9">
         <v>1129</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D131" s="12"/>
-      <c r="E131" s="9">
-        <v>1</v>
-      </c>
-      <c r="F131" s="13"/>
-      <c r="G131" s="14"/>
+      <c r="F131" s="9">
+        <v>1</v>
+      </c>
+      <c r="G131" s="13"/>
       <c r="H131" s="14"/>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
@@ -8705,23 +8769,23 @@
       <c r="AJ131" s="14"/>
       <c r="AK131" s="14"/>
       <c r="AL131" s="14"/>
-    </row>
-    <row r="132" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM131" s="14"/>
+    </row>
+    <row r="132" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="9">
         <v>1130</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D132" s="12"/>
-      <c r="E132" s="9">
+      <c r="F132" s="9">
         <v>0</v>
       </c>
-      <c r="F132" s="13"/>
-      <c r="G132" s="14"/>
+      <c r="G132" s="13"/>
       <c r="H132" s="14"/>
       <c r="I132" s="14"/>
       <c r="J132" s="14"/>
@@ -8753,23 +8817,23 @@
       <c r="AJ132" s="14"/>
       <c r="AK132" s="14"/>
       <c r="AL132" s="14"/>
-    </row>
-    <row r="133" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM132" s="14"/>
+    </row>
+    <row r="133" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A133" s="9">
         <v>1131</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D133" s="12"/>
-      <c r="E133" s="9">
+      <c r="F133" s="9">
         <v>2</v>
       </c>
-      <c r="F133" s="13"/>
-      <c r="G133" s="14"/>
+      <c r="G133" s="13"/>
       <c r="H133" s="14"/>
       <c r="I133" s="14"/>
       <c r="J133" s="14"/>
@@ -8801,23 +8865,23 @@
       <c r="AJ133" s="14"/>
       <c r="AK133" s="14"/>
       <c r="AL133" s="14"/>
-    </row>
-    <row r="134" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM133" s="14"/>
+    </row>
+    <row r="134" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="9">
         <v>1132</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D134" s="12"/>
-      <c r="E134" s="9">
-        <v>1</v>
-      </c>
-      <c r="F134" s="13"/>
-      <c r="G134" s="14"/>
+      <c r="F134" s="9">
+        <v>1</v>
+      </c>
+      <c r="G134" s="13"/>
       <c r="H134" s="14"/>
       <c r="I134" s="14"/>
       <c r="J134" s="14"/>
@@ -8849,23 +8913,23 @@
       <c r="AJ134" s="14"/>
       <c r="AK134" s="14"/>
       <c r="AL134" s="14"/>
-    </row>
-    <row r="135" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM134" s="14"/>
+    </row>
+    <row r="135" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="9">
         <v>1133</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D135" s="12"/>
-      <c r="E135" s="9">
+      <c r="F135" s="9">
         <v>0</v>
       </c>
-      <c r="F135" s="13"/>
-      <c r="G135" s="14"/>
+      <c r="G135" s="13"/>
       <c r="H135" s="14"/>
       <c r="I135" s="14"/>
       <c r="J135" s="14"/>
@@ -8897,23 +8961,23 @@
       <c r="AJ135" s="14"/>
       <c r="AK135" s="14"/>
       <c r="AL135" s="14"/>
-    </row>
-    <row r="136" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM135" s="14"/>
+    </row>
+    <row r="136" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A136" s="9">
         <v>1134</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D136" s="12"/>
-      <c r="E136" s="9">
+      <c r="F136" s="9">
         <v>2</v>
       </c>
-      <c r="F136" s="13"/>
-      <c r="G136" s="14"/>
+      <c r="G136" s="13"/>
       <c r="H136" s="14"/>
       <c r="I136" s="14"/>
       <c r="J136" s="14"/>
@@ -8945,23 +9009,23 @@
       <c r="AJ136" s="14"/>
       <c r="AK136" s="14"/>
       <c r="AL136" s="14"/>
-    </row>
-    <row r="137" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM136" s="14"/>
+    </row>
+    <row r="137" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="9">
         <v>1135</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D137" s="12"/>
-      <c r="E137" s="9">
+      <c r="F137" s="9">
         <v>3</v>
       </c>
-      <c r="F137" s="13"/>
-      <c r="G137" s="14"/>
+      <c r="G137" s="13"/>
       <c r="H137" s="14"/>
       <c r="I137" s="14"/>
       <c r="J137" s="14"/>
@@ -8993,31 +9057,31 @@
       <c r="AJ137" s="14"/>
       <c r="AK137" s="14"/>
       <c r="AL137" s="14"/>
-    </row>
-    <row r="138" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM137" s="14"/>
+    </row>
+    <row r="138" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="9">
         <v>1136</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D138" s="12"/>
-      <c r="E138" s="9">
+      <c r="F138" s="9">
         <v>0</v>
       </c>
-      <c r="F138" s="13"/>
-      <c r="G138" s="14"/>
+      <c r="G138" s="13"/>
       <c r="H138" s="14"/>
       <c r="I138" s="14"/>
       <c r="J138" s="14"/>
       <c r="K138" s="14"/>
-      <c r="L138" s="9">
+      <c r="L138" s="14"/>
+      <c r="M138" s="9">
         <v>-5</v>
       </c>
-      <c r="M138" s="14"/>
       <c r="N138" s="14"/>
       <c r="O138" s="14"/>
       <c r="P138" s="14"/>
@@ -9043,28 +9107,27 @@
       <c r="AJ138" s="14"/>
       <c r="AK138" s="14"/>
       <c r="AL138" s="14"/>
-    </row>
-    <row r="139" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM138" s="14"/>
+    </row>
+    <row r="139" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="9">
         <v>1137</v>
       </c>
       <c r="B139" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="D139" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="C139" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="E139" s="9">
-        <v>1</v>
-      </c>
-      <c r="F139" s="13"/>
-      <c r="G139" s="14"/>
-      <c r="H139" s="9">
-        <v>2</v>
-      </c>
+      <c r="E139" s="10"/>
+      <c r="F139" s="9">
+        <v>1</v>
+      </c>
+      <c r="G139" s="13"/>
+      <c r="H139" s="14"/>
       <c r="I139" s="9">
         <v>2</v>
       </c>
@@ -9077,7 +9140,9 @@
       <c r="L139" s="9">
         <v>2</v>
       </c>
-      <c r="M139" s="14"/>
+      <c r="M139" s="9">
+        <v>2</v>
+      </c>
       <c r="N139" s="14"/>
       <c r="O139" s="14"/>
       <c r="P139" s="14"/>
@@ -9103,32 +9168,32 @@
       <c r="AJ139" s="14"/>
       <c r="AK139" s="14"/>
       <c r="AL139" s="14"/>
-    </row>
-    <row r="140" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM139" s="14"/>
+    </row>
+    <row r="140" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A140" s="9">
         <v>1138</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D140" s="12"/>
-      <c r="E140" s="9">
+      <c r="F140" s="9">
         <v>0</v>
       </c>
-      <c r="F140" s="13"/>
-      <c r="G140" s="14"/>
+      <c r="G140" s="13"/>
       <c r="H140" s="14"/>
       <c r="I140" s="14"/>
       <c r="J140" s="14"/>
       <c r="K140" s="14"/>
       <c r="L140" s="14"/>
-      <c r="M140" s="9">
-        <v>1</v>
-      </c>
-      <c r="N140" s="14"/>
+      <c r="M140" s="14"/>
+      <c r="N140" s="9">
+        <v>1</v>
+      </c>
       <c r="O140" s="14"/>
       <c r="P140" s="14"/>
       <c r="Q140" s="14"/>
@@ -9153,32 +9218,32 @@
       <c r="AJ140" s="14"/>
       <c r="AK140" s="14"/>
       <c r="AL140" s="14"/>
-    </row>
-    <row r="141" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM140" s="14"/>
+    </row>
+    <row r="141" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="9">
         <v>1139</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D141" s="12"/>
-      <c r="E141" s="9">
-        <v>1</v>
-      </c>
-      <c r="F141" s="13"/>
-      <c r="G141" s="14"/>
+      <c r="F141" s="9">
+        <v>1</v>
+      </c>
+      <c r="G141" s="13"/>
       <c r="H141" s="14"/>
       <c r="I141" s="14"/>
       <c r="J141" s="14"/>
       <c r="K141" s="14"/>
       <c r="L141" s="14"/>
-      <c r="M141" s="9">
+      <c r="M141" s="14"/>
+      <c r="N141" s="9">
         <v>2</v>
       </c>
-      <c r="N141" s="14"/>
       <c r="O141" s="14"/>
       <c r="P141" s="14"/>
       <c r="Q141" s="14"/>
@@ -9203,32 +9268,32 @@
       <c r="AJ141" s="14"/>
       <c r="AK141" s="14"/>
       <c r="AL141" s="14"/>
-    </row>
-    <row r="142" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM141" s="14"/>
+    </row>
+    <row r="142" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A142" s="9">
         <v>1140</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D142" s="12"/>
-      <c r="E142" s="9">
+      <c r="F142" s="9">
         <v>2</v>
       </c>
-      <c r="F142" s="13"/>
-      <c r="G142" s="14"/>
+      <c r="G142" s="13"/>
       <c r="H142" s="14"/>
       <c r="I142" s="14"/>
       <c r="J142" s="14"/>
       <c r="K142" s="14"/>
       <c r="L142" s="14"/>
-      <c r="M142" s="9">
+      <c r="M142" s="14"/>
+      <c r="N142" s="9">
         <v>4</v>
       </c>
-      <c r="N142" s="14"/>
       <c r="O142" s="14"/>
       <c r="P142" s="14"/>
       <c r="Q142" s="14"/>
@@ -9253,32 +9318,32 @@
       <c r="AJ142" s="14"/>
       <c r="AK142" s="14"/>
       <c r="AL142" s="14"/>
-    </row>
-    <row r="143" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM142" s="14"/>
+    </row>
+    <row r="143" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="9">
         <v>1141</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D143" s="12"/>
-      <c r="E143" s="9">
+      <c r="F143" s="9">
         <v>3</v>
       </c>
-      <c r="F143" s="13"/>
-      <c r="G143" s="14"/>
+      <c r="G143" s="13"/>
       <c r="H143" s="14"/>
       <c r="I143" s="14"/>
       <c r="J143" s="14"/>
       <c r="K143" s="14"/>
       <c r="L143" s="14"/>
-      <c r="M143" s="9">
+      <c r="M143" s="14"/>
+      <c r="N143" s="9">
         <v>8</v>
       </c>
-      <c r="N143" s="14"/>
       <c r="O143" s="14"/>
       <c r="P143" s="14"/>
       <c r="Q143" s="14"/>
@@ -9303,33 +9368,33 @@
       <c r="AJ143" s="14"/>
       <c r="AK143" s="14"/>
       <c r="AL143" s="14"/>
-    </row>
-    <row r="144" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM143" s="14"/>
+    </row>
+    <row r="144" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A144" s="9">
         <v>1142</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D144" s="12"/>
-      <c r="E144" s="9">
+      <c r="F144" s="9">
         <v>0</v>
       </c>
-      <c r="F144" s="13"/>
-      <c r="G144" s="14"/>
+      <c r="G144" s="13"/>
       <c r="H144" s="14"/>
       <c r="I144" s="14"/>
       <c r="J144" s="14"/>
       <c r="K144" s="14"/>
       <c r="L144" s="14"/>
       <c r="M144" s="14"/>
-      <c r="N144" s="9">
-        <v>1</v>
-      </c>
-      <c r="O144" s="14"/>
+      <c r="N144" s="14"/>
+      <c r="O144" s="9">
+        <v>1</v>
+      </c>
       <c r="P144" s="14"/>
       <c r="Q144" s="14"/>
       <c r="R144" s="14"/>
@@ -9345,57 +9410,57 @@
       <c r="AB144" s="14"/>
       <c r="AC144" s="14"/>
       <c r="AD144" s="14"/>
-      <c r="AE144" s="15" t="s">
+      <c r="AE144" s="14"/>
+      <c r="AF144" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG144" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH144" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF144" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG144" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH144" s="9">
+      <c r="AI144" s="9">
         <v>1110</v>
       </c>
-      <c r="AI144" s="9">
+      <c r="AJ144" s="9">
         <v>1003</v>
       </c>
-      <c r="AJ144" s="9">
+      <c r="AK144" s="9">
         <v>1004</v>
       </c>
-      <c r="AK144" s="9">
+      <c r="AL144" s="9">
         <v>1124</v>
       </c>
-      <c r="AL144" s="9">
+      <c r="AM144" s="9">
         <v>1125</v>
       </c>
     </row>
-    <row r="145" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A145" s="9">
         <v>1143</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D145" s="12"/>
-      <c r="E145" s="9">
-        <v>1</v>
-      </c>
-      <c r="F145" s="13"/>
-      <c r="G145" s="14"/>
+      <c r="F145" s="9">
+        <v>1</v>
+      </c>
+      <c r="G145" s="13"/>
       <c r="H145" s="14"/>
       <c r="I145" s="14"/>
       <c r="J145" s="14"/>
       <c r="K145" s="14"/>
       <c r="L145" s="14"/>
       <c r="M145" s="14"/>
-      <c r="N145" s="9">
+      <c r="N145" s="14"/>
+      <c r="O145" s="9">
         <v>2</v>
       </c>
-      <c r="O145" s="14"/>
       <c r="P145" s="14"/>
       <c r="Q145" s="14"/>
       <c r="R145" s="14"/>
@@ -9411,57 +9476,57 @@
       <c r="AB145" s="14"/>
       <c r="AC145" s="14"/>
       <c r="AD145" s="14"/>
-      <c r="AE145" s="15" t="s">
+      <c r="AE145" s="14"/>
+      <c r="AF145" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG145" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH145" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF145" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG145" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH145" s="9">
+      <c r="AI145" s="9">
         <v>1110</v>
       </c>
-      <c r="AI145" s="9">
+      <c r="AJ145" s="9">
         <v>1003</v>
       </c>
-      <c r="AJ145" s="9">
+      <c r="AK145" s="9">
         <v>1004</v>
       </c>
-      <c r="AK145" s="9">
+      <c r="AL145" s="9">
         <v>1124</v>
       </c>
-      <c r="AL145" s="9">
+      <c r="AM145" s="9">
         <v>1125</v>
       </c>
     </row>
-    <row r="146" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A146" s="9">
         <v>1144</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D146" s="12"/>
-      <c r="E146" s="9">
+      <c r="F146" s="9">
         <v>2</v>
       </c>
-      <c r="F146" s="13"/>
-      <c r="G146" s="14"/>
+      <c r="G146" s="13"/>
       <c r="H146" s="14"/>
       <c r="I146" s="14"/>
       <c r="J146" s="14"/>
       <c r="K146" s="14"/>
       <c r="L146" s="14"/>
       <c r="M146" s="14"/>
-      <c r="N146" s="9">
+      <c r="N146" s="14"/>
+      <c r="O146" s="9">
         <v>3</v>
       </c>
-      <c r="O146" s="14"/>
       <c r="P146" s="14"/>
       <c r="Q146" s="14"/>
       <c r="R146" s="14"/>
@@ -9485,23 +9550,23 @@
       <c r="AJ146" s="14"/>
       <c r="AK146" s="14"/>
       <c r="AL146" s="14"/>
-    </row>
-    <row r="147" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM146" s="14"/>
+    </row>
+    <row r="147" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="9">
         <v>1145</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D147" s="12"/>
-      <c r="E147" s="9">
-        <v>1</v>
-      </c>
-      <c r="F147" s="13"/>
-      <c r="G147" s="14"/>
+      <c r="F147" s="9">
+        <v>1</v>
+      </c>
+      <c r="G147" s="13"/>
       <c r="H147" s="14"/>
       <c r="I147" s="14"/>
       <c r="J147" s="14"/>
@@ -9509,55 +9574,55 @@
       <c r="L147" s="14"/>
       <c r="M147" s="14"/>
       <c r="N147" s="14"/>
-      <c r="O147" s="9">
+      <c r="O147" s="14"/>
+      <c r="P147" s="9">
         <v>1138</v>
       </c>
-      <c r="P147" s="9">
+      <c r="Q147" s="9">
         <v>1133</v>
       </c>
-      <c r="Q147" s="9">
+      <c r="R147" s="9">
         <v>1125</v>
       </c>
-      <c r="R147" s="9">
+      <c r="S147" s="9">
         <v>1128</v>
       </c>
-      <c r="S147" s="9">
+      <c r="T147" s="9">
         <v>1129</v>
       </c>
-      <c r="T147" s="9">
+      <c r="U147" s="9">
         <v>1131</v>
       </c>
-      <c r="U147" s="9">
+      <c r="V147" s="9">
         <v>1111</v>
       </c>
-      <c r="V147" s="9">
+      <c r="W147" s="9">
         <v>1108</v>
       </c>
-      <c r="W147" s="9">
+      <c r="X147" s="9">
         <v>1071</v>
       </c>
-      <c r="X147" s="9">
+      <c r="Y147" s="9">
         <v>1072</v>
       </c>
-      <c r="Y147" s="9">
+      <c r="Z147" s="9">
         <v>1044</v>
       </c>
-      <c r="Z147" s="9">
+      <c r="AA147" s="9">
         <v>1039</v>
       </c>
-      <c r="AA147" s="9">
+      <c r="AB147" s="9">
         <v>1040</v>
       </c>
-      <c r="AB147" s="9">
+      <c r="AC147" s="9">
         <v>1033</v>
       </c>
-      <c r="AC147" s="9">
+      <c r="AD147" s="9">
         <v>1031</v>
       </c>
-      <c r="AD147" s="9">
+      <c r="AE147" s="9">
         <v>1002</v>
       </c>
-      <c r="AE147" s="14"/>
       <c r="AF147" s="14"/>
       <c r="AG147" s="14"/>
       <c r="AH147" s="14"/>
@@ -9565,23 +9630,23 @@
       <c r="AJ147" s="14"/>
       <c r="AK147" s="14"/>
       <c r="AL147" s="14"/>
-    </row>
-    <row r="148" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM147" s="14"/>
+    </row>
+    <row r="148" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="9">
         <v>1146</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D148" s="12"/>
-      <c r="E148" s="9">
-        <v>1</v>
-      </c>
-      <c r="F148" s="13"/>
-      <c r="G148" s="14"/>
+      <c r="F148" s="9">
+        <v>1</v>
+      </c>
+      <c r="G148" s="13"/>
       <c r="H148" s="14"/>
       <c r="I148" s="14"/>
       <c r="J148" s="14"/>
@@ -9589,28 +9654,28 @@
       <c r="L148" s="14"/>
       <c r="M148" s="14"/>
       <c r="N148" s="14"/>
-      <c r="O148" s="9" t="s">
+      <c r="O148" s="14"/>
+      <c r="P148" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q148" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="R148" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="P148" s="9" t="s">
+      <c r="S148" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="Q148" s="9" t="s">
+      <c r="T148" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="R148" s="9" t="s">
+      <c r="U148" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="S148" s="9" t="s">
+      <c r="V148" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="T148" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="U148" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="V148" s="14"/>
       <c r="W148" s="14"/>
       <c r="X148" s="14"/>
       <c r="Y148" s="14"/>
@@ -9627,23 +9692,23 @@
       <c r="AJ148" s="14"/>
       <c r="AK148" s="14"/>
       <c r="AL148" s="14"/>
-    </row>
-    <row r="149" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM148" s="14"/>
+    </row>
+    <row r="149" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A149" s="9">
         <v>1147</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D149" s="12"/>
-      <c r="E149" s="9">
+      <c r="F149" s="9">
         <v>3</v>
       </c>
-      <c r="F149" s="13"/>
-      <c r="G149" s="14"/>
+      <c r="G149" s="13"/>
       <c r="H149" s="14"/>
       <c r="I149" s="14"/>
       <c r="J149" s="14"/>
@@ -9675,26 +9740,24 @@
       <c r="AJ149" s="14"/>
       <c r="AK149" s="14"/>
       <c r="AL149" s="14"/>
-    </row>
-    <row r="150" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM149" s="14"/>
+    </row>
+    <row r="150" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A150" s="9">
         <v>1148</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D150" s="12"/>
-      <c r="E150" s="9">
+      <c r="F150" s="9">
         <v>2</v>
       </c>
-      <c r="F150" s="13"/>
-      <c r="G150" s="14"/>
-      <c r="H150" s="9">
-        <v>-2</v>
-      </c>
+      <c r="G150" s="13"/>
+      <c r="H150" s="14"/>
       <c r="I150" s="9">
         <v>-2</v>
       </c>
@@ -9707,7 +9770,9 @@
       <c r="L150" s="9">
         <v>-2</v>
       </c>
-      <c r="M150" s="14"/>
+      <c r="M150" s="9">
+        <v>-2</v>
+      </c>
       <c r="N150" s="14"/>
       <c r="O150" s="14"/>
       <c r="P150" s="14"/>
@@ -9733,32 +9798,32 @@
       <c r="AJ150" s="14"/>
       <c r="AK150" s="14"/>
       <c r="AL150" s="14"/>
-    </row>
-    <row r="151" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM150" s="14"/>
+    </row>
+    <row r="151" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="9">
         <v>2001</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D151" s="12"/>
-      <c r="E151" s="9">
+      <c r="F151" s="9">
         <v>2</v>
       </c>
-      <c r="F151" s="9">
-        <v>1</v>
-      </c>
-      <c r="G151" s="14"/>
+      <c r="G151" s="9">
+        <v>1</v>
+      </c>
       <c r="H151" s="14"/>
       <c r="I151" s="14"/>
       <c r="J151" s="14"/>
-      <c r="K151" s="9">
+      <c r="K151" s="14"/>
+      <c r="L151" s="9">
         <v>4</v>
       </c>
-      <c r="L151" s="14"/>
       <c r="M151" s="14"/>
       <c r="N151" s="14"/>
       <c r="O151" s="14"/>
@@ -9785,31 +9850,31 @@
       <c r="AJ151" s="14"/>
       <c r="AK151" s="14"/>
       <c r="AL151" s="14"/>
-    </row>
-    <row r="152" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM151" s="14"/>
+    </row>
+    <row r="152" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="9">
         <v>2002</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D152" s="12"/>
-      <c r="E152" s="9">
+      <c r="F152" s="9">
         <v>2</v>
       </c>
-      <c r="F152" s="9">
-        <v>1</v>
-      </c>
-      <c r="G152" s="14"/>
+      <c r="G152" s="9">
+        <v>1</v>
+      </c>
       <c r="H152" s="14"/>
       <c r="I152" s="14"/>
-      <c r="J152" s="9">
+      <c r="J152" s="14"/>
+      <c r="K152" s="9">
         <v>4</v>
       </c>
-      <c r="K152" s="14"/>
       <c r="L152" s="14"/>
       <c r="M152" s="14"/>
       <c r="N152" s="14"/>
@@ -9837,25 +9902,25 @@
       <c r="AJ152" s="14"/>
       <c r="AK152" s="14"/>
       <c r="AL152" s="14"/>
-    </row>
-    <row r="153" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM152" s="14"/>
+    </row>
+    <row r="153" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="9">
         <v>2003</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D153" s="12"/>
-      <c r="E153" s="9">
+      <c r="F153" s="9">
         <v>0</v>
       </c>
-      <c r="F153" s="9">
-        <v>1</v>
-      </c>
-      <c r="G153" s="14"/>
+      <c r="G153" s="9">
+        <v>1</v>
+      </c>
       <c r="H153" s="14"/>
       <c r="I153" s="14"/>
       <c r="J153" s="14"/>
@@ -9887,25 +9952,25 @@
       <c r="AJ153" s="14"/>
       <c r="AK153" s="14"/>
       <c r="AL153" s="14"/>
-    </row>
-    <row r="154" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM153" s="14"/>
+    </row>
+    <row r="154" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A154" s="9">
         <v>2004</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D154" s="12"/>
-      <c r="E154" s="9">
+      <c r="F154" s="9">
         <v>0</v>
       </c>
-      <c r="F154" s="9">
-        <v>1</v>
-      </c>
-      <c r="G154" s="14"/>
+      <c r="G154" s="9">
+        <v>1</v>
+      </c>
       <c r="H154" s="14"/>
       <c r="I154" s="14"/>
       <c r="J154" s="14"/>
@@ -9937,25 +10002,25 @@
       <c r="AJ154" s="14"/>
       <c r="AK154" s="14"/>
       <c r="AL154" s="14"/>
-    </row>
-    <row r="155" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM154" s="14"/>
+    </row>
+    <row r="155" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A155" s="9">
         <v>2005</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C155" s="11">
         <v>3.1415926000000001</v>
       </c>
       <c r="D155" s="12"/>
-      <c r="E155" s="9">
+      <c r="F155" s="9">
         <v>0</v>
       </c>
-      <c r="F155" s="9">
-        <v>1</v>
-      </c>
-      <c r="G155" s="14"/>
+      <c r="G155" s="9">
+        <v>1</v>
+      </c>
       <c r="H155" s="14"/>
       <c r="I155" s="14"/>
       <c r="J155" s="14"/>
@@ -9987,35 +10052,35 @@
       <c r="AJ155" s="14"/>
       <c r="AK155" s="14"/>
       <c r="AL155" s="14"/>
-    </row>
-    <row r="156" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM155" s="14"/>
+    </row>
+    <row r="156" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A156" s="9">
         <v>2006</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D156" s="12"/>
-      <c r="E156" s="9">
-        <v>1</v>
-      </c>
       <c r="F156" s="9">
         <v>1</v>
       </c>
-      <c r="G156" s="14"/>
+      <c r="G156" s="9">
+        <v>1</v>
+      </c>
       <c r="H156" s="14"/>
       <c r="I156" s="14"/>
       <c r="J156" s="14"/>
       <c r="K156" s="14"/>
       <c r="L156" s="14"/>
       <c r="M156" s="14"/>
-      <c r="N156" s="9">
+      <c r="N156" s="14"/>
+      <c r="O156" s="9">
         <v>2</v>
       </c>
-      <c r="O156" s="14"/>
       <c r="P156" s="14"/>
       <c r="Q156" s="14"/>
       <c r="R156" s="14"/>
@@ -10031,65 +10096,66 @@
       <c r="AB156" s="14"/>
       <c r="AC156" s="14"/>
       <c r="AD156" s="14"/>
-      <c r="AE156" s="15" t="s">
+      <c r="AE156" s="14"/>
+      <c r="AF156" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG156" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH156" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF156" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG156" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH156" s="9">
+      <c r="AI156" s="9">
         <v>1110</v>
       </c>
-      <c r="AI156" s="9">
+      <c r="AJ156" s="9">
         <v>1003</v>
       </c>
-      <c r="AJ156" s="9">
+      <c r="AK156" s="9">
         <v>1004</v>
       </c>
-      <c r="AK156" s="9">
+      <c r="AL156" s="9">
         <v>1124</v>
       </c>
-      <c r="AL156" s="9">
+      <c r="AM156" s="9">
         <v>1125</v>
       </c>
     </row>
-    <row r="157" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A157" s="9">
         <v>2007</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="E157" s="9">
+        <v>237</v>
+      </c>
+      <c r="E157" s="10"/>
+      <c r="F157" s="9">
         <v>0</v>
       </c>
-      <c r="F157" s="9">
-        <v>1</v>
-      </c>
-      <c r="G157" s="14"/>
-      <c r="H157" s="9">
-        <v>1</v>
-      </c>
+      <c r="G157" s="9">
+        <v>1</v>
+      </c>
+      <c r="H157" s="14"/>
       <c r="I157" s="9">
         <v>1</v>
       </c>
       <c r="J157" s="9">
         <v>1</v>
       </c>
-      <c r="K157" s="14"/>
-      <c r="L157" s="9">
-        <v>1</v>
-      </c>
-      <c r="M157" s="14"/>
+      <c r="K157" s="9">
+        <v>1</v>
+      </c>
+      <c r="L157" s="14"/>
+      <c r="M157" s="9">
+        <v>1</v>
+      </c>
       <c r="N157" s="14"/>
       <c r="O157" s="14"/>
       <c r="P157" s="14"/>
@@ -10115,30 +10181,29 @@
       <c r="AJ157" s="14"/>
       <c r="AK157" s="14"/>
       <c r="AL157" s="14"/>
-    </row>
-    <row r="158" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM157" s="14"/>
+    </row>
+    <row r="158" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A158" s="9">
         <v>2008</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="E158" s="9">
+        <v>265</v>
+      </c>
+      <c r="E158" s="17"/>
+      <c r="F158" s="9">
         <v>0</v>
       </c>
-      <c r="F158" s="9">
-        <v>1</v>
-      </c>
-      <c r="G158" s="14"/>
-      <c r="H158" s="9">
-        <v>1</v>
-      </c>
+      <c r="G158" s="9">
+        <v>1</v>
+      </c>
+      <c r="H158" s="14"/>
       <c r="I158" s="9">
         <v>1</v>
       </c>
@@ -10151,7 +10216,9 @@
       <c r="L158" s="9">
         <v>1</v>
       </c>
-      <c r="M158" s="14"/>
+      <c r="M158" s="9">
+        <v>1</v>
+      </c>
       <c r="N158" s="14"/>
       <c r="O158" s="14"/>
       <c r="P158" s="14"/>
@@ -10177,35 +10244,35 @@
       <c r="AJ158" s="14"/>
       <c r="AK158" s="14"/>
       <c r="AL158" s="14"/>
-    </row>
-    <row r="159" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM158" s="14"/>
+    </row>
+    <row r="159" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A159" s="9">
         <v>2009</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D159" s="12"/>
-      <c r="E159" s="9">
+      <c r="F159" s="9">
         <v>0</v>
       </c>
-      <c r="F159" s="9">
-        <v>1</v>
-      </c>
-      <c r="G159" s="14"/>
+      <c r="G159" s="9">
+        <v>1</v>
+      </c>
       <c r="H159" s="14"/>
       <c r="I159" s="14"/>
       <c r="J159" s="14"/>
       <c r="K159" s="14"/>
       <c r="L159" s="14"/>
       <c r="M159" s="14"/>
-      <c r="N159" s="9">
+      <c r="N159" s="14"/>
+      <c r="O159" s="9">
         <v>0</v>
       </c>
-      <c r="O159" s="14"/>
       <c r="P159" s="14"/>
       <c r="Q159" s="14"/>
       <c r="R159" s="14"/>
@@ -10221,59 +10288,59 @@
       <c r="AB159" s="14"/>
       <c r="AC159" s="14"/>
       <c r="AD159" s="14"/>
-      <c r="AE159" s="15" t="s">
+      <c r="AE159" s="14"/>
+      <c r="AF159" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG159" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH159" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF159" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG159" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH159" s="9">
+      <c r="AI159" s="9">
         <v>1110</v>
       </c>
-      <c r="AI159" s="9">
+      <c r="AJ159" s="9">
         <v>1003</v>
       </c>
-      <c r="AJ159" s="9">
+      <c r="AK159" s="9">
         <v>1004</v>
       </c>
-      <c r="AK159" s="9">
+      <c r="AL159" s="9">
         <v>1124</v>
       </c>
-      <c r="AL159" s="9">
+      <c r="AM159" s="9">
         <v>1125</v>
       </c>
     </row>
-    <row r="160" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A160" s="9">
         <v>2010</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D160" s="12"/>
-      <c r="E160" s="9">
+      <c r="F160" s="9">
         <v>0</v>
       </c>
-      <c r="F160" s="9">
-        <v>1</v>
-      </c>
-      <c r="G160" s="14"/>
+      <c r="G160" s="9">
+        <v>1</v>
+      </c>
       <c r="H160" s="14"/>
       <c r="I160" s="14"/>
       <c r="J160" s="14"/>
       <c r="K160" s="14"/>
       <c r="L160" s="14"/>
       <c r="M160" s="14"/>
-      <c r="N160" s="9">
+      <c r="N160" s="14"/>
+      <c r="O160" s="9">
         <v>0</v>
       </c>
-      <c r="O160" s="14"/>
       <c r="P160" s="14"/>
       <c r="Q160" s="14"/>
       <c r="R160" s="14"/>
@@ -10289,59 +10356,59 @@
       <c r="AB160" s="14"/>
       <c r="AC160" s="14"/>
       <c r="AD160" s="14"/>
-      <c r="AE160" s="15" t="s">
+      <c r="AE160" s="14"/>
+      <c r="AF160" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG160" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH160" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF160" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG160" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH160" s="9">
+      <c r="AI160" s="9">
         <v>1110</v>
       </c>
-      <c r="AI160" s="9">
+      <c r="AJ160" s="9">
         <v>1003</v>
       </c>
-      <c r="AJ160" s="9">
+      <c r="AK160" s="9">
         <v>1004</v>
       </c>
-      <c r="AK160" s="9">
+      <c r="AL160" s="9">
         <v>1124</v>
       </c>
-      <c r="AL160" s="9">
+      <c r="AM160" s="9">
         <v>1125</v>
       </c>
     </row>
-    <row r="161" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A161" s="9">
         <v>2011</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D161" s="12"/>
-      <c r="E161" s="9">
+      <c r="F161" s="9">
         <v>0</v>
       </c>
-      <c r="F161" s="9">
-        <v>1</v>
-      </c>
-      <c r="G161" s="14"/>
+      <c r="G161" s="9">
+        <v>1</v>
+      </c>
       <c r="H161" s="14"/>
       <c r="I161" s="14"/>
       <c r="J161" s="14"/>
       <c r="K161" s="14"/>
       <c r="L161" s="14"/>
       <c r="M161" s="14"/>
-      <c r="N161" s="9">
+      <c r="N161" s="14"/>
+      <c r="O161" s="9">
         <v>0</v>
       </c>
-      <c r="O161" s="14"/>
       <c r="P161" s="14"/>
       <c r="Q161" s="14"/>
       <c r="R161" s="14"/>
@@ -10357,59 +10424,59 @@
       <c r="AB161" s="14"/>
       <c r="AC161" s="14"/>
       <c r="AD161" s="14"/>
-      <c r="AE161" s="15" t="s">
+      <c r="AE161" s="14"/>
+      <c r="AF161" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG161" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH161" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF161" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG161" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH161" s="9">
+      <c r="AI161" s="9">
         <v>1110</v>
       </c>
-      <c r="AI161" s="9">
+      <c r="AJ161" s="9">
         <v>1003</v>
       </c>
-      <c r="AJ161" s="9">
+      <c r="AK161" s="9">
         <v>1004</v>
       </c>
-      <c r="AK161" s="9">
+      <c r="AL161" s="9">
         <v>1124</v>
       </c>
-      <c r="AL161" s="9">
+      <c r="AM161" s="9">
         <v>1125</v>
       </c>
     </row>
-    <row r="162" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A162" s="9">
         <v>2012</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D162" s="12"/>
-      <c r="E162" s="9">
+      <c r="F162" s="9">
         <v>0</v>
       </c>
-      <c r="F162" s="9">
-        <v>1</v>
-      </c>
-      <c r="G162" s="14"/>
+      <c r="G162" s="9">
+        <v>1</v>
+      </c>
       <c r="H162" s="14"/>
       <c r="I162" s="14"/>
       <c r="J162" s="14"/>
       <c r="K162" s="14"/>
       <c r="L162" s="14"/>
       <c r="M162" s="14"/>
-      <c r="N162" s="9">
+      <c r="N162" s="14"/>
+      <c r="O162" s="9">
         <v>0</v>
       </c>
-      <c r="O162" s="14"/>
       <c r="P162" s="14"/>
       <c r="Q162" s="14"/>
       <c r="R162" s="14"/>
@@ -10425,59 +10492,59 @@
       <c r="AB162" s="14"/>
       <c r="AC162" s="14"/>
       <c r="AD162" s="14"/>
-      <c r="AE162" s="15" t="s">
+      <c r="AE162" s="14"/>
+      <c r="AF162" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG162" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH162" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF162" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG162" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH162" s="9">
+      <c r="AI162" s="9">
         <v>1110</v>
       </c>
-      <c r="AI162" s="9">
+      <c r="AJ162" s="9">
         <v>1003</v>
       </c>
-      <c r="AJ162" s="9">
+      <c r="AK162" s="9">
         <v>1004</v>
       </c>
-      <c r="AK162" s="9">
+      <c r="AL162" s="9">
         <v>1124</v>
       </c>
-      <c r="AL162" s="9">
+      <c r="AM162" s="9">
         <v>1125</v>
       </c>
     </row>
-    <row r="163" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A163" s="9">
         <v>2013</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D163" s="12"/>
-      <c r="E163" s="9">
+      <c r="F163" s="9">
         <v>0</v>
       </c>
-      <c r="F163" s="9">
-        <v>1</v>
-      </c>
-      <c r="G163" s="14"/>
+      <c r="G163" s="9">
+        <v>1</v>
+      </c>
       <c r="H163" s="14"/>
       <c r="I163" s="14"/>
       <c r="J163" s="14"/>
       <c r="K163" s="14"/>
       <c r="L163" s="14"/>
       <c r="M163" s="14"/>
-      <c r="N163" s="9">
+      <c r="N163" s="14"/>
+      <c r="O163" s="9">
         <v>0</v>
       </c>
-      <c r="O163" s="14"/>
       <c r="P163" s="14"/>
       <c r="Q163" s="14"/>
       <c r="R163" s="14"/>
@@ -10493,49 +10560,49 @@
       <c r="AB163" s="14"/>
       <c r="AC163" s="14"/>
       <c r="AD163" s="14"/>
-      <c r="AE163" s="15" t="s">
+      <c r="AE163" s="14"/>
+      <c r="AF163" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG163" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH163" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AF163" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG163" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH163" s="9">
+      <c r="AI163" s="9">
         <v>1110</v>
       </c>
-      <c r="AI163" s="9">
+      <c r="AJ163" s="9">
         <v>1003</v>
       </c>
-      <c r="AJ163" s="9">
+      <c r="AK163" s="9">
         <v>1004</v>
       </c>
-      <c r="AK163" s="9">
+      <c r="AL163" s="9">
         <v>1124</v>
       </c>
-      <c r="AL163" s="9">
+      <c r="AM163" s="9">
         <v>1125</v>
       </c>
     </row>
-    <row r="164" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A164" s="9">
         <v>2014</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D164" s="12"/>
-      <c r="E164" s="9">
+      <c r="F164" s="9">
         <v>0</v>
       </c>
-      <c r="F164" s="9">
-        <v>1</v>
-      </c>
-      <c r="G164" s="14"/>
+      <c r="G164" s="9">
+        <v>1</v>
+      </c>
       <c r="H164" s="14"/>
       <c r="I164" s="14"/>
       <c r="J164" s="14"/>
@@ -10567,46 +10634,46 @@
       <c r="AJ164" s="14"/>
       <c r="AK164" s="14"/>
       <c r="AL164" s="14"/>
-    </row>
-    <row r="165" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM164" s="14"/>
+    </row>
+    <row r="165" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A165" s="9">
         <v>2015</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D165" s="12"/>
-      <c r="E165" s="9">
+      <c r="F165" s="9">
         <v>3</v>
       </c>
-      <c r="F165" s="9">
-        <v>1</v>
-      </c>
       <c r="G165" s="9">
         <v>1</v>
       </c>
       <c r="H165" s="9">
+        <v>1</v>
+      </c>
+      <c r="I165" s="9">
         <v>5</v>
       </c>
-      <c r="I165" s="9">
-        <v>1</v>
-      </c>
       <c r="J165" s="9">
         <v>1</v>
       </c>
       <c r="K165" s="9">
+        <v>1</v>
+      </c>
+      <c r="L165" s="9">
         <v>2</v>
       </c>
-      <c r="L165" s="9">
-        <v>1</v>
-      </c>
       <c r="M165" s="9">
         <v>1</v>
       </c>
-      <c r="N165" s="14"/>
+      <c r="N165" s="9">
+        <v>1</v>
+      </c>
       <c r="O165" s="14"/>
       <c r="P165" s="14"/>
       <c r="Q165" s="14"/>
@@ -10631,25 +10698,25 @@
       <c r="AJ165" s="14"/>
       <c r="AK165" s="14"/>
       <c r="AL165" s="14"/>
-    </row>
-    <row r="166" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM165" s="14"/>
+    </row>
+    <row r="166" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A166" s="9">
         <v>2016</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D166" s="12"/>
-      <c r="E166" s="9">
+      <c r="F166" s="9">
         <v>2</v>
       </c>
-      <c r="F166" s="9">
-        <v>1</v>
-      </c>
-      <c r="G166" s="14"/>
+      <c r="G166" s="9">
+        <v>1</v>
+      </c>
       <c r="H166" s="14"/>
       <c r="I166" s="14"/>
       <c r="J166" s="14"/>
@@ -10657,28 +10724,28 @@
       <c r="L166" s="14"/>
       <c r="M166" s="14"/>
       <c r="N166" s="14"/>
-      <c r="O166" s="9">
+      <c r="O166" s="14"/>
+      <c r="P166" s="9">
         <v>1141</v>
       </c>
-      <c r="P166" s="9">
+      <c r="Q166" s="9">
         <v>1135</v>
       </c>
-      <c r="Q166" s="9">
+      <c r="R166" s="9">
         <v>1114</v>
       </c>
-      <c r="R166" s="9">
+      <c r="S166" s="9">
         <v>1023</v>
       </c>
-      <c r="S166" s="9">
+      <c r="T166" s="9">
         <v>1048</v>
       </c>
-      <c r="T166" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="U166" s="9">
+      <c r="U166" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="V166" s="9">
         <v>1147</v>
       </c>
-      <c r="V166" s="14"/>
       <c r="W166" s="14"/>
       <c r="X166" s="14"/>
       <c r="Y166" s="14"/>
@@ -10695,25 +10762,25 @@
       <c r="AJ166" s="14"/>
       <c r="AK166" s="14"/>
       <c r="AL166" s="14"/>
-    </row>
-    <row r="167" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM166" s="14"/>
+    </row>
+    <row r="167" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A167" s="9">
         <v>2017</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D167" s="12"/>
-      <c r="E167" s="9">
+      <c r="F167" s="9">
         <v>0</v>
       </c>
-      <c r="F167" s="9">
-        <v>1</v>
-      </c>
-      <c r="G167" s="14"/>
+      <c r="G167" s="9">
+        <v>1</v>
+      </c>
       <c r="H167" s="14"/>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
@@ -10745,34 +10812,35 @@
       <c r="AJ167" s="14"/>
       <c r="AK167" s="14"/>
       <c r="AL167" s="14"/>
-    </row>
-    <row r="168" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM167" s="14"/>
+    </row>
+    <row r="168" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A168" s="9">
         <v>2018</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E168" s="9">
+        <v>144</v>
+      </c>
+      <c r="E168" s="10"/>
+      <c r="F168" s="9">
         <v>0</v>
       </c>
-      <c r="F168" s="9">
-        <v>1</v>
-      </c>
-      <c r="G168" s="14"/>
+      <c r="G168" s="9">
+        <v>1</v>
+      </c>
       <c r="H168" s="14"/>
       <c r="I168" s="14"/>
       <c r="J168" s="14"/>
-      <c r="K168" s="9">
+      <c r="K168" s="14"/>
+      <c r="L168" s="9">
         <v>-2</v>
       </c>
-      <c r="L168" s="14"/>
       <c r="M168" s="14"/>
       <c r="N168" s="14"/>
       <c r="O168" s="14"/>
@@ -10799,32 +10867,33 @@
       <c r="AJ168" s="14"/>
       <c r="AK168" s="14"/>
       <c r="AL168" s="14"/>
-    </row>
-    <row r="169" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM168" s="14"/>
+    </row>
+    <row r="169" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A169" s="9">
         <v>2019</v>
       </c>
       <c r="B169" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D169" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="C169" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="D169" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="E169" s="9">
-        <v>1</v>
-      </c>
+      <c r="E169" s="10"/>
       <c r="F169" s="9">
         <v>1</v>
       </c>
-      <c r="G169" s="14"/>
+      <c r="G169" s="9">
+        <v>1</v>
+      </c>
       <c r="H169" s="14"/>
-      <c r="I169" s="9">
+      <c r="I169" s="14"/>
+      <c r="J169" s="9">
         <v>3</v>
       </c>
-      <c r="J169" s="14"/>
       <c r="K169" s="14"/>
       <c r="L169" s="14"/>
       <c r="M169" s="14"/>
@@ -10853,33 +10922,34 @@
       <c r="AJ169" s="14"/>
       <c r="AK169" s="14"/>
       <c r="AL169" s="14"/>
-    </row>
-    <row r="170" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM169" s="14"/>
+    </row>
+    <row r="170" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A170" s="9">
         <v>2020</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E170" s="9">
+        <v>135</v>
+      </c>
+      <c r="E170" s="10"/>
+      <c r="F170" s="9">
         <v>0</v>
       </c>
-      <c r="F170" s="9">
-        <v>1</v>
-      </c>
-      <c r="G170" s="14"/>
+      <c r="G170" s="9">
+        <v>1</v>
+      </c>
       <c r="H170" s="14"/>
       <c r="I170" s="14"/>
-      <c r="J170" s="9">
+      <c r="J170" s="14"/>
+      <c r="K170" s="9">
         <v>-2</v>
       </c>
-      <c r="K170" s="14"/>
       <c r="L170" s="14"/>
       <c r="M170" s="14"/>
       <c r="N170" s="14"/>
@@ -10907,25 +10977,25 @@
       <c r="AJ170" s="14"/>
       <c r="AK170" s="14"/>
       <c r="AL170" s="14"/>
-    </row>
-    <row r="171" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM170" s="14"/>
+    </row>
+    <row r="171" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="9">
         <v>2021</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D171" s="12"/>
-      <c r="E171" s="9">
+      <c r="F171" s="9">
         <v>2</v>
       </c>
-      <c r="F171" s="9">
-        <v>1</v>
-      </c>
-      <c r="G171" s="14"/>
+      <c r="G171" s="9">
+        <v>1</v>
+      </c>
       <c r="H171" s="14"/>
       <c r="I171" s="14"/>
       <c r="J171" s="14"/>
@@ -10933,51 +11003,51 @@
       <c r="L171" s="14"/>
       <c r="M171" s="14"/>
       <c r="N171" s="14"/>
-      <c r="O171" s="15" t="s">
+      <c r="O171" s="14"/>
+      <c r="P171" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q171" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="R171" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="P171" s="15" t="s">
+      <c r="S171" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="Q171" s="15" t="s">
+      <c r="T171" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="R171" s="15" t="s">
+      <c r="U171" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="S171" s="15" t="s">
+      <c r="V171" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="T171" s="15" t="s">
+      <c r="W171" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="U171" s="15" t="s">
+      <c r="X171" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="V171" s="15" t="s">
+      <c r="Y171" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="W171" s="15" t="s">
+      <c r="Z171" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="X171" s="15" t="s">
+      <c r="AA171" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="Y171" s="15" t="s">
+      <c r="AB171" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="Z171" s="15" t="s">
+      <c r="AC171" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="AA171" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="AB171" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="AC171" s="9"/>
       <c r="AD171" s="9"/>
-      <c r="AE171" s="14"/>
+      <c r="AE171" s="9"/>
       <c r="AF171" s="14"/>
       <c r="AG171" s="14"/>
       <c r="AH171" s="14"/>
@@ -10985,25 +11055,25 @@
       <c r="AJ171" s="14"/>
       <c r="AK171" s="14"/>
       <c r="AL171" s="14"/>
-    </row>
-    <row r="172" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM171" s="14"/>
+    </row>
+    <row r="172" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="9">
         <v>2022</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D172" s="12"/>
-      <c r="E172" s="9">
-        <v>1</v>
-      </c>
       <c r="F172" s="9">
         <v>1</v>
       </c>
-      <c r="G172" s="14"/>
+      <c r="G172" s="9">
+        <v>1</v>
+      </c>
       <c r="H172" s="14"/>
       <c r="I172" s="14"/>
       <c r="J172" s="14"/>
@@ -11035,25 +11105,25 @@
       <c r="AJ172" s="14"/>
       <c r="AK172" s="14"/>
       <c r="AL172" s="14"/>
-    </row>
-    <row r="173" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM172" s="14"/>
+    </row>
+    <row r="173" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="9">
         <v>2023</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D173" s="12"/>
-      <c r="E173" s="9">
+      <c r="F173" s="9">
         <v>0</v>
       </c>
-      <c r="F173" s="9">
-        <v>1</v>
-      </c>
-      <c r="G173" s="14"/>
+      <c r="G173" s="9">
+        <v>1</v>
+      </c>
       <c r="H173" s="14"/>
       <c r="I173" s="14"/>
       <c r="J173" s="14"/>
@@ -11085,25 +11155,25 @@
       <c r="AJ173" s="14"/>
       <c r="AK173" s="14"/>
       <c r="AL173" s="14"/>
-    </row>
-    <row r="174" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM173" s="14"/>
+    </row>
+    <row r="174" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="9">
         <v>2024</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D174" s="12"/>
-      <c r="E174" s="9">
+      <c r="F174" s="9">
         <v>2</v>
       </c>
-      <c r="F174" s="9">
-        <v>1</v>
-      </c>
-      <c r="G174" s="14"/>
+      <c r="G174" s="9">
+        <v>1</v>
+      </c>
       <c r="H174" s="14"/>
       <c r="I174" s="14"/>
       <c r="J174" s="14"/>
@@ -11135,35 +11205,35 @@
       <c r="AJ174" s="14"/>
       <c r="AK174" s="14"/>
       <c r="AL174" s="14"/>
-    </row>
-    <row r="175" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM174" s="14"/>
+    </row>
+    <row r="175" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="9">
         <v>2025</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D175" s="12"/>
-      <c r="E175" s="9">
+      <c r="F175" s="9">
         <v>2</v>
       </c>
-      <c r="F175" s="9">
-        <v>1</v>
-      </c>
-      <c r="G175" s="14"/>
+      <c r="G175" s="9">
+        <v>1</v>
+      </c>
       <c r="H175" s="14"/>
       <c r="I175" s="14"/>
       <c r="J175" s="14"/>
       <c r="K175" s="14"/>
       <c r="L175" s="14"/>
       <c r="M175" s="14"/>
-      <c r="N175" s="9">
+      <c r="N175" s="14"/>
+      <c r="O175" s="9">
         <v>3</v>
       </c>
-      <c r="O175" s="14"/>
       <c r="P175" s="14"/>
       <c r="Q175" s="14"/>
       <c r="R175" s="14"/>
@@ -11187,30 +11257,29 @@
       <c r="AJ175" s="14"/>
       <c r="AK175" s="14"/>
       <c r="AL175" s="14"/>
-    </row>
-    <row r="176" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM175" s="14"/>
+    </row>
+    <row r="176" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="9">
         <v>2026</v>
       </c>
       <c r="B176" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="D176" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="C176" s="11" t="s">
-        <v>429</v>
-      </c>
-      <c r="D176" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="E176" s="9">
-        <v>1</v>
-      </c>
+      <c r="E176" s="10"/>
       <c r="F176" s="9">
         <v>1</v>
       </c>
-      <c r="G176" s="14"/>
-      <c r="H176" s="9">
-        <v>1</v>
-      </c>
+      <c r="G176" s="9">
+        <v>1</v>
+      </c>
+      <c r="H176" s="14"/>
       <c r="I176" s="9">
         <v>1</v>
       </c>
@@ -11223,7 +11292,9 @@
       <c r="L176" s="9">
         <v>1</v>
       </c>
-      <c r="M176" s="14"/>
+      <c r="M176" s="9">
+        <v>1</v>
+      </c>
       <c r="N176" s="14"/>
       <c r="O176" s="14"/>
       <c r="P176" s="14"/>
@@ -11249,25 +11320,25 @@
       <c r="AJ176" s="14"/>
       <c r="AK176" s="14"/>
       <c r="AL176" s="14"/>
-    </row>
-    <row r="177" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM176" s="14"/>
+    </row>
+    <row r="177" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="9">
         <v>2027</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D177" s="12"/>
-      <c r="E177" s="9">
-        <v>1</v>
-      </c>
       <c r="F177" s="9">
         <v>1</v>
       </c>
-      <c r="G177" s="14"/>
+      <c r="G177" s="9">
+        <v>1</v>
+      </c>
       <c r="H177" s="14"/>
       <c r="I177" s="14"/>
       <c r="J177" s="14"/>
@@ -11275,31 +11346,31 @@
       <c r="L177" s="14"/>
       <c r="M177" s="14"/>
       <c r="N177" s="14"/>
-      <c r="O177" s="9">
+      <c r="O177" s="14"/>
+      <c r="P177" s="9">
         <v>2028</v>
       </c>
-      <c r="P177" s="9">
+      <c r="Q177" s="9">
         <v>2029</v>
       </c>
-      <c r="Q177" s="9">
+      <c r="R177" s="9">
         <v>2030</v>
       </c>
-      <c r="R177" s="9">
+      <c r="S177" s="9">
         <v>2031</v>
       </c>
-      <c r="S177" s="9">
+      <c r="T177" s="9">
         <v>2032</v>
       </c>
-      <c r="T177" s="9">
+      <c r="U177" s="9">
         <v>2033</v>
       </c>
-      <c r="U177" s="9">
+      <c r="V177" s="9">
         <v>2034</v>
       </c>
-      <c r="V177" s="9">
+      <c r="W177" s="9">
         <v>2035</v>
       </c>
-      <c r="W177" s="14"/>
       <c r="X177" s="14"/>
       <c r="Y177" s="14"/>
       <c r="Z177" s="14"/>
@@ -11315,29 +11386,29 @@
       <c r="AJ177" s="14"/>
       <c r="AK177" s="14"/>
       <c r="AL177" s="14"/>
-    </row>
-    <row r="178" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM177" s="14"/>
+    </row>
+    <row r="178" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="9">
         <v>2028</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D178" s="12"/>
-      <c r="E178" s="9">
-        <v>1</v>
-      </c>
       <c r="F178" s="9">
         <v>1</v>
       </c>
-      <c r="G178" s="14"/>
-      <c r="H178" s="9">
+      <c r="G178" s="9">
+        <v>1</v>
+      </c>
+      <c r="H178" s="14"/>
+      <c r="I178" s="9">
         <v>-2</v>
       </c>
-      <c r="I178" s="14"/>
       <c r="J178" s="14"/>
       <c r="K178" s="14"/>
       <c r="L178" s="14"/>
@@ -11367,29 +11438,29 @@
       <c r="AJ178" s="14"/>
       <c r="AK178" s="14"/>
       <c r="AL178" s="14"/>
-    </row>
-    <row r="179" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM178" s="14"/>
+    </row>
+    <row r="179" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="9">
         <v>2029</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D179" s="12"/>
-      <c r="E179" s="9">
-        <v>1</v>
-      </c>
       <c r="F179" s="9">
         <v>1</v>
       </c>
-      <c r="G179" s="14"/>
-      <c r="H179" s="9">
+      <c r="G179" s="9">
+        <v>1</v>
+      </c>
+      <c r="H179" s="14"/>
+      <c r="I179" s="9">
         <v>-2</v>
       </c>
-      <c r="I179" s="14"/>
       <c r="J179" s="14"/>
       <c r="K179" s="14"/>
       <c r="L179" s="14"/>
@@ -11419,29 +11490,29 @@
       <c r="AJ179" s="14"/>
       <c r="AK179" s="14"/>
       <c r="AL179" s="14"/>
-    </row>
-    <row r="180" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM179" s="14"/>
+    </row>
+    <row r="180" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="9">
         <v>2030</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D180" s="12"/>
-      <c r="E180" s="9">
-        <v>1</v>
-      </c>
       <c r="F180" s="9">
         <v>1</v>
       </c>
-      <c r="G180" s="14"/>
-      <c r="H180" s="9">
+      <c r="G180" s="9">
+        <v>1</v>
+      </c>
+      <c r="H180" s="14"/>
+      <c r="I180" s="9">
         <v>-2</v>
       </c>
-      <c r="I180" s="14"/>
       <c r="J180" s="14"/>
       <c r="K180" s="14"/>
       <c r="L180" s="14"/>
@@ -11471,29 +11542,29 @@
       <c r="AJ180" s="14"/>
       <c r="AK180" s="14"/>
       <c r="AL180" s="14"/>
-    </row>
-    <row r="181" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM180" s="14"/>
+    </row>
+    <row r="181" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="9">
         <v>2031</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D181" s="12"/>
-      <c r="E181" s="9">
-        <v>1</v>
-      </c>
       <c r="F181" s="9">
         <v>1</v>
       </c>
-      <c r="G181" s="14"/>
-      <c r="H181" s="9">
+      <c r="G181" s="9">
+        <v>1</v>
+      </c>
+      <c r="H181" s="14"/>
+      <c r="I181" s="9">
         <v>-2</v>
       </c>
-      <c r="I181" s="14"/>
       <c r="J181" s="14"/>
       <c r="K181" s="14"/>
       <c r="L181" s="14"/>
@@ -11523,29 +11594,29 @@
       <c r="AJ181" s="14"/>
       <c r="AK181" s="14"/>
       <c r="AL181" s="14"/>
-    </row>
-    <row r="182" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM181" s="14"/>
+    </row>
+    <row r="182" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="9">
         <v>2032</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D182" s="12"/>
-      <c r="E182" s="9">
-        <v>1</v>
-      </c>
       <c r="F182" s="9">
         <v>1</v>
       </c>
-      <c r="G182" s="14"/>
-      <c r="H182" s="9">
+      <c r="G182" s="9">
+        <v>1</v>
+      </c>
+      <c r="H182" s="14"/>
+      <c r="I182" s="9">
         <v>114509</v>
       </c>
-      <c r="I182" s="14"/>
       <c r="J182" s="14"/>
       <c r="K182" s="14"/>
       <c r="L182" s="14"/>
@@ -11575,29 +11646,29 @@
       <c r="AJ182" s="14"/>
       <c r="AK182" s="14"/>
       <c r="AL182" s="14"/>
-    </row>
-    <row r="183" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM182" s="14"/>
+    </row>
+    <row r="183" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="9">
         <v>2033</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D183" s="12"/>
-      <c r="E183" s="9">
-        <v>1</v>
-      </c>
       <c r="F183" s="9">
         <v>1</v>
       </c>
-      <c r="G183" s="14"/>
-      <c r="H183" s="9">
+      <c r="G183" s="9">
+        <v>1</v>
+      </c>
+      <c r="H183" s="14"/>
+      <c r="I183" s="9">
         <v>2</v>
       </c>
-      <c r="I183" s="14"/>
       <c r="J183" s="14"/>
       <c r="K183" s="14"/>
       <c r="L183" s="14"/>
@@ -11627,29 +11698,29 @@
       <c r="AJ183" s="14"/>
       <c r="AK183" s="14"/>
       <c r="AL183" s="14"/>
-    </row>
-    <row r="184" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM183" s="14"/>
+    </row>
+    <row r="184" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="9">
         <v>2034</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D184" s="12"/>
-      <c r="E184" s="9">
-        <v>1</v>
-      </c>
       <c r="F184" s="9">
         <v>1</v>
       </c>
-      <c r="G184" s="14"/>
-      <c r="H184" s="9">
+      <c r="G184" s="9">
+        <v>1</v>
+      </c>
+      <c r="H184" s="14"/>
+      <c r="I184" s="9">
         <v>2</v>
       </c>
-      <c r="I184" s="14"/>
       <c r="J184" s="14"/>
       <c r="K184" s="14"/>
       <c r="L184" s="14"/>
@@ -11679,29 +11750,29 @@
       <c r="AJ184" s="14"/>
       <c r="AK184" s="14"/>
       <c r="AL184" s="14"/>
-    </row>
-    <row r="185" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM184" s="14"/>
+    </row>
+    <row r="185" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="9">
         <v>2035</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D185" s="12"/>
-      <c r="E185" s="9">
-        <v>1</v>
-      </c>
       <c r="F185" s="9">
         <v>1</v>
       </c>
-      <c r="G185" s="14"/>
-      <c r="H185" s="9">
+      <c r="G185" s="9">
+        <v>1</v>
+      </c>
+      <c r="H185" s="14"/>
+      <c r="I185" s="9">
         <v>2</v>
       </c>
-      <c r="I185" s="14"/>
       <c r="J185" s="14"/>
       <c r="K185" s="14"/>
       <c r="L185" s="14"/>
@@ -11731,25 +11802,25 @@
       <c r="AJ185" s="14"/>
       <c r="AK185" s="14"/>
       <c r="AL185" s="14"/>
-    </row>
-    <row r="186" spans="1:38" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AM185" s="14"/>
+    </row>
+    <row r="186" spans="1:39" ht="39.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="9">
         <v>2036</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D186" s="12"/>
-      <c r="E186" s="9">
+      <c r="F186" s="9">
         <v>2</v>
       </c>
-      <c r="F186" s="9">
-        <v>1</v>
-      </c>
-      <c r="G186" s="14"/>
+      <c r="G186" s="9">
+        <v>1</v>
+      </c>
       <c r="H186" s="14"/>
       <c r="I186" s="14"/>
       <c r="J186" s="14"/>
@@ -11781,6 +11852,7 @@
       <c r="AJ186" s="14"/>
       <c r="AK186" s="14"/>
       <c r="AL186" s="14"/>
+      <c r="AM186" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
